--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{033808B8-8A19-4E73-B247-5809D0614E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9121CAE-5C36-4702-B995-1754C5BEC885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F8293A-8A14-414C-8BA1-65972DD02A92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44819861-42F3-4A24-A9D1-F43700F568CC}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9121CAE-5C36-4702-B995-1754C5BEC885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B18C535-CD7F-4F27-A223-75A005D30D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44819861-42F3-4A24-A9D1-F43700F568CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4AEB857-B009-4239-A488-4A614905572D}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B18C535-CD7F-4F27-A223-75A005D30D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{119401AF-4A8C-42FF-97CA-D4FF3162BA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4AEB857-B009-4239-A488-4A614905572D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561DF167-CD2D-470D-AF82-5083A740B6F2}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{119401AF-4A8C-42FF-97CA-D4FF3162BA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC5636C-C62A-48CB-B277-3FE93C2E07F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561DF167-CD2D-470D-AF82-5083A740B6F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9397B95-A786-417D-A3EA-11F101A7AE6B}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DC5636C-C62A-48CB-B277-3FE93C2E07F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AF124CC-05FE-42F6-8DDE-05A8F60DE6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9397B95-A786-417D-A3EA-11F101A7AE6B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19D85B2-796D-424A-9C5A-719F45E22B1D}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AF124CC-05FE-42F6-8DDE-05A8F60DE6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE3040F6-1227-49A6-AFA7-67D29E2496A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19D85B2-796D-424A-9C5A-719F45E22B1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7212C178-9807-45CF-9484-D58A04BADE45}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE3040F6-1227-49A6-AFA7-67D29E2496A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D51409E-EA2E-4992-8DB5-9009100D289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7212C178-9807-45CF-9484-D58A04BADE45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{896FA6B6-A68F-4CD4-98A4-89099C20CAE2}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D51409E-EA2E-4992-8DB5-9009100D289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C3290E1-0751-4798-97DE-82F7EC3E5C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{896FA6B6-A68F-4CD4-98A4-89099C20CAE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045961B5-8C89-475C-96B8-C9E11F9019EE}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C3290E1-0751-4798-97DE-82F7EC3E5C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F988052-AF58-4D1D-A987-3B2F5AC06CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VEDA_Sets-Comm" sheetId="2" r:id="rId1"/>
@@ -22001,7 +22001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045961B5-8C89-475C-96B8-C9E11F9019EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8930446D-8A98-45E9-A8D8-66A90C598415}">
   <dimension ref="B9:E3479"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52472DFC-DF60-4650-B965-3EF7DC74A139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BFB2A8-91A1-47FF-8604-8215AB1A8583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2278,696 +2278,6 @@
     <t>e_BR411*</t>
   </si>
   <si>
-    <t>rez_sol_001</t>
-  </si>
-  <si>
-    <t>elc_sol_001</t>
-  </si>
-  <si>
-    <t>rez_sol_002</t>
-  </si>
-  <si>
-    <t>elc_sol_002</t>
-  </si>
-  <si>
-    <t>rez_sol_003</t>
-  </si>
-  <si>
-    <t>elc_sol_003</t>
-  </si>
-  <si>
-    <t>rez_sol_004</t>
-  </si>
-  <si>
-    <t>elc_sol_004</t>
-  </si>
-  <si>
-    <t>rez_sol_005</t>
-  </si>
-  <si>
-    <t>elc_sol_005</t>
-  </si>
-  <si>
-    <t>rez_sol_006</t>
-  </si>
-  <si>
-    <t>elc_sol_006</t>
-  </si>
-  <si>
-    <t>rez_sol_007</t>
-  </si>
-  <si>
-    <t>elc_sol_007</t>
-  </si>
-  <si>
-    <t>rez_sol_008</t>
-  </si>
-  <si>
-    <t>elc_sol_008</t>
-  </si>
-  <si>
-    <t>rez_sol_009</t>
-  </si>
-  <si>
-    <t>elc_sol_009</t>
-  </si>
-  <si>
-    <t>rez_sol_010</t>
-  </si>
-  <si>
-    <t>elc_sol_010</t>
-  </si>
-  <si>
-    <t>rez_sol_011</t>
-  </si>
-  <si>
-    <t>elc_sol_011</t>
-  </si>
-  <si>
-    <t>rez_sol_012</t>
-  </si>
-  <si>
-    <t>elc_sol_012</t>
-  </si>
-  <si>
-    <t>rez_sol_013</t>
-  </si>
-  <si>
-    <t>elc_sol_013</t>
-  </si>
-  <si>
-    <t>rez_sol_014</t>
-  </si>
-  <si>
-    <t>elc_sol_014</t>
-  </si>
-  <si>
-    <t>rez_sol_015</t>
-  </si>
-  <si>
-    <t>elc_sol_015</t>
-  </si>
-  <si>
-    <t>rez_sol_016</t>
-  </si>
-  <si>
-    <t>elc_sol_016</t>
-  </si>
-  <si>
-    <t>rez_sol_017</t>
-  </si>
-  <si>
-    <t>elc_sol_017</t>
-  </si>
-  <si>
-    <t>rez_sol_018</t>
-  </si>
-  <si>
-    <t>elc_sol_018</t>
-  </si>
-  <si>
-    <t>rez_sol_019</t>
-  </si>
-  <si>
-    <t>elc_sol_019</t>
-  </si>
-  <si>
-    <t>rez_sol_020</t>
-  </si>
-  <si>
-    <t>elc_sol_020</t>
-  </si>
-  <si>
-    <t>rez_sol_021</t>
-  </si>
-  <si>
-    <t>elc_sol_021</t>
-  </si>
-  <si>
-    <t>rez_sol_022</t>
-  </si>
-  <si>
-    <t>elc_sol_022</t>
-  </si>
-  <si>
-    <t>rez_sol_023</t>
-  </si>
-  <si>
-    <t>elc_sol_023</t>
-  </si>
-  <si>
-    <t>rez_sol_024</t>
-  </si>
-  <si>
-    <t>elc_sol_024</t>
-  </si>
-  <si>
-    <t>rez_sol_025</t>
-  </si>
-  <si>
-    <t>elc_sol_025</t>
-  </si>
-  <si>
-    <t>rez_sol_026</t>
-  </si>
-  <si>
-    <t>elc_sol_026</t>
-  </si>
-  <si>
-    <t>rez_sol_027</t>
-  </si>
-  <si>
-    <t>elc_sol_027</t>
-  </si>
-  <si>
-    <t>rez_sol_028</t>
-  </si>
-  <si>
-    <t>elc_sol_028</t>
-  </si>
-  <si>
-    <t>rez_sol_029</t>
-  </si>
-  <si>
-    <t>elc_sol_029</t>
-  </si>
-  <si>
-    <t>rez_sol_030</t>
-  </si>
-  <si>
-    <t>elc_sol_030</t>
-  </si>
-  <si>
-    <t>rez_sol_031</t>
-  </si>
-  <si>
-    <t>elc_sol_031</t>
-  </si>
-  <si>
-    <t>rez_sol_032</t>
-  </si>
-  <si>
-    <t>elc_sol_032</t>
-  </si>
-  <si>
-    <t>rez_sol_033</t>
-  </si>
-  <si>
-    <t>elc_sol_033</t>
-  </si>
-  <si>
-    <t>rez_sol_034</t>
-  </si>
-  <si>
-    <t>elc_sol_034</t>
-  </si>
-  <si>
-    <t>rez_sol_035</t>
-  </si>
-  <si>
-    <t>elc_sol_035</t>
-  </si>
-  <si>
-    <t>rez_sol_036</t>
-  </si>
-  <si>
-    <t>elc_sol_036</t>
-  </si>
-  <si>
-    <t>rez_sol_037</t>
-  </si>
-  <si>
-    <t>elc_sol_037</t>
-  </si>
-  <si>
-    <t>rez_sol_038</t>
-  </si>
-  <si>
-    <t>elc_sol_038</t>
-  </si>
-  <si>
-    <t>rez_sol_039</t>
-  </si>
-  <si>
-    <t>elc_sol_039</t>
-  </si>
-  <si>
-    <t>rez_sol_040</t>
-  </si>
-  <si>
-    <t>elc_sol_040</t>
-  </si>
-  <si>
-    <t>rez_sol_041</t>
-  </si>
-  <si>
-    <t>elc_sol_041</t>
-  </si>
-  <si>
-    <t>rez_sol_042</t>
-  </si>
-  <si>
-    <t>elc_sol_042</t>
-  </si>
-  <si>
-    <t>rez_sol_043</t>
-  </si>
-  <si>
-    <t>elc_sol_043</t>
-  </si>
-  <si>
-    <t>rez_sol_044</t>
-  </si>
-  <si>
-    <t>elc_sol_044</t>
-  </si>
-  <si>
-    <t>rez_sol_045</t>
-  </si>
-  <si>
-    <t>elc_sol_045</t>
-  </si>
-  <si>
-    <t>rez_sol_046</t>
-  </si>
-  <si>
-    <t>elc_sol_046</t>
-  </si>
-  <si>
-    <t>rez_sol_047</t>
-  </si>
-  <si>
-    <t>elc_sol_047</t>
-  </si>
-  <si>
-    <t>rez_sol_048</t>
-  </si>
-  <si>
-    <t>elc_sol_048</t>
-  </si>
-  <si>
-    <t>rez_sol_049</t>
-  </si>
-  <si>
-    <t>elc_sol_049</t>
-  </si>
-  <si>
-    <t>rez_sol_050</t>
-  </si>
-  <si>
-    <t>elc_sol_050</t>
-  </si>
-  <si>
-    <t>rez_sol_051</t>
-  </si>
-  <si>
-    <t>elc_sol_051</t>
-  </si>
-  <si>
-    <t>rez_sol_052</t>
-  </si>
-  <si>
-    <t>elc_sol_052</t>
-  </si>
-  <si>
-    <t>rez_sol_053</t>
-  </si>
-  <si>
-    <t>elc_sol_053</t>
-  </si>
-  <si>
-    <t>rez_sol_054</t>
-  </si>
-  <si>
-    <t>elc_sol_054</t>
-  </si>
-  <si>
-    <t>rez_sol_055</t>
-  </si>
-  <si>
-    <t>elc_sol_055</t>
-  </si>
-  <si>
-    <t>rez_sol_056</t>
-  </si>
-  <si>
-    <t>elc_sol_056</t>
-  </si>
-  <si>
-    <t>rez_sol_057</t>
-  </si>
-  <si>
-    <t>elc_sol_057</t>
-  </si>
-  <si>
-    <t>rez_sol_058</t>
-  </si>
-  <si>
-    <t>elc_sol_058</t>
-  </si>
-  <si>
-    <t>rez_sol_059</t>
-  </si>
-  <si>
-    <t>elc_sol_059</t>
-  </si>
-  <si>
-    <t>rez_sol_060</t>
-  </si>
-  <si>
-    <t>elc_sol_060</t>
-  </si>
-  <si>
-    <t>rez_sol_061</t>
-  </si>
-  <si>
-    <t>elc_sol_061</t>
-  </si>
-  <si>
-    <t>rez_sol_062</t>
-  </si>
-  <si>
-    <t>elc_sol_062</t>
-  </si>
-  <si>
-    <t>rez_sol_063</t>
-  </si>
-  <si>
-    <t>elc_sol_063</t>
-  </si>
-  <si>
-    <t>rez_sol_064</t>
-  </si>
-  <si>
-    <t>elc_sol_064</t>
-  </si>
-  <si>
-    <t>rez_sol_065</t>
-  </si>
-  <si>
-    <t>elc_sol_065</t>
-  </si>
-  <si>
-    <t>rez_sol_066</t>
-  </si>
-  <si>
-    <t>elc_sol_066</t>
-  </si>
-  <si>
-    <t>rez_sol_067</t>
-  </si>
-  <si>
-    <t>elc_sol_067</t>
-  </si>
-  <si>
-    <t>rez_sol_068</t>
-  </si>
-  <si>
-    <t>elc_sol_068</t>
-  </si>
-  <si>
-    <t>rez_sol_069</t>
-  </si>
-  <si>
-    <t>elc_sol_069</t>
-  </si>
-  <si>
-    <t>rez_sol_070</t>
-  </si>
-  <si>
-    <t>elc_sol_070</t>
-  </si>
-  <si>
-    <t>rez_sol_071</t>
-  </si>
-  <si>
-    <t>elc_sol_071</t>
-  </si>
-  <si>
-    <t>rez_sol_072</t>
-  </si>
-  <si>
-    <t>elc_sol_072</t>
-  </si>
-  <si>
-    <t>rez_sol_073</t>
-  </si>
-  <si>
-    <t>elc_sol_073</t>
-  </si>
-  <si>
-    <t>rez_sol_074</t>
-  </si>
-  <si>
-    <t>elc_sol_074</t>
-  </si>
-  <si>
-    <t>rez_sol_075</t>
-  </si>
-  <si>
-    <t>elc_sol_075</t>
-  </si>
-  <si>
-    <t>rez_sol_076</t>
-  </si>
-  <si>
-    <t>elc_sol_076</t>
-  </si>
-  <si>
-    <t>rez_sol_077</t>
-  </si>
-  <si>
-    <t>elc_sol_077</t>
-  </si>
-  <si>
-    <t>rez_sol_078</t>
-  </si>
-  <si>
-    <t>elc_sol_078</t>
-  </si>
-  <si>
-    <t>rez_sol_079</t>
-  </si>
-  <si>
-    <t>elc_sol_079</t>
-  </si>
-  <si>
-    <t>rez_sol_080</t>
-  </si>
-  <si>
-    <t>elc_sol_080</t>
-  </si>
-  <si>
-    <t>rez_sol_081</t>
-  </si>
-  <si>
-    <t>elc_sol_081</t>
-  </si>
-  <si>
-    <t>rez_sol_082</t>
-  </si>
-  <si>
-    <t>elc_sol_082</t>
-  </si>
-  <si>
-    <t>rez_sol_083</t>
-  </si>
-  <si>
-    <t>elc_sol_083</t>
-  </si>
-  <si>
-    <t>rez_sol_084</t>
-  </si>
-  <si>
-    <t>elc_sol_084</t>
-  </si>
-  <si>
-    <t>rez_sol_085</t>
-  </si>
-  <si>
-    <t>elc_sol_085</t>
-  </si>
-  <si>
-    <t>rez_sol_086</t>
-  </si>
-  <si>
-    <t>elc_sol_086</t>
-  </si>
-  <si>
-    <t>rez_sol_087</t>
-  </si>
-  <si>
-    <t>elc_sol_087</t>
-  </si>
-  <si>
-    <t>rez_sol_088</t>
-  </si>
-  <si>
-    <t>elc_sol_088</t>
-  </si>
-  <si>
-    <t>rez_sol_089</t>
-  </si>
-  <si>
-    <t>elc_sol_089</t>
-  </si>
-  <si>
-    <t>rez_sol_090</t>
-  </si>
-  <si>
-    <t>elc_sol_090</t>
-  </si>
-  <si>
-    <t>rez_sol_091</t>
-  </si>
-  <si>
-    <t>elc_sol_091</t>
-  </si>
-  <si>
-    <t>rez_sol_092</t>
-  </si>
-  <si>
-    <t>elc_sol_092</t>
-  </si>
-  <si>
-    <t>rez_sol_093</t>
-  </si>
-  <si>
-    <t>elc_sol_093</t>
-  </si>
-  <si>
-    <t>rez_sol_094</t>
-  </si>
-  <si>
-    <t>elc_sol_094</t>
-  </si>
-  <si>
-    <t>rez_sol_095</t>
-  </si>
-  <si>
-    <t>elc_sol_095</t>
-  </si>
-  <si>
-    <t>rez_sol_096</t>
-  </si>
-  <si>
-    <t>elc_sol_096</t>
-  </si>
-  <si>
-    <t>rez_sol_097</t>
-  </si>
-  <si>
-    <t>elc_sol_097</t>
-  </si>
-  <si>
-    <t>rez_sol_098</t>
-  </si>
-  <si>
-    <t>elc_sol_098</t>
-  </si>
-  <si>
-    <t>rez_sol_099</t>
-  </si>
-  <si>
-    <t>elc_sol_099</t>
-  </si>
-  <si>
-    <t>rez_sol_100</t>
-  </si>
-  <si>
-    <t>elc_sol_100</t>
-  </si>
-  <si>
-    <t>rez_sol_101</t>
-  </si>
-  <si>
-    <t>elc_sol_101</t>
-  </si>
-  <si>
-    <t>rez_sol_102</t>
-  </si>
-  <si>
-    <t>elc_sol_102</t>
-  </si>
-  <si>
-    <t>rez_sol_103</t>
-  </si>
-  <si>
-    <t>elc_sol_103</t>
-  </si>
-  <si>
-    <t>rez_sol_104</t>
-  </si>
-  <si>
-    <t>elc_sol_104</t>
-  </si>
-  <si>
-    <t>rez_sol_105</t>
-  </si>
-  <si>
-    <t>elc_sol_105</t>
-  </si>
-  <si>
-    <t>rez_sol_106</t>
-  </si>
-  <si>
-    <t>elc_sol_106</t>
-  </si>
-  <si>
-    <t>rez_sol_107</t>
-  </si>
-  <si>
-    <t>elc_sol_107</t>
-  </si>
-  <si>
-    <t>rez_sol_108</t>
-  </si>
-  <si>
-    <t>elc_sol_108</t>
-  </si>
-  <si>
-    <t>rez_sol_109</t>
-  </si>
-  <si>
-    <t>elc_sol_109</t>
-  </si>
-  <si>
-    <t>rez_sol_110</t>
-  </si>
-  <si>
-    <t>elc_sol_110</t>
-  </si>
-  <si>
-    <t>rez_sol_111</t>
-  </si>
-  <si>
-    <t>elc_sol_111</t>
-  </si>
-  <si>
-    <t>rez_sol_112</t>
-  </si>
-  <si>
-    <t>elc_sol_112</t>
-  </si>
-  <si>
-    <t>rez_sol_113</t>
-  </si>
-  <si>
-    <t>elc_sol_113</t>
-  </si>
-  <si>
-    <t>rez_sol_114</t>
-  </si>
-  <si>
-    <t>elc_sol_114</t>
-  </si>
-  <si>
-    <t>rez_sol_115</t>
-  </si>
-  <si>
-    <t>elc_sol_115</t>
-  </si>
-  <si>
     <t>rez_won_001</t>
   </si>
   <si>
@@ -3566,6 +2876,696 @@
   </si>
   <si>
     <t>elc_wof_031</t>
+  </si>
+  <si>
+    <t>rez_spv_001</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>rez_spv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>rez_spv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>rez_spv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>rez_spv_005</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>rez_spv_006</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>rez_spv_007</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>rez_spv_008</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>rez_spv_009</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>rez_spv_010</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>rez_spv_011</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>rez_spv_012</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>rez_spv_013</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>rez_spv_014</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>rez_spv_015</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>rez_spv_016</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>rez_spv_017</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>rez_spv_018</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>rez_spv_019</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>rez_spv_020</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>rez_spv_021</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>rez_spv_022</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>rez_spv_023</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>rez_spv_024</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>rez_spv_025</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>rez_spv_026</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>rez_spv_027</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>rez_spv_028</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>rez_spv_029</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>rez_spv_030</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>rez_spv_031</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>rez_spv_032</t>
+  </si>
+  <si>
+    <t>elc_spv_032</t>
+  </si>
+  <si>
+    <t>rez_spv_033</t>
+  </si>
+  <si>
+    <t>elc_spv_033</t>
+  </si>
+  <si>
+    <t>rez_spv_034</t>
+  </si>
+  <si>
+    <t>elc_spv_034</t>
+  </si>
+  <si>
+    <t>rez_spv_035</t>
+  </si>
+  <si>
+    <t>elc_spv_035</t>
+  </si>
+  <si>
+    <t>rez_spv_036</t>
+  </si>
+  <si>
+    <t>elc_spv_036</t>
+  </si>
+  <si>
+    <t>rez_spv_037</t>
+  </si>
+  <si>
+    <t>elc_spv_037</t>
+  </si>
+  <si>
+    <t>rez_spv_038</t>
+  </si>
+  <si>
+    <t>elc_spv_038</t>
+  </si>
+  <si>
+    <t>rez_spv_039</t>
+  </si>
+  <si>
+    <t>elc_spv_039</t>
+  </si>
+  <si>
+    <t>rez_spv_040</t>
+  </si>
+  <si>
+    <t>elc_spv_040</t>
+  </si>
+  <si>
+    <t>rez_spv_041</t>
+  </si>
+  <si>
+    <t>elc_spv_041</t>
+  </si>
+  <si>
+    <t>rez_spv_042</t>
+  </si>
+  <si>
+    <t>elc_spv_042</t>
+  </si>
+  <si>
+    <t>rez_spv_043</t>
+  </si>
+  <si>
+    <t>elc_spv_043</t>
+  </si>
+  <si>
+    <t>rez_spv_044</t>
+  </si>
+  <si>
+    <t>elc_spv_044</t>
+  </si>
+  <si>
+    <t>rez_spv_045</t>
+  </si>
+  <si>
+    <t>elc_spv_045</t>
+  </si>
+  <si>
+    <t>rez_spv_046</t>
+  </si>
+  <si>
+    <t>elc_spv_046</t>
+  </si>
+  <si>
+    <t>rez_spv_047</t>
+  </si>
+  <si>
+    <t>elc_spv_047</t>
+  </si>
+  <si>
+    <t>rez_spv_048</t>
+  </si>
+  <si>
+    <t>elc_spv_048</t>
+  </si>
+  <si>
+    <t>rez_spv_049</t>
+  </si>
+  <si>
+    <t>elc_spv_049</t>
+  </si>
+  <si>
+    <t>rez_spv_050</t>
+  </si>
+  <si>
+    <t>elc_spv_050</t>
+  </si>
+  <si>
+    <t>rez_spv_051</t>
+  </si>
+  <si>
+    <t>elc_spv_051</t>
+  </si>
+  <si>
+    <t>rez_spv_052</t>
+  </si>
+  <si>
+    <t>elc_spv_052</t>
+  </si>
+  <si>
+    <t>rez_spv_053</t>
+  </si>
+  <si>
+    <t>elc_spv_053</t>
+  </si>
+  <si>
+    <t>rez_spv_054</t>
+  </si>
+  <si>
+    <t>elc_spv_054</t>
+  </si>
+  <si>
+    <t>rez_spv_055</t>
+  </si>
+  <si>
+    <t>elc_spv_055</t>
+  </si>
+  <si>
+    <t>rez_spv_056</t>
+  </si>
+  <si>
+    <t>elc_spv_056</t>
+  </si>
+  <si>
+    <t>rez_spv_057</t>
+  </si>
+  <si>
+    <t>elc_spv_057</t>
+  </si>
+  <si>
+    <t>rez_spv_058</t>
+  </si>
+  <si>
+    <t>elc_spv_058</t>
+  </si>
+  <si>
+    <t>rez_spv_059</t>
+  </si>
+  <si>
+    <t>elc_spv_059</t>
+  </si>
+  <si>
+    <t>rez_spv_060</t>
+  </si>
+  <si>
+    <t>elc_spv_060</t>
+  </si>
+  <si>
+    <t>rez_spv_061</t>
+  </si>
+  <si>
+    <t>elc_spv_061</t>
+  </si>
+  <si>
+    <t>rez_spv_062</t>
+  </si>
+  <si>
+    <t>elc_spv_062</t>
+  </si>
+  <si>
+    <t>rez_spv_063</t>
+  </si>
+  <si>
+    <t>elc_spv_063</t>
+  </si>
+  <si>
+    <t>rez_spv_064</t>
+  </si>
+  <si>
+    <t>elc_spv_064</t>
+  </si>
+  <si>
+    <t>rez_spv_065</t>
+  </si>
+  <si>
+    <t>elc_spv_065</t>
+  </si>
+  <si>
+    <t>rez_spv_066</t>
+  </si>
+  <si>
+    <t>elc_spv_066</t>
+  </si>
+  <si>
+    <t>rez_spv_067</t>
+  </si>
+  <si>
+    <t>elc_spv_067</t>
+  </si>
+  <si>
+    <t>rez_spv_068</t>
+  </si>
+  <si>
+    <t>elc_spv_068</t>
+  </si>
+  <si>
+    <t>rez_spv_069</t>
+  </si>
+  <si>
+    <t>elc_spv_069</t>
+  </si>
+  <si>
+    <t>rez_spv_070</t>
+  </si>
+  <si>
+    <t>elc_spv_070</t>
+  </si>
+  <si>
+    <t>rez_spv_071</t>
+  </si>
+  <si>
+    <t>elc_spv_071</t>
+  </si>
+  <si>
+    <t>rez_spv_072</t>
+  </si>
+  <si>
+    <t>elc_spv_072</t>
+  </si>
+  <si>
+    <t>rez_spv_073</t>
+  </si>
+  <si>
+    <t>elc_spv_073</t>
+  </si>
+  <si>
+    <t>rez_spv_074</t>
+  </si>
+  <si>
+    <t>elc_spv_074</t>
+  </si>
+  <si>
+    <t>rez_spv_075</t>
+  </si>
+  <si>
+    <t>elc_spv_075</t>
+  </si>
+  <si>
+    <t>rez_spv_076</t>
+  </si>
+  <si>
+    <t>elc_spv_076</t>
+  </si>
+  <si>
+    <t>rez_spv_077</t>
+  </si>
+  <si>
+    <t>elc_spv_077</t>
+  </si>
+  <si>
+    <t>rez_spv_078</t>
+  </si>
+  <si>
+    <t>elc_spv_078</t>
+  </si>
+  <si>
+    <t>rez_spv_079</t>
+  </si>
+  <si>
+    <t>elc_spv_079</t>
+  </si>
+  <si>
+    <t>rez_spv_080</t>
+  </si>
+  <si>
+    <t>elc_spv_080</t>
+  </si>
+  <si>
+    <t>rez_spv_081</t>
+  </si>
+  <si>
+    <t>elc_spv_081</t>
+  </si>
+  <si>
+    <t>rez_spv_082</t>
+  </si>
+  <si>
+    <t>elc_spv_082</t>
+  </si>
+  <si>
+    <t>rez_spv_083</t>
+  </si>
+  <si>
+    <t>elc_spv_083</t>
+  </si>
+  <si>
+    <t>rez_spv_084</t>
+  </si>
+  <si>
+    <t>elc_spv_084</t>
+  </si>
+  <si>
+    <t>rez_spv_085</t>
+  </si>
+  <si>
+    <t>elc_spv_085</t>
+  </si>
+  <si>
+    <t>rez_spv_086</t>
+  </si>
+  <si>
+    <t>elc_spv_086</t>
+  </si>
+  <si>
+    <t>rez_spv_087</t>
+  </si>
+  <si>
+    <t>elc_spv_087</t>
+  </si>
+  <si>
+    <t>rez_spv_088</t>
+  </si>
+  <si>
+    <t>elc_spv_088</t>
+  </si>
+  <si>
+    <t>rez_spv_089</t>
+  </si>
+  <si>
+    <t>elc_spv_089</t>
+  </si>
+  <si>
+    <t>rez_spv_090</t>
+  </si>
+  <si>
+    <t>elc_spv_090</t>
+  </si>
+  <si>
+    <t>rez_spv_091</t>
+  </si>
+  <si>
+    <t>elc_spv_091</t>
+  </si>
+  <si>
+    <t>rez_spv_092</t>
+  </si>
+  <si>
+    <t>elc_spv_092</t>
+  </si>
+  <si>
+    <t>rez_spv_093</t>
+  </si>
+  <si>
+    <t>elc_spv_093</t>
+  </si>
+  <si>
+    <t>rez_spv_094</t>
+  </si>
+  <si>
+    <t>elc_spv_094</t>
+  </si>
+  <si>
+    <t>rez_spv_095</t>
+  </si>
+  <si>
+    <t>elc_spv_095</t>
+  </si>
+  <si>
+    <t>rez_spv_096</t>
+  </si>
+  <si>
+    <t>elc_spv_096</t>
+  </si>
+  <si>
+    <t>rez_spv_097</t>
+  </si>
+  <si>
+    <t>elc_spv_097</t>
+  </si>
+  <si>
+    <t>rez_spv_098</t>
+  </si>
+  <si>
+    <t>elc_spv_098</t>
+  </si>
+  <si>
+    <t>rez_spv_099</t>
+  </si>
+  <si>
+    <t>elc_spv_099</t>
+  </si>
+  <si>
+    <t>rez_spv_100</t>
+  </si>
+  <si>
+    <t>elc_spv_100</t>
+  </si>
+  <si>
+    <t>rez_spv_101</t>
+  </si>
+  <si>
+    <t>elc_spv_101</t>
+  </si>
+  <si>
+    <t>rez_spv_102</t>
+  </si>
+  <si>
+    <t>elc_spv_102</t>
+  </si>
+  <si>
+    <t>rez_spv_103</t>
+  </si>
+  <si>
+    <t>elc_spv_103</t>
+  </si>
+  <si>
+    <t>rez_spv_104</t>
+  </si>
+  <si>
+    <t>elc_spv_104</t>
+  </si>
+  <si>
+    <t>rez_spv_105</t>
+  </si>
+  <si>
+    <t>elc_spv_105</t>
+  </si>
+  <si>
+    <t>rez_spv_106</t>
+  </si>
+  <si>
+    <t>elc_spv_106</t>
+  </si>
+  <si>
+    <t>rez_spv_107</t>
+  </si>
+  <si>
+    <t>elc_spv_107</t>
+  </si>
+  <si>
+    <t>rez_spv_108</t>
+  </si>
+  <si>
+    <t>elc_spv_108</t>
+  </si>
+  <si>
+    <t>rez_spv_109</t>
+  </si>
+  <si>
+    <t>elc_spv_109</t>
+  </si>
+  <si>
+    <t>rez_spv_110</t>
+  </si>
+  <si>
+    <t>elc_spv_110</t>
+  </si>
+  <si>
+    <t>rez_spv_111</t>
+  </si>
+  <si>
+    <t>elc_spv_111</t>
+  </si>
+  <si>
+    <t>rez_spv_112</t>
+  </si>
+  <si>
+    <t>elc_spv_112</t>
+  </si>
+  <si>
+    <t>rez_spv_113</t>
+  </si>
+  <si>
+    <t>elc_spv_113</t>
+  </si>
+  <si>
+    <t>rez_spv_114</t>
+  </si>
+  <si>
+    <t>elc_spv_114</t>
+  </si>
+  <si>
+    <t>rez_spv_115</t>
+  </si>
+  <si>
+    <t>elc_spv_115</t>
   </si>
 </sst>
 </file>
@@ -4406,6 +4406,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1511DC3F-90EC-40F9-8035-02FAF19A6694}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
@@ -8922,13 +8927,13 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B332" t="s">
-        <v>746</v>
+        <v>946</v>
       </c>
       <c r="C332" t="s">
-        <v>747</v>
+        <v>947</v>
       </c>
       <c r="D332" t="s">
-        <v>747</v>
+        <v>947</v>
       </c>
       <c r="E332" t="s">
         <v>105</v>
@@ -8936,13 +8941,13 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B333" t="s">
-        <v>748</v>
+        <v>948</v>
       </c>
       <c r="C333" t="s">
-        <v>749</v>
+        <v>949</v>
       </c>
       <c r="D333" t="s">
-        <v>749</v>
+        <v>949</v>
       </c>
       <c r="E333" t="s">
         <v>105</v>
@@ -8950,13 +8955,13 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B334" t="s">
-        <v>750</v>
+        <v>950</v>
       </c>
       <c r="C334" t="s">
-        <v>751</v>
+        <v>951</v>
       </c>
       <c r="D334" t="s">
-        <v>751</v>
+        <v>951</v>
       </c>
       <c r="E334" t="s">
         <v>105</v>
@@ -8964,13 +8969,13 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B335" t="s">
-        <v>752</v>
+        <v>952</v>
       </c>
       <c r="C335" t="s">
-        <v>753</v>
+        <v>953</v>
       </c>
       <c r="D335" t="s">
-        <v>753</v>
+        <v>953</v>
       </c>
       <c r="E335" t="s">
         <v>105</v>
@@ -8978,13 +8983,13 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B336" t="s">
-        <v>754</v>
+        <v>954</v>
       </c>
       <c r="C336" t="s">
-        <v>755</v>
+        <v>955</v>
       </c>
       <c r="D336" t="s">
-        <v>755</v>
+        <v>955</v>
       </c>
       <c r="E336" t="s">
         <v>105</v>
@@ -8992,13 +8997,13 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B337" t="s">
-        <v>756</v>
+        <v>956</v>
       </c>
       <c r="C337" t="s">
-        <v>757</v>
+        <v>957</v>
       </c>
       <c r="D337" t="s">
-        <v>757</v>
+        <v>957</v>
       </c>
       <c r="E337" t="s">
         <v>105</v>
@@ -9006,13 +9011,13 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B338" t="s">
-        <v>758</v>
+        <v>958</v>
       </c>
       <c r="C338" t="s">
-        <v>759</v>
+        <v>959</v>
       </c>
       <c r="D338" t="s">
-        <v>759</v>
+        <v>959</v>
       </c>
       <c r="E338" t="s">
         <v>105</v>
@@ -9020,13 +9025,13 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B339" t="s">
-        <v>760</v>
+        <v>960</v>
       </c>
       <c r="C339" t="s">
-        <v>761</v>
+        <v>961</v>
       </c>
       <c r="D339" t="s">
-        <v>761</v>
+        <v>961</v>
       </c>
       <c r="E339" t="s">
         <v>105</v>
@@ -9034,13 +9039,13 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B340" t="s">
-        <v>762</v>
+        <v>962</v>
       </c>
       <c r="C340" t="s">
-        <v>763</v>
+        <v>963</v>
       </c>
       <c r="D340" t="s">
-        <v>763</v>
+        <v>963</v>
       </c>
       <c r="E340" t="s">
         <v>105</v>
@@ -9048,13 +9053,13 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B341" t="s">
-        <v>764</v>
+        <v>964</v>
       </c>
       <c r="C341" t="s">
-        <v>765</v>
+        <v>965</v>
       </c>
       <c r="D341" t="s">
-        <v>765</v>
+        <v>965</v>
       </c>
       <c r="E341" t="s">
         <v>105</v>
@@ -9062,13 +9067,13 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B342" t="s">
-        <v>766</v>
+        <v>966</v>
       </c>
       <c r="C342" t="s">
-        <v>767</v>
+        <v>967</v>
       </c>
       <c r="D342" t="s">
-        <v>767</v>
+        <v>967</v>
       </c>
       <c r="E342" t="s">
         <v>105</v>
@@ -9076,13 +9081,13 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B343" t="s">
-        <v>768</v>
+        <v>968</v>
       </c>
       <c r="C343" t="s">
-        <v>769</v>
+        <v>969</v>
       </c>
       <c r="D343" t="s">
-        <v>769</v>
+        <v>969</v>
       </c>
       <c r="E343" t="s">
         <v>105</v>
@@ -9090,13 +9095,13 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B344" t="s">
-        <v>770</v>
+        <v>970</v>
       </c>
       <c r="C344" t="s">
-        <v>771</v>
+        <v>971</v>
       </c>
       <c r="D344" t="s">
-        <v>771</v>
+        <v>971</v>
       </c>
       <c r="E344" t="s">
         <v>105</v>
@@ -9104,13 +9109,13 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B345" t="s">
-        <v>772</v>
+        <v>972</v>
       </c>
       <c r="C345" t="s">
-        <v>773</v>
+        <v>973</v>
       </c>
       <c r="D345" t="s">
-        <v>773</v>
+        <v>973</v>
       </c>
       <c r="E345" t="s">
         <v>105</v>
@@ -9118,13 +9123,13 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B346" t="s">
-        <v>774</v>
+        <v>974</v>
       </c>
       <c r="C346" t="s">
-        <v>775</v>
+        <v>975</v>
       </c>
       <c r="D346" t="s">
-        <v>775</v>
+        <v>975</v>
       </c>
       <c r="E346" t="s">
         <v>105</v>
@@ -9132,13 +9137,13 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B347" t="s">
-        <v>776</v>
+        <v>976</v>
       </c>
       <c r="C347" t="s">
-        <v>777</v>
+        <v>977</v>
       </c>
       <c r="D347" t="s">
-        <v>777</v>
+        <v>977</v>
       </c>
       <c r="E347" t="s">
         <v>105</v>
@@ -9146,13 +9151,13 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B348" t="s">
-        <v>778</v>
+        <v>978</v>
       </c>
       <c r="C348" t="s">
-        <v>779</v>
+        <v>979</v>
       </c>
       <c r="D348" t="s">
-        <v>779</v>
+        <v>979</v>
       </c>
       <c r="E348" t="s">
         <v>105</v>
@@ -9160,13 +9165,13 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B349" t="s">
-        <v>780</v>
+        <v>980</v>
       </c>
       <c r="C349" t="s">
-        <v>781</v>
+        <v>981</v>
       </c>
       <c r="D349" t="s">
-        <v>781</v>
+        <v>981</v>
       </c>
       <c r="E349" t="s">
         <v>105</v>
@@ -9174,13 +9179,13 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B350" t="s">
-        <v>782</v>
+        <v>982</v>
       </c>
       <c r="C350" t="s">
-        <v>783</v>
+        <v>983</v>
       </c>
       <c r="D350" t="s">
-        <v>783</v>
+        <v>983</v>
       </c>
       <c r="E350" t="s">
         <v>105</v>
@@ -9188,13 +9193,13 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B351" t="s">
-        <v>784</v>
+        <v>984</v>
       </c>
       <c r="C351" t="s">
-        <v>785</v>
+        <v>985</v>
       </c>
       <c r="D351" t="s">
-        <v>785</v>
+        <v>985</v>
       </c>
       <c r="E351" t="s">
         <v>105</v>
@@ -9202,13 +9207,13 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B352" t="s">
-        <v>786</v>
+        <v>986</v>
       </c>
       <c r="C352" t="s">
-        <v>787</v>
+        <v>987</v>
       </c>
       <c r="D352" t="s">
-        <v>787</v>
+        <v>987</v>
       </c>
       <c r="E352" t="s">
         <v>105</v>
@@ -9216,13 +9221,13 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B353" t="s">
-        <v>788</v>
+        <v>988</v>
       </c>
       <c r="C353" t="s">
-        <v>789</v>
+        <v>989</v>
       </c>
       <c r="D353" t="s">
-        <v>789</v>
+        <v>989</v>
       </c>
       <c r="E353" t="s">
         <v>105</v>
@@ -9230,13 +9235,13 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B354" t="s">
-        <v>790</v>
+        <v>990</v>
       </c>
       <c r="C354" t="s">
-        <v>791</v>
+        <v>991</v>
       </c>
       <c r="D354" t="s">
-        <v>791</v>
+        <v>991</v>
       </c>
       <c r="E354" t="s">
         <v>105</v>
@@ -9244,13 +9249,13 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B355" t="s">
-        <v>792</v>
+        <v>992</v>
       </c>
       <c r="C355" t="s">
-        <v>793</v>
+        <v>993</v>
       </c>
       <c r="D355" t="s">
-        <v>793</v>
+        <v>993</v>
       </c>
       <c r="E355" t="s">
         <v>105</v>
@@ -9258,13 +9263,13 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B356" t="s">
-        <v>794</v>
+        <v>994</v>
       </c>
       <c r="C356" t="s">
-        <v>795</v>
+        <v>995</v>
       </c>
       <c r="D356" t="s">
-        <v>795</v>
+        <v>995</v>
       </c>
       <c r="E356" t="s">
         <v>105</v>
@@ -9272,13 +9277,13 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B357" t="s">
-        <v>796</v>
+        <v>996</v>
       </c>
       <c r="C357" t="s">
-        <v>797</v>
+        <v>997</v>
       </c>
       <c r="D357" t="s">
-        <v>797</v>
+        <v>997</v>
       </c>
       <c r="E357" t="s">
         <v>105</v>
@@ -9286,13 +9291,13 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B358" t="s">
-        <v>798</v>
+        <v>998</v>
       </c>
       <c r="C358" t="s">
-        <v>799</v>
+        <v>999</v>
       </c>
       <c r="D358" t="s">
-        <v>799</v>
+        <v>999</v>
       </c>
       <c r="E358" t="s">
         <v>105</v>
@@ -9300,13 +9305,13 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B359" t="s">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C359" t="s">
-        <v>801</v>
+        <v>1001</v>
       </c>
       <c r="D359" t="s">
-        <v>801</v>
+        <v>1001</v>
       </c>
       <c r="E359" t="s">
         <v>105</v>
@@ -9314,13 +9319,13 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B360" t="s">
-        <v>802</v>
+        <v>1002</v>
       </c>
       <c r="C360" t="s">
-        <v>803</v>
+        <v>1003</v>
       </c>
       <c r="D360" t="s">
-        <v>803</v>
+        <v>1003</v>
       </c>
       <c r="E360" t="s">
         <v>105</v>
@@ -9328,13 +9333,13 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B361" t="s">
-        <v>804</v>
+        <v>1004</v>
       </c>
       <c r="C361" t="s">
-        <v>805</v>
+        <v>1005</v>
       </c>
       <c r="D361" t="s">
-        <v>805</v>
+        <v>1005</v>
       </c>
       <c r="E361" t="s">
         <v>105</v>
@@ -9342,13 +9347,13 @@
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B362" t="s">
-        <v>806</v>
+        <v>1006</v>
       </c>
       <c r="C362" t="s">
-        <v>807</v>
+        <v>1007</v>
       </c>
       <c r="D362" t="s">
-        <v>807</v>
+        <v>1007</v>
       </c>
       <c r="E362" t="s">
         <v>105</v>
@@ -9356,13 +9361,13 @@
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B363" t="s">
-        <v>808</v>
+        <v>1008</v>
       </c>
       <c r="C363" t="s">
-        <v>809</v>
+        <v>1009</v>
       </c>
       <c r="D363" t="s">
-        <v>809</v>
+        <v>1009</v>
       </c>
       <c r="E363" t="s">
         <v>105</v>
@@ -9370,13 +9375,13 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B364" t="s">
-        <v>810</v>
+        <v>1010</v>
       </c>
       <c r="C364" t="s">
-        <v>811</v>
+        <v>1011</v>
       </c>
       <c r="D364" t="s">
-        <v>811</v>
+        <v>1011</v>
       </c>
       <c r="E364" t="s">
         <v>105</v>
@@ -9384,13 +9389,13 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B365" t="s">
-        <v>812</v>
+        <v>1012</v>
       </c>
       <c r="C365" t="s">
-        <v>813</v>
+        <v>1013</v>
       </c>
       <c r="D365" t="s">
-        <v>813</v>
+        <v>1013</v>
       </c>
       <c r="E365" t="s">
         <v>105</v>
@@ -9398,13 +9403,13 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B366" t="s">
-        <v>814</v>
+        <v>1014</v>
       </c>
       <c r="C366" t="s">
-        <v>815</v>
+        <v>1015</v>
       </c>
       <c r="D366" t="s">
-        <v>815</v>
+        <v>1015</v>
       </c>
       <c r="E366" t="s">
         <v>105</v>
@@ -9412,13 +9417,13 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B367" t="s">
-        <v>816</v>
+        <v>1016</v>
       </c>
       <c r="C367" t="s">
-        <v>817</v>
+        <v>1017</v>
       </c>
       <c r="D367" t="s">
-        <v>817</v>
+        <v>1017</v>
       </c>
       <c r="E367" t="s">
         <v>105</v>
@@ -9426,13 +9431,13 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B368" t="s">
-        <v>818</v>
+        <v>1018</v>
       </c>
       <c r="C368" t="s">
-        <v>819</v>
+        <v>1019</v>
       </c>
       <c r="D368" t="s">
-        <v>819</v>
+        <v>1019</v>
       </c>
       <c r="E368" t="s">
         <v>105</v>
@@ -9440,13 +9445,13 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B369" t="s">
-        <v>820</v>
+        <v>1020</v>
       </c>
       <c r="C369" t="s">
-        <v>821</v>
+        <v>1021</v>
       </c>
       <c r="D369" t="s">
-        <v>821</v>
+        <v>1021</v>
       </c>
       <c r="E369" t="s">
         <v>105</v>
@@ -9454,13 +9459,13 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B370" t="s">
-        <v>822</v>
+        <v>1022</v>
       </c>
       <c r="C370" t="s">
-        <v>823</v>
+        <v>1023</v>
       </c>
       <c r="D370" t="s">
-        <v>823</v>
+        <v>1023</v>
       </c>
       <c r="E370" t="s">
         <v>105</v>
@@ -9468,13 +9473,13 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B371" t="s">
-        <v>824</v>
+        <v>1024</v>
       </c>
       <c r="C371" t="s">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="D371" t="s">
-        <v>825</v>
+        <v>1025</v>
       </c>
       <c r="E371" t="s">
         <v>105</v>
@@ -9482,13 +9487,13 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B372" t="s">
-        <v>826</v>
+        <v>1026</v>
       </c>
       <c r="C372" t="s">
-        <v>827</v>
+        <v>1027</v>
       </c>
       <c r="D372" t="s">
-        <v>827</v>
+        <v>1027</v>
       </c>
       <c r="E372" t="s">
         <v>105</v>
@@ -9496,13 +9501,13 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B373" t="s">
-        <v>828</v>
+        <v>1028</v>
       </c>
       <c r="C373" t="s">
-        <v>829</v>
+        <v>1029</v>
       </c>
       <c r="D373" t="s">
-        <v>829</v>
+        <v>1029</v>
       </c>
       <c r="E373" t="s">
         <v>105</v>
@@ -9510,13 +9515,13 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B374" t="s">
-        <v>830</v>
+        <v>1030</v>
       </c>
       <c r="C374" t="s">
-        <v>831</v>
+        <v>1031</v>
       </c>
       <c r="D374" t="s">
-        <v>831</v>
+        <v>1031</v>
       </c>
       <c r="E374" t="s">
         <v>105</v>
@@ -9524,13 +9529,13 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B375" t="s">
-        <v>832</v>
+        <v>1032</v>
       </c>
       <c r="C375" t="s">
-        <v>833</v>
+        <v>1033</v>
       </c>
       <c r="D375" t="s">
-        <v>833</v>
+        <v>1033</v>
       </c>
       <c r="E375" t="s">
         <v>105</v>
@@ -9538,13 +9543,13 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B376" t="s">
-        <v>834</v>
+        <v>1034</v>
       </c>
       <c r="C376" t="s">
-        <v>835</v>
+        <v>1035</v>
       </c>
       <c r="D376" t="s">
-        <v>835</v>
+        <v>1035</v>
       </c>
       <c r="E376" t="s">
         <v>105</v>
@@ -9552,13 +9557,13 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B377" t="s">
-        <v>836</v>
+        <v>1036</v>
       </c>
       <c r="C377" t="s">
-        <v>837</v>
+        <v>1037</v>
       </c>
       <c r="D377" t="s">
-        <v>837</v>
+        <v>1037</v>
       </c>
       <c r="E377" t="s">
         <v>105</v>
@@ -9566,13 +9571,13 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B378" t="s">
-        <v>838</v>
+        <v>1038</v>
       </c>
       <c r="C378" t="s">
-        <v>839</v>
+        <v>1039</v>
       </c>
       <c r="D378" t="s">
-        <v>839</v>
+        <v>1039</v>
       </c>
       <c r="E378" t="s">
         <v>105</v>
@@ -9580,13 +9585,13 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B379" t="s">
-        <v>840</v>
+        <v>1040</v>
       </c>
       <c r="C379" t="s">
-        <v>841</v>
+        <v>1041</v>
       </c>
       <c r="D379" t="s">
-        <v>841</v>
+        <v>1041</v>
       </c>
       <c r="E379" t="s">
         <v>105</v>
@@ -9594,13 +9599,13 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B380" t="s">
-        <v>842</v>
+        <v>1042</v>
       </c>
       <c r="C380" t="s">
-        <v>843</v>
+        <v>1043</v>
       </c>
       <c r="D380" t="s">
-        <v>843</v>
+        <v>1043</v>
       </c>
       <c r="E380" t="s">
         <v>105</v>
@@ -9608,13 +9613,13 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B381" t="s">
-        <v>844</v>
+        <v>1044</v>
       </c>
       <c r="C381" t="s">
-        <v>845</v>
+        <v>1045</v>
       </c>
       <c r="D381" t="s">
-        <v>845</v>
+        <v>1045</v>
       </c>
       <c r="E381" t="s">
         <v>105</v>
@@ -9622,13 +9627,13 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B382" t="s">
-        <v>846</v>
+        <v>1046</v>
       </c>
       <c r="C382" t="s">
-        <v>847</v>
+        <v>1047</v>
       </c>
       <c r="D382" t="s">
-        <v>847</v>
+        <v>1047</v>
       </c>
       <c r="E382" t="s">
         <v>105</v>
@@ -9636,13 +9641,13 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B383" t="s">
-        <v>848</v>
+        <v>1048</v>
       </c>
       <c r="C383" t="s">
-        <v>849</v>
+        <v>1049</v>
       </c>
       <c r="D383" t="s">
-        <v>849</v>
+        <v>1049</v>
       </c>
       <c r="E383" t="s">
         <v>105</v>
@@ -9650,13 +9655,13 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B384" t="s">
-        <v>850</v>
+        <v>1050</v>
       </c>
       <c r="C384" t="s">
-        <v>851</v>
+        <v>1051</v>
       </c>
       <c r="D384" t="s">
-        <v>851</v>
+        <v>1051</v>
       </c>
       <c r="E384" t="s">
         <v>105</v>
@@ -9664,13 +9669,13 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B385" t="s">
-        <v>852</v>
+        <v>1052</v>
       </c>
       <c r="C385" t="s">
-        <v>853</v>
+        <v>1053</v>
       </c>
       <c r="D385" t="s">
-        <v>853</v>
+        <v>1053</v>
       </c>
       <c r="E385" t="s">
         <v>105</v>
@@ -9678,13 +9683,13 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B386" t="s">
-        <v>854</v>
+        <v>1054</v>
       </c>
       <c r="C386" t="s">
-        <v>855</v>
+        <v>1055</v>
       </c>
       <c r="D386" t="s">
-        <v>855</v>
+        <v>1055</v>
       </c>
       <c r="E386" t="s">
         <v>105</v>
@@ -9692,13 +9697,13 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B387" t="s">
-        <v>856</v>
+        <v>1056</v>
       </c>
       <c r="C387" t="s">
-        <v>857</v>
+        <v>1057</v>
       </c>
       <c r="D387" t="s">
-        <v>857</v>
+        <v>1057</v>
       </c>
       <c r="E387" t="s">
         <v>105</v>
@@ -9706,13 +9711,13 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B388" t="s">
-        <v>858</v>
+        <v>1058</v>
       </c>
       <c r="C388" t="s">
-        <v>859</v>
+        <v>1059</v>
       </c>
       <c r="D388" t="s">
-        <v>859</v>
+        <v>1059</v>
       </c>
       <c r="E388" t="s">
         <v>105</v>
@@ -9720,13 +9725,13 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B389" t="s">
-        <v>860</v>
+        <v>1060</v>
       </c>
       <c r="C389" t="s">
-        <v>861</v>
+        <v>1061</v>
       </c>
       <c r="D389" t="s">
-        <v>861</v>
+        <v>1061</v>
       </c>
       <c r="E389" t="s">
         <v>105</v>
@@ -9734,13 +9739,13 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B390" t="s">
-        <v>862</v>
+        <v>1062</v>
       </c>
       <c r="C390" t="s">
-        <v>863</v>
+        <v>1063</v>
       </c>
       <c r="D390" t="s">
-        <v>863</v>
+        <v>1063</v>
       </c>
       <c r="E390" t="s">
         <v>105</v>
@@ -9748,13 +9753,13 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B391" t="s">
-        <v>864</v>
+        <v>1064</v>
       </c>
       <c r="C391" t="s">
-        <v>865</v>
+        <v>1065</v>
       </c>
       <c r="D391" t="s">
-        <v>865</v>
+        <v>1065</v>
       </c>
       <c r="E391" t="s">
         <v>105</v>
@@ -9762,13 +9767,13 @@
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B392" t="s">
-        <v>866</v>
+        <v>1066</v>
       </c>
       <c r="C392" t="s">
-        <v>867</v>
+        <v>1067</v>
       </c>
       <c r="D392" t="s">
-        <v>867</v>
+        <v>1067</v>
       </c>
       <c r="E392" t="s">
         <v>105</v>
@@ -9776,13 +9781,13 @@
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B393" t="s">
-        <v>868</v>
+        <v>1068</v>
       </c>
       <c r="C393" t="s">
-        <v>869</v>
+        <v>1069</v>
       </c>
       <c r="D393" t="s">
-        <v>869</v>
+        <v>1069</v>
       </c>
       <c r="E393" t="s">
         <v>105</v>
@@ -9790,13 +9795,13 @@
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
-        <v>870</v>
+        <v>1070</v>
       </c>
       <c r="C394" t="s">
-        <v>871</v>
+        <v>1071</v>
       </c>
       <c r="D394" t="s">
-        <v>871</v>
+        <v>1071</v>
       </c>
       <c r="E394" t="s">
         <v>105</v>
@@ -9804,13 +9809,13 @@
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B395" t="s">
-        <v>872</v>
+        <v>1072</v>
       </c>
       <c r="C395" t="s">
-        <v>873</v>
+        <v>1073</v>
       </c>
       <c r="D395" t="s">
-        <v>873</v>
+        <v>1073</v>
       </c>
       <c r="E395" t="s">
         <v>105</v>
@@ -9818,13 +9823,13 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B396" t="s">
-        <v>874</v>
+        <v>1074</v>
       </c>
       <c r="C396" t="s">
-        <v>875</v>
+        <v>1075</v>
       </c>
       <c r="D396" t="s">
-        <v>875</v>
+        <v>1075</v>
       </c>
       <c r="E396" t="s">
         <v>105</v>
@@ -9832,13 +9837,13 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B397" t="s">
-        <v>876</v>
+        <v>1076</v>
       </c>
       <c r="C397" t="s">
-        <v>877</v>
+        <v>1077</v>
       </c>
       <c r="D397" t="s">
-        <v>877</v>
+        <v>1077</v>
       </c>
       <c r="E397" t="s">
         <v>105</v>
@@ -9846,13 +9851,13 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B398" t="s">
-        <v>878</v>
+        <v>1078</v>
       </c>
       <c r="C398" t="s">
-        <v>879</v>
+        <v>1079</v>
       </c>
       <c r="D398" t="s">
-        <v>879</v>
+        <v>1079</v>
       </c>
       <c r="E398" t="s">
         <v>105</v>
@@ -9860,13 +9865,13 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B399" t="s">
-        <v>880</v>
+        <v>1080</v>
       </c>
       <c r="C399" t="s">
-        <v>881</v>
+        <v>1081</v>
       </c>
       <c r="D399" t="s">
-        <v>881</v>
+        <v>1081</v>
       </c>
       <c r="E399" t="s">
         <v>105</v>
@@ -9874,13 +9879,13 @@
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B400" t="s">
-        <v>882</v>
+        <v>1082</v>
       </c>
       <c r="C400" t="s">
-        <v>883</v>
+        <v>1083</v>
       </c>
       <c r="D400" t="s">
-        <v>883</v>
+        <v>1083</v>
       </c>
       <c r="E400" t="s">
         <v>105</v>
@@ -9888,13 +9893,13 @@
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B401" t="s">
-        <v>884</v>
+        <v>1084</v>
       </c>
       <c r="C401" t="s">
-        <v>885</v>
+        <v>1085</v>
       </c>
       <c r="D401" t="s">
-        <v>885</v>
+        <v>1085</v>
       </c>
       <c r="E401" t="s">
         <v>105</v>
@@ -9902,13 +9907,13 @@
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B402" t="s">
-        <v>886</v>
+        <v>1086</v>
       </c>
       <c r="C402" t="s">
-        <v>887</v>
+        <v>1087</v>
       </c>
       <c r="D402" t="s">
-        <v>887</v>
+        <v>1087</v>
       </c>
       <c r="E402" t="s">
         <v>105</v>
@@ -9916,13 +9921,13 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B403" t="s">
-        <v>888</v>
+        <v>1088</v>
       </c>
       <c r="C403" t="s">
-        <v>889</v>
+        <v>1089</v>
       </c>
       <c r="D403" t="s">
-        <v>889</v>
+        <v>1089</v>
       </c>
       <c r="E403" t="s">
         <v>105</v>
@@ -9930,13 +9935,13 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B404" t="s">
-        <v>890</v>
+        <v>1090</v>
       </c>
       <c r="C404" t="s">
-        <v>891</v>
+        <v>1091</v>
       </c>
       <c r="D404" t="s">
-        <v>891</v>
+        <v>1091</v>
       </c>
       <c r="E404" t="s">
         <v>105</v>
@@ -9944,13 +9949,13 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B405" t="s">
-        <v>892</v>
+        <v>1092</v>
       </c>
       <c r="C405" t="s">
-        <v>893</v>
+        <v>1093</v>
       </c>
       <c r="D405" t="s">
-        <v>893</v>
+        <v>1093</v>
       </c>
       <c r="E405" t="s">
         <v>105</v>
@@ -9958,13 +9963,13 @@
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B406" t="s">
-        <v>894</v>
+        <v>1094</v>
       </c>
       <c r="C406" t="s">
-        <v>895</v>
+        <v>1095</v>
       </c>
       <c r="D406" t="s">
-        <v>895</v>
+        <v>1095</v>
       </c>
       <c r="E406" t="s">
         <v>105</v>
@@ -9972,13 +9977,13 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B407" t="s">
-        <v>896</v>
+        <v>1096</v>
       </c>
       <c r="C407" t="s">
-        <v>897</v>
+        <v>1097</v>
       </c>
       <c r="D407" t="s">
-        <v>897</v>
+        <v>1097</v>
       </c>
       <c r="E407" t="s">
         <v>105</v>
@@ -9986,13 +9991,13 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B408" t="s">
-        <v>898</v>
+        <v>1098</v>
       </c>
       <c r="C408" t="s">
-        <v>899</v>
+        <v>1099</v>
       </c>
       <c r="D408" t="s">
-        <v>899</v>
+        <v>1099</v>
       </c>
       <c r="E408" t="s">
         <v>105</v>
@@ -10000,13 +10005,13 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B409" t="s">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="C409" t="s">
-        <v>901</v>
+        <v>1101</v>
       </c>
       <c r="D409" t="s">
-        <v>901</v>
+        <v>1101</v>
       </c>
       <c r="E409" t="s">
         <v>105</v>
@@ -10014,13 +10019,13 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B410" t="s">
-        <v>902</v>
+        <v>1102</v>
       </c>
       <c r="C410" t="s">
-        <v>903</v>
+        <v>1103</v>
       </c>
       <c r="D410" t="s">
-        <v>903</v>
+        <v>1103</v>
       </c>
       <c r="E410" t="s">
         <v>105</v>
@@ -10028,13 +10033,13 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B411" t="s">
-        <v>904</v>
+        <v>1104</v>
       </c>
       <c r="C411" t="s">
-        <v>905</v>
+        <v>1105</v>
       </c>
       <c r="D411" t="s">
-        <v>905</v>
+        <v>1105</v>
       </c>
       <c r="E411" t="s">
         <v>105</v>
@@ -10042,13 +10047,13 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B412" t="s">
-        <v>906</v>
+        <v>1106</v>
       </c>
       <c r="C412" t="s">
-        <v>907</v>
+        <v>1107</v>
       </c>
       <c r="D412" t="s">
-        <v>907</v>
+        <v>1107</v>
       </c>
       <c r="E412" t="s">
         <v>105</v>
@@ -10056,13 +10061,13 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B413" t="s">
-        <v>908</v>
+        <v>1108</v>
       </c>
       <c r="C413" t="s">
-        <v>909</v>
+        <v>1109</v>
       </c>
       <c r="D413" t="s">
-        <v>909</v>
+        <v>1109</v>
       </c>
       <c r="E413" t="s">
         <v>105</v>
@@ -10070,13 +10075,13 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B414" t="s">
-        <v>910</v>
+        <v>1110</v>
       </c>
       <c r="C414" t="s">
-        <v>911</v>
+        <v>1111</v>
       </c>
       <c r="D414" t="s">
-        <v>911</v>
+        <v>1111</v>
       </c>
       <c r="E414" t="s">
         <v>105</v>
@@ -10084,13 +10089,13 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B415" t="s">
-        <v>912</v>
+        <v>1112</v>
       </c>
       <c r="C415" t="s">
-        <v>913</v>
+        <v>1113</v>
       </c>
       <c r="D415" t="s">
-        <v>913</v>
+        <v>1113</v>
       </c>
       <c r="E415" t="s">
         <v>105</v>
@@ -10098,13 +10103,13 @@
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B416" t="s">
-        <v>914</v>
+        <v>1114</v>
       </c>
       <c r="C416" t="s">
-        <v>915</v>
+        <v>1115</v>
       </c>
       <c r="D416" t="s">
-        <v>915</v>
+        <v>1115</v>
       </c>
       <c r="E416" t="s">
         <v>105</v>
@@ -10112,13 +10117,13 @@
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B417" t="s">
-        <v>916</v>
+        <v>1116</v>
       </c>
       <c r="C417" t="s">
-        <v>917</v>
+        <v>1117</v>
       </c>
       <c r="D417" t="s">
-        <v>917</v>
+        <v>1117</v>
       </c>
       <c r="E417" t="s">
         <v>105</v>
@@ -10126,13 +10131,13 @@
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B418" t="s">
-        <v>918</v>
+        <v>1118</v>
       </c>
       <c r="C418" t="s">
-        <v>919</v>
+        <v>1119</v>
       </c>
       <c r="D418" t="s">
-        <v>919</v>
+        <v>1119</v>
       </c>
       <c r="E418" t="s">
         <v>105</v>
@@ -10140,13 +10145,13 @@
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B419" t="s">
-        <v>920</v>
+        <v>1120</v>
       </c>
       <c r="C419" t="s">
-        <v>921</v>
+        <v>1121</v>
       </c>
       <c r="D419" t="s">
-        <v>921</v>
+        <v>1121</v>
       </c>
       <c r="E419" t="s">
         <v>105</v>
@@ -10154,13 +10159,13 @@
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B420" t="s">
-        <v>922</v>
+        <v>1122</v>
       </c>
       <c r="C420" t="s">
-        <v>923</v>
+        <v>1123</v>
       </c>
       <c r="D420" t="s">
-        <v>923</v>
+        <v>1123</v>
       </c>
       <c r="E420" t="s">
         <v>105</v>
@@ -10168,13 +10173,13 @@
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B421" t="s">
-        <v>924</v>
+        <v>1124</v>
       </c>
       <c r="C421" t="s">
-        <v>925</v>
+        <v>1125</v>
       </c>
       <c r="D421" t="s">
-        <v>925</v>
+        <v>1125</v>
       </c>
       <c r="E421" t="s">
         <v>105</v>
@@ -10182,13 +10187,13 @@
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B422" t="s">
-        <v>926</v>
+        <v>1126</v>
       </c>
       <c r="C422" t="s">
-        <v>927</v>
+        <v>1127</v>
       </c>
       <c r="D422" t="s">
-        <v>927</v>
+        <v>1127</v>
       </c>
       <c r="E422" t="s">
         <v>105</v>
@@ -10196,13 +10201,13 @@
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B423" t="s">
-        <v>928</v>
+        <v>1128</v>
       </c>
       <c r="C423" t="s">
-        <v>929</v>
+        <v>1129</v>
       </c>
       <c r="D423" t="s">
-        <v>929</v>
+        <v>1129</v>
       </c>
       <c r="E423" t="s">
         <v>105</v>
@@ -10210,13 +10215,13 @@
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B424" t="s">
-        <v>930</v>
+        <v>1130</v>
       </c>
       <c r="C424" t="s">
-        <v>931</v>
+        <v>1131</v>
       </c>
       <c r="D424" t="s">
-        <v>931</v>
+        <v>1131</v>
       </c>
       <c r="E424" t="s">
         <v>105</v>
@@ -10224,13 +10229,13 @@
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B425" t="s">
-        <v>932</v>
+        <v>1132</v>
       </c>
       <c r="C425" t="s">
-        <v>933</v>
+        <v>1133</v>
       </c>
       <c r="D425" t="s">
-        <v>933</v>
+        <v>1133</v>
       </c>
       <c r="E425" t="s">
         <v>105</v>
@@ -10238,13 +10243,13 @@
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B426" t="s">
-        <v>934</v>
+        <v>1134</v>
       </c>
       <c r="C426" t="s">
-        <v>935</v>
+        <v>1135</v>
       </c>
       <c r="D426" t="s">
-        <v>935</v>
+        <v>1135</v>
       </c>
       <c r="E426" t="s">
         <v>105</v>
@@ -10252,13 +10257,13 @@
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B427" t="s">
-        <v>936</v>
+        <v>1136</v>
       </c>
       <c r="C427" t="s">
-        <v>937</v>
+        <v>1137</v>
       </c>
       <c r="D427" t="s">
-        <v>937</v>
+        <v>1137</v>
       </c>
       <c r="E427" t="s">
         <v>105</v>
@@ -10266,13 +10271,13 @@
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B428" t="s">
-        <v>938</v>
+        <v>1138</v>
       </c>
       <c r="C428" t="s">
-        <v>939</v>
+        <v>1139</v>
       </c>
       <c r="D428" t="s">
-        <v>939</v>
+        <v>1139</v>
       </c>
       <c r="E428" t="s">
         <v>105</v>
@@ -10280,13 +10285,13 @@
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B429" t="s">
-        <v>940</v>
+        <v>1140</v>
       </c>
       <c r="C429" t="s">
-        <v>941</v>
+        <v>1141</v>
       </c>
       <c r="D429" t="s">
-        <v>941</v>
+        <v>1141</v>
       </c>
       <c r="E429" t="s">
         <v>105</v>
@@ -10294,13 +10299,13 @@
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B430" t="s">
-        <v>942</v>
+        <v>1142</v>
       </c>
       <c r="C430" t="s">
-        <v>943</v>
+        <v>1143</v>
       </c>
       <c r="D430" t="s">
-        <v>943</v>
+        <v>1143</v>
       </c>
       <c r="E430" t="s">
         <v>105</v>
@@ -10308,13 +10313,13 @@
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B431" t="s">
-        <v>944</v>
+        <v>1144</v>
       </c>
       <c r="C431" t="s">
-        <v>945</v>
+        <v>1145</v>
       </c>
       <c r="D431" t="s">
-        <v>945</v>
+        <v>1145</v>
       </c>
       <c r="E431" t="s">
         <v>105</v>
@@ -10322,13 +10327,13 @@
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B432" t="s">
-        <v>946</v>
+        <v>1146</v>
       </c>
       <c r="C432" t="s">
-        <v>947</v>
+        <v>1147</v>
       </c>
       <c r="D432" t="s">
-        <v>947</v>
+        <v>1147</v>
       </c>
       <c r="E432" t="s">
         <v>105</v>
@@ -10336,13 +10341,13 @@
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B433" t="s">
-        <v>948</v>
+        <v>1148</v>
       </c>
       <c r="C433" t="s">
-        <v>949</v>
+        <v>1149</v>
       </c>
       <c r="D433" t="s">
-        <v>949</v>
+        <v>1149</v>
       </c>
       <c r="E433" t="s">
         <v>105</v>
@@ -10350,13 +10355,13 @@
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B434" t="s">
-        <v>950</v>
+        <v>1150</v>
       </c>
       <c r="C434" t="s">
-        <v>951</v>
+        <v>1151</v>
       </c>
       <c r="D434" t="s">
-        <v>951</v>
+        <v>1151</v>
       </c>
       <c r="E434" t="s">
         <v>105</v>
@@ -10364,13 +10369,13 @@
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B435" t="s">
-        <v>952</v>
+        <v>1152</v>
       </c>
       <c r="C435" t="s">
-        <v>953</v>
+        <v>1153</v>
       </c>
       <c r="D435" t="s">
-        <v>953</v>
+        <v>1153</v>
       </c>
       <c r="E435" t="s">
         <v>105</v>
@@ -10378,13 +10383,13 @@
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B436" t="s">
-        <v>954</v>
+        <v>1154</v>
       </c>
       <c r="C436" t="s">
-        <v>955</v>
+        <v>1155</v>
       </c>
       <c r="D436" t="s">
-        <v>955</v>
+        <v>1155</v>
       </c>
       <c r="E436" t="s">
         <v>105</v>
@@ -10392,13 +10397,13 @@
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B437" t="s">
-        <v>956</v>
+        <v>1156</v>
       </c>
       <c r="C437" t="s">
-        <v>957</v>
+        <v>1157</v>
       </c>
       <c r="D437" t="s">
-        <v>957</v>
+        <v>1157</v>
       </c>
       <c r="E437" t="s">
         <v>105</v>
@@ -10406,13 +10411,13 @@
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B438" t="s">
-        <v>958</v>
+        <v>1158</v>
       </c>
       <c r="C438" t="s">
-        <v>959</v>
+        <v>1159</v>
       </c>
       <c r="D438" t="s">
-        <v>959</v>
+        <v>1159</v>
       </c>
       <c r="E438" t="s">
         <v>105</v>
@@ -10420,13 +10425,13 @@
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B439" t="s">
-        <v>960</v>
+        <v>1160</v>
       </c>
       <c r="C439" t="s">
-        <v>961</v>
+        <v>1161</v>
       </c>
       <c r="D439" t="s">
-        <v>961</v>
+        <v>1161</v>
       </c>
       <c r="E439" t="s">
         <v>105</v>
@@ -10434,13 +10439,13 @@
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B440" t="s">
-        <v>962</v>
+        <v>1162</v>
       </c>
       <c r="C440" t="s">
-        <v>963</v>
+        <v>1163</v>
       </c>
       <c r="D440" t="s">
-        <v>963</v>
+        <v>1163</v>
       </c>
       <c r="E440" t="s">
         <v>105</v>
@@ -10448,13 +10453,13 @@
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B441" t="s">
-        <v>964</v>
+        <v>1164</v>
       </c>
       <c r="C441" t="s">
-        <v>965</v>
+        <v>1165</v>
       </c>
       <c r="D441" t="s">
-        <v>965</v>
+        <v>1165</v>
       </c>
       <c r="E441" t="s">
         <v>105</v>
@@ -10462,13 +10467,13 @@
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B442" t="s">
-        <v>966</v>
+        <v>1166</v>
       </c>
       <c r="C442" t="s">
-        <v>967</v>
+        <v>1167</v>
       </c>
       <c r="D442" t="s">
-        <v>967</v>
+        <v>1167</v>
       </c>
       <c r="E442" t="s">
         <v>105</v>
@@ -10476,13 +10481,13 @@
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B443" t="s">
-        <v>968</v>
+        <v>1168</v>
       </c>
       <c r="C443" t="s">
-        <v>969</v>
+        <v>1169</v>
       </c>
       <c r="D443" t="s">
-        <v>969</v>
+        <v>1169</v>
       </c>
       <c r="E443" t="s">
         <v>105</v>
@@ -10490,13 +10495,13 @@
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B444" t="s">
-        <v>970</v>
+        <v>1170</v>
       </c>
       <c r="C444" t="s">
-        <v>971</v>
+        <v>1171</v>
       </c>
       <c r="D444" t="s">
-        <v>971</v>
+        <v>1171</v>
       </c>
       <c r="E444" t="s">
         <v>105</v>
@@ -10504,13 +10509,13 @@
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B445" t="s">
-        <v>972</v>
+        <v>1172</v>
       </c>
       <c r="C445" t="s">
-        <v>973</v>
+        <v>1173</v>
       </c>
       <c r="D445" t="s">
-        <v>973</v>
+        <v>1173</v>
       </c>
       <c r="E445" t="s">
         <v>105</v>
@@ -10518,13 +10523,13 @@
     </row>
     <row r="446" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B446" t="s">
-        <v>974</v>
+        <v>1174</v>
       </c>
       <c r="C446" t="s">
-        <v>975</v>
+        <v>1175</v>
       </c>
       <c r="D446" t="s">
-        <v>975</v>
+        <v>1175</v>
       </c>
       <c r="E446" t="s">
         <v>105</v>
@@ -10532,13 +10537,13 @@
     </row>
     <row r="447" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B447" t="s">
-        <v>976</v>
+        <v>746</v>
       </c>
       <c r="C447" t="s">
-        <v>977</v>
+        <v>747</v>
       </c>
       <c r="D447" t="s">
-        <v>977</v>
+        <v>747</v>
       </c>
       <c r="E447" t="s">
         <v>105</v>
@@ -10546,13 +10551,13 @@
     </row>
     <row r="448" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B448" t="s">
-        <v>978</v>
+        <v>748</v>
       </c>
       <c r="C448" t="s">
-        <v>979</v>
+        <v>749</v>
       </c>
       <c r="D448" t="s">
-        <v>979</v>
+        <v>749</v>
       </c>
       <c r="E448" t="s">
         <v>105</v>
@@ -10560,13 +10565,13 @@
     </row>
     <row r="449" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B449" t="s">
-        <v>980</v>
+        <v>750</v>
       </c>
       <c r="C449" t="s">
-        <v>981</v>
+        <v>751</v>
       </c>
       <c r="D449" t="s">
-        <v>981</v>
+        <v>751</v>
       </c>
       <c r="E449" t="s">
         <v>105</v>
@@ -10574,13 +10579,13 @@
     </row>
     <row r="450" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B450" t="s">
-        <v>982</v>
+        <v>752</v>
       </c>
       <c r="C450" t="s">
-        <v>983</v>
+        <v>753</v>
       </c>
       <c r="D450" t="s">
-        <v>983</v>
+        <v>753</v>
       </c>
       <c r="E450" t="s">
         <v>105</v>
@@ -10588,13 +10593,13 @@
     </row>
     <row r="451" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B451" t="s">
-        <v>984</v>
+        <v>754</v>
       </c>
       <c r="C451" t="s">
-        <v>985</v>
+        <v>755</v>
       </c>
       <c r="D451" t="s">
-        <v>985</v>
+        <v>755</v>
       </c>
       <c r="E451" t="s">
         <v>105</v>
@@ -10602,13 +10607,13 @@
     </row>
     <row r="452" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B452" t="s">
-        <v>986</v>
+        <v>756</v>
       </c>
       <c r="C452" t="s">
-        <v>987</v>
+        <v>757</v>
       </c>
       <c r="D452" t="s">
-        <v>987</v>
+        <v>757</v>
       </c>
       <c r="E452" t="s">
         <v>105</v>
@@ -10616,13 +10621,13 @@
     </row>
     <row r="453" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B453" t="s">
-        <v>988</v>
+        <v>758</v>
       </c>
       <c r="C453" t="s">
-        <v>989</v>
+        <v>759</v>
       </c>
       <c r="D453" t="s">
-        <v>989</v>
+        <v>759</v>
       </c>
       <c r="E453" t="s">
         <v>105</v>
@@ -10630,13 +10635,13 @@
     </row>
     <row r="454" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B454" t="s">
-        <v>990</v>
+        <v>760</v>
       </c>
       <c r="C454" t="s">
-        <v>991</v>
+        <v>761</v>
       </c>
       <c r="D454" t="s">
-        <v>991</v>
+        <v>761</v>
       </c>
       <c r="E454" t="s">
         <v>105</v>
@@ -10644,13 +10649,13 @@
     </row>
     <row r="455" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B455" t="s">
-        <v>992</v>
+        <v>762</v>
       </c>
       <c r="C455" t="s">
-        <v>993</v>
+        <v>763</v>
       </c>
       <c r="D455" t="s">
-        <v>993</v>
+        <v>763</v>
       </c>
       <c r="E455" t="s">
         <v>105</v>
@@ -10658,13 +10663,13 @@
     </row>
     <row r="456" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B456" t="s">
-        <v>994</v>
+        <v>764</v>
       </c>
       <c r="C456" t="s">
-        <v>995</v>
+        <v>765</v>
       </c>
       <c r="D456" t="s">
-        <v>995</v>
+        <v>765</v>
       </c>
       <c r="E456" t="s">
         <v>105</v>
@@ -10672,13 +10677,13 @@
     </row>
     <row r="457" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B457" t="s">
-        <v>996</v>
+        <v>766</v>
       </c>
       <c r="C457" t="s">
-        <v>997</v>
+        <v>767</v>
       </c>
       <c r="D457" t="s">
-        <v>997</v>
+        <v>767</v>
       </c>
       <c r="E457" t="s">
         <v>105</v>
@@ -10686,13 +10691,13 @@
     </row>
     <row r="458" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B458" t="s">
-        <v>998</v>
+        <v>768</v>
       </c>
       <c r="C458" t="s">
-        <v>999</v>
+        <v>769</v>
       </c>
       <c r="D458" t="s">
-        <v>999</v>
+        <v>769</v>
       </c>
       <c r="E458" t="s">
         <v>105</v>
@@ -10700,13 +10705,13 @@
     </row>
     <row r="459" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B459" t="s">
-        <v>1000</v>
+        <v>770</v>
       </c>
       <c r="C459" t="s">
-        <v>1001</v>
+        <v>771</v>
       </c>
       <c r="D459" t="s">
-        <v>1001</v>
+        <v>771</v>
       </c>
       <c r="E459" t="s">
         <v>105</v>
@@ -10714,13 +10719,13 @@
     </row>
     <row r="460" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B460" t="s">
-        <v>1002</v>
+        <v>772</v>
       </c>
       <c r="C460" t="s">
-        <v>1003</v>
+        <v>773</v>
       </c>
       <c r="D460" t="s">
-        <v>1003</v>
+        <v>773</v>
       </c>
       <c r="E460" t="s">
         <v>105</v>
@@ -10728,13 +10733,13 @@
     </row>
     <row r="461" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B461" t="s">
-        <v>1004</v>
+        <v>774</v>
       </c>
       <c r="C461" t="s">
-        <v>1005</v>
+        <v>775</v>
       </c>
       <c r="D461" t="s">
-        <v>1005</v>
+        <v>775</v>
       </c>
       <c r="E461" t="s">
         <v>105</v>
@@ -10742,13 +10747,13 @@
     </row>
     <row r="462" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B462" t="s">
-        <v>1006</v>
+        <v>776</v>
       </c>
       <c r="C462" t="s">
-        <v>1007</v>
+        <v>777</v>
       </c>
       <c r="D462" t="s">
-        <v>1007</v>
+        <v>777</v>
       </c>
       <c r="E462" t="s">
         <v>105</v>
@@ -10756,13 +10761,13 @@
     </row>
     <row r="463" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B463" t="s">
-        <v>1008</v>
+        <v>778</v>
       </c>
       <c r="C463" t="s">
-        <v>1009</v>
+        <v>779</v>
       </c>
       <c r="D463" t="s">
-        <v>1009</v>
+        <v>779</v>
       </c>
       <c r="E463" t="s">
         <v>105</v>
@@ -10770,13 +10775,13 @@
     </row>
     <row r="464" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B464" t="s">
-        <v>1010</v>
+        <v>780</v>
       </c>
       <c r="C464" t="s">
-        <v>1011</v>
+        <v>781</v>
       </c>
       <c r="D464" t="s">
-        <v>1011</v>
+        <v>781</v>
       </c>
       <c r="E464" t="s">
         <v>105</v>
@@ -10784,13 +10789,13 @@
     </row>
     <row r="465" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B465" t="s">
-        <v>1012</v>
+        <v>782</v>
       </c>
       <c r="C465" t="s">
-        <v>1013</v>
+        <v>783</v>
       </c>
       <c r="D465" t="s">
-        <v>1013</v>
+        <v>783</v>
       </c>
       <c r="E465" t="s">
         <v>105</v>
@@ -10798,13 +10803,13 @@
     </row>
     <row r="466" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B466" t="s">
-        <v>1014</v>
+        <v>784</v>
       </c>
       <c r="C466" t="s">
-        <v>1015</v>
+        <v>785</v>
       </c>
       <c r="D466" t="s">
-        <v>1015</v>
+        <v>785</v>
       </c>
       <c r="E466" t="s">
         <v>105</v>
@@ -10812,13 +10817,13 @@
     </row>
     <row r="467" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B467" t="s">
-        <v>1016</v>
+        <v>786</v>
       </c>
       <c r="C467" t="s">
-        <v>1017</v>
+        <v>787</v>
       </c>
       <c r="D467" t="s">
-        <v>1017</v>
+        <v>787</v>
       </c>
       <c r="E467" t="s">
         <v>105</v>
@@ -10826,13 +10831,13 @@
     </row>
     <row r="468" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B468" t="s">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="C468" t="s">
-        <v>1019</v>
+        <v>789</v>
       </c>
       <c r="D468" t="s">
-        <v>1019</v>
+        <v>789</v>
       </c>
       <c r="E468" t="s">
         <v>105</v>
@@ -10840,13 +10845,13 @@
     </row>
     <row r="469" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B469" t="s">
-        <v>1020</v>
+        <v>790</v>
       </c>
       <c r="C469" t="s">
-        <v>1021</v>
+        <v>791</v>
       </c>
       <c r="D469" t="s">
-        <v>1021</v>
+        <v>791</v>
       </c>
       <c r="E469" t="s">
         <v>105</v>
@@ -10854,13 +10859,13 @@
     </row>
     <row r="470" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B470" t="s">
-        <v>1022</v>
+        <v>792</v>
       </c>
       <c r="C470" t="s">
-        <v>1023</v>
+        <v>793</v>
       </c>
       <c r="D470" t="s">
-        <v>1023</v>
+        <v>793</v>
       </c>
       <c r="E470" t="s">
         <v>105</v>
@@ -10868,13 +10873,13 @@
     </row>
     <row r="471" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B471" t="s">
-        <v>1024</v>
+        <v>794</v>
       </c>
       <c r="C471" t="s">
-        <v>1025</v>
+        <v>795</v>
       </c>
       <c r="D471" t="s">
-        <v>1025</v>
+        <v>795</v>
       </c>
       <c r="E471" t="s">
         <v>105</v>
@@ -10882,13 +10887,13 @@
     </row>
     <row r="472" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B472" t="s">
-        <v>1026</v>
+        <v>796</v>
       </c>
       <c r="C472" t="s">
-        <v>1027</v>
+        <v>797</v>
       </c>
       <c r="D472" t="s">
-        <v>1027</v>
+        <v>797</v>
       </c>
       <c r="E472" t="s">
         <v>105</v>
@@ -10896,13 +10901,13 @@
     </row>
     <row r="473" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B473" t="s">
-        <v>1028</v>
+        <v>798</v>
       </c>
       <c r="C473" t="s">
-        <v>1029</v>
+        <v>799</v>
       </c>
       <c r="D473" t="s">
-        <v>1029</v>
+        <v>799</v>
       </c>
       <c r="E473" t="s">
         <v>105</v>
@@ -10910,13 +10915,13 @@
     </row>
     <row r="474" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B474" t="s">
-        <v>1030</v>
+        <v>800</v>
       </c>
       <c r="C474" t="s">
-        <v>1031</v>
+        <v>801</v>
       </c>
       <c r="D474" t="s">
-        <v>1031</v>
+        <v>801</v>
       </c>
       <c r="E474" t="s">
         <v>105</v>
@@ -10924,13 +10929,13 @@
     </row>
     <row r="475" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B475" t="s">
-        <v>1032</v>
+        <v>802</v>
       </c>
       <c r="C475" t="s">
-        <v>1033</v>
+        <v>803</v>
       </c>
       <c r="D475" t="s">
-        <v>1033</v>
+        <v>803</v>
       </c>
       <c r="E475" t="s">
         <v>105</v>
@@ -10938,13 +10943,13 @@
     </row>
     <row r="476" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B476" t="s">
-        <v>1034</v>
+        <v>804</v>
       </c>
       <c r="C476" t="s">
-        <v>1035</v>
+        <v>805</v>
       </c>
       <c r="D476" t="s">
-        <v>1035</v>
+        <v>805</v>
       </c>
       <c r="E476" t="s">
         <v>105</v>
@@ -10952,13 +10957,13 @@
     </row>
     <row r="477" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B477" t="s">
-        <v>1036</v>
+        <v>806</v>
       </c>
       <c r="C477" t="s">
-        <v>1037</v>
+        <v>807</v>
       </c>
       <c r="D477" t="s">
-        <v>1037</v>
+        <v>807</v>
       </c>
       <c r="E477" t="s">
         <v>105</v>
@@ -10966,13 +10971,13 @@
     </row>
     <row r="478" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B478" t="s">
-        <v>1038</v>
+        <v>808</v>
       </c>
       <c r="C478" t="s">
-        <v>1039</v>
+        <v>809</v>
       </c>
       <c r="D478" t="s">
-        <v>1039</v>
+        <v>809</v>
       </c>
       <c r="E478" t="s">
         <v>105</v>
@@ -10980,13 +10985,13 @@
     </row>
     <row r="479" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B479" t="s">
-        <v>1040</v>
+        <v>810</v>
       </c>
       <c r="C479" t="s">
-        <v>1041</v>
+        <v>811</v>
       </c>
       <c r="D479" t="s">
-        <v>1041</v>
+        <v>811</v>
       </c>
       <c r="E479" t="s">
         <v>105</v>
@@ -10994,13 +10999,13 @@
     </row>
     <row r="480" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B480" t="s">
-        <v>1042</v>
+        <v>812</v>
       </c>
       <c r="C480" t="s">
-        <v>1043</v>
+        <v>813</v>
       </c>
       <c r="D480" t="s">
-        <v>1043</v>
+        <v>813</v>
       </c>
       <c r="E480" t="s">
         <v>105</v>
@@ -11008,13 +11013,13 @@
     </row>
     <row r="481" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B481" t="s">
-        <v>1044</v>
+        <v>814</v>
       </c>
       <c r="C481" t="s">
-        <v>1045</v>
+        <v>815</v>
       </c>
       <c r="D481" t="s">
-        <v>1045</v>
+        <v>815</v>
       </c>
       <c r="E481" t="s">
         <v>105</v>
@@ -11022,13 +11027,13 @@
     </row>
     <row r="482" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B482" t="s">
-        <v>1046</v>
+        <v>816</v>
       </c>
       <c r="C482" t="s">
-        <v>1047</v>
+        <v>817</v>
       </c>
       <c r="D482" t="s">
-        <v>1047</v>
+        <v>817</v>
       </c>
       <c r="E482" t="s">
         <v>105</v>
@@ -11036,13 +11041,13 @@
     </row>
     <row r="483" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B483" t="s">
-        <v>1048</v>
+        <v>818</v>
       </c>
       <c r="C483" t="s">
-        <v>1049</v>
+        <v>819</v>
       </c>
       <c r="D483" t="s">
-        <v>1049</v>
+        <v>819</v>
       </c>
       <c r="E483" t="s">
         <v>105</v>
@@ -11050,13 +11055,13 @@
     </row>
     <row r="484" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B484" t="s">
-        <v>1050</v>
+        <v>820</v>
       </c>
       <c r="C484" t="s">
-        <v>1051</v>
+        <v>821</v>
       </c>
       <c r="D484" t="s">
-        <v>1051</v>
+        <v>821</v>
       </c>
       <c r="E484" t="s">
         <v>105</v>
@@ -11064,13 +11069,13 @@
     </row>
     <row r="485" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B485" t="s">
-        <v>1052</v>
+        <v>822</v>
       </c>
       <c r="C485" t="s">
-        <v>1053</v>
+        <v>823</v>
       </c>
       <c r="D485" t="s">
-        <v>1053</v>
+        <v>823</v>
       </c>
       <c r="E485" t="s">
         <v>105</v>
@@ -11078,13 +11083,13 @@
     </row>
     <row r="486" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B486" t="s">
-        <v>1054</v>
+        <v>824</v>
       </c>
       <c r="C486" t="s">
-        <v>1055</v>
+        <v>825</v>
       </c>
       <c r="D486" t="s">
-        <v>1055</v>
+        <v>825</v>
       </c>
       <c r="E486" t="s">
         <v>105</v>
@@ -11092,13 +11097,13 @@
     </row>
     <row r="487" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B487" t="s">
-        <v>1056</v>
+        <v>826</v>
       </c>
       <c r="C487" t="s">
-        <v>1057</v>
+        <v>827</v>
       </c>
       <c r="D487" t="s">
-        <v>1057</v>
+        <v>827</v>
       </c>
       <c r="E487" t="s">
         <v>105</v>
@@ -11106,13 +11111,13 @@
     </row>
     <row r="488" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B488" t="s">
-        <v>1058</v>
+        <v>828</v>
       </c>
       <c r="C488" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="D488" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="E488" t="s">
         <v>105</v>
@@ -11120,13 +11125,13 @@
     </row>
     <row r="489" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B489" t="s">
-        <v>1060</v>
+        <v>830</v>
       </c>
       <c r="C489" t="s">
-        <v>1061</v>
+        <v>831</v>
       </c>
       <c r="D489" t="s">
-        <v>1061</v>
+        <v>831</v>
       </c>
       <c r="E489" t="s">
         <v>105</v>
@@ -11134,13 +11139,13 @@
     </row>
     <row r="490" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B490" t="s">
-        <v>1062</v>
+        <v>832</v>
       </c>
       <c r="C490" t="s">
-        <v>1063</v>
+        <v>833</v>
       </c>
       <c r="D490" t="s">
-        <v>1063</v>
+        <v>833</v>
       </c>
       <c r="E490" t="s">
         <v>105</v>
@@ -11148,13 +11153,13 @@
     </row>
     <row r="491" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B491" t="s">
-        <v>1064</v>
+        <v>834</v>
       </c>
       <c r="C491" t="s">
-        <v>1065</v>
+        <v>835</v>
       </c>
       <c r="D491" t="s">
-        <v>1065</v>
+        <v>835</v>
       </c>
       <c r="E491" t="s">
         <v>105</v>
@@ -11162,13 +11167,13 @@
     </row>
     <row r="492" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B492" t="s">
-        <v>1066</v>
+        <v>836</v>
       </c>
       <c r="C492" t="s">
-        <v>1067</v>
+        <v>837</v>
       </c>
       <c r="D492" t="s">
-        <v>1067</v>
+        <v>837</v>
       </c>
       <c r="E492" t="s">
         <v>105</v>
@@ -11176,13 +11181,13 @@
     </row>
     <row r="493" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B493" t="s">
-        <v>1068</v>
+        <v>838</v>
       </c>
       <c r="C493" t="s">
-        <v>1069</v>
+        <v>839</v>
       </c>
       <c r="D493" t="s">
-        <v>1069</v>
+        <v>839</v>
       </c>
       <c r="E493" t="s">
         <v>105</v>
@@ -11190,13 +11195,13 @@
     </row>
     <row r="494" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B494" t="s">
-        <v>1070</v>
+        <v>840</v>
       </c>
       <c r="C494" t="s">
-        <v>1071</v>
+        <v>841</v>
       </c>
       <c r="D494" t="s">
-        <v>1071</v>
+        <v>841</v>
       </c>
       <c r="E494" t="s">
         <v>105</v>
@@ -11204,13 +11209,13 @@
     </row>
     <row r="495" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B495" t="s">
-        <v>1072</v>
+        <v>842</v>
       </c>
       <c r="C495" t="s">
-        <v>1073</v>
+        <v>843</v>
       </c>
       <c r="D495" t="s">
-        <v>1073</v>
+        <v>843</v>
       </c>
       <c r="E495" t="s">
         <v>105</v>
@@ -11218,13 +11223,13 @@
     </row>
     <row r="496" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B496" t="s">
-        <v>1074</v>
+        <v>844</v>
       </c>
       <c r="C496" t="s">
-        <v>1075</v>
+        <v>845</v>
       </c>
       <c r="D496" t="s">
-        <v>1075</v>
+        <v>845</v>
       </c>
       <c r="E496" t="s">
         <v>105</v>
@@ -11232,13 +11237,13 @@
     </row>
     <row r="497" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B497" t="s">
-        <v>1076</v>
+        <v>846</v>
       </c>
       <c r="C497" t="s">
-        <v>1077</v>
+        <v>847</v>
       </c>
       <c r="D497" t="s">
-        <v>1077</v>
+        <v>847</v>
       </c>
       <c r="E497" t="s">
         <v>105</v>
@@ -11246,13 +11251,13 @@
     </row>
     <row r="498" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B498" t="s">
-        <v>1078</v>
+        <v>848</v>
       </c>
       <c r="C498" t="s">
-        <v>1079</v>
+        <v>849</v>
       </c>
       <c r="D498" t="s">
-        <v>1079</v>
+        <v>849</v>
       </c>
       <c r="E498" t="s">
         <v>105</v>
@@ -11260,13 +11265,13 @@
     </row>
     <row r="499" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B499" t="s">
-        <v>1080</v>
+        <v>850</v>
       </c>
       <c r="C499" t="s">
-        <v>1081</v>
+        <v>851</v>
       </c>
       <c r="D499" t="s">
-        <v>1081</v>
+        <v>851</v>
       </c>
       <c r="E499" t="s">
         <v>105</v>
@@ -11274,13 +11279,13 @@
     </row>
     <row r="500" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B500" t="s">
-        <v>1082</v>
+        <v>852</v>
       </c>
       <c r="C500" t="s">
-        <v>1083</v>
+        <v>853</v>
       </c>
       <c r="D500" t="s">
-        <v>1083</v>
+        <v>853</v>
       </c>
       <c r="E500" t="s">
         <v>105</v>
@@ -11288,13 +11293,13 @@
     </row>
     <row r="501" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B501" t="s">
-        <v>1084</v>
+        <v>854</v>
       </c>
       <c r="C501" t="s">
-        <v>1085</v>
+        <v>855</v>
       </c>
       <c r="D501" t="s">
-        <v>1085</v>
+        <v>855</v>
       </c>
       <c r="E501" t="s">
         <v>105</v>
@@ -11302,13 +11307,13 @@
     </row>
     <row r="502" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B502" t="s">
-        <v>1086</v>
+        <v>856</v>
       </c>
       <c r="C502" t="s">
-        <v>1087</v>
+        <v>857</v>
       </c>
       <c r="D502" t="s">
-        <v>1087</v>
+        <v>857</v>
       </c>
       <c r="E502" t="s">
         <v>105</v>
@@ -11316,13 +11321,13 @@
     </row>
     <row r="503" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B503" t="s">
-        <v>1088</v>
+        <v>858</v>
       </c>
       <c r="C503" t="s">
-        <v>1089</v>
+        <v>859</v>
       </c>
       <c r="D503" t="s">
-        <v>1089</v>
+        <v>859</v>
       </c>
       <c r="E503" t="s">
         <v>105</v>
@@ -11330,13 +11335,13 @@
     </row>
     <row r="504" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B504" t="s">
-        <v>1090</v>
+        <v>860</v>
       </c>
       <c r="C504" t="s">
-        <v>1091</v>
+        <v>861</v>
       </c>
       <c r="D504" t="s">
-        <v>1091</v>
+        <v>861</v>
       </c>
       <c r="E504" t="s">
         <v>105</v>
@@ -11344,13 +11349,13 @@
     </row>
     <row r="505" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B505" t="s">
-        <v>1092</v>
+        <v>862</v>
       </c>
       <c r="C505" t="s">
-        <v>1093</v>
+        <v>863</v>
       </c>
       <c r="D505" t="s">
-        <v>1093</v>
+        <v>863</v>
       </c>
       <c r="E505" t="s">
         <v>105</v>
@@ -11358,13 +11363,13 @@
     </row>
     <row r="506" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B506" t="s">
-        <v>1094</v>
+        <v>864</v>
       </c>
       <c r="C506" t="s">
-        <v>1095</v>
+        <v>865</v>
       </c>
       <c r="D506" t="s">
-        <v>1095</v>
+        <v>865</v>
       </c>
       <c r="E506" t="s">
         <v>105</v>
@@ -11372,13 +11377,13 @@
     </row>
     <row r="507" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B507" t="s">
-        <v>1096</v>
+        <v>866</v>
       </c>
       <c r="C507" t="s">
-        <v>1097</v>
+        <v>867</v>
       </c>
       <c r="D507" t="s">
-        <v>1097</v>
+        <v>867</v>
       </c>
       <c r="E507" t="s">
         <v>105</v>
@@ -11386,13 +11391,13 @@
     </row>
     <row r="508" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B508" t="s">
-        <v>1098</v>
+        <v>868</v>
       </c>
       <c r="C508" t="s">
-        <v>1099</v>
+        <v>869</v>
       </c>
       <c r="D508" t="s">
-        <v>1099</v>
+        <v>869</v>
       </c>
       <c r="E508" t="s">
         <v>105</v>
@@ -11400,13 +11405,13 @@
     </row>
     <row r="509" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B509" t="s">
-        <v>1100</v>
+        <v>870</v>
       </c>
       <c r="C509" t="s">
-        <v>1101</v>
+        <v>871</v>
       </c>
       <c r="D509" t="s">
-        <v>1101</v>
+        <v>871</v>
       </c>
       <c r="E509" t="s">
         <v>105</v>
@@ -11414,13 +11419,13 @@
     </row>
     <row r="510" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B510" t="s">
-        <v>1102</v>
+        <v>872</v>
       </c>
       <c r="C510" t="s">
-        <v>1103</v>
+        <v>873</v>
       </c>
       <c r="D510" t="s">
-        <v>1103</v>
+        <v>873</v>
       </c>
       <c r="E510" t="s">
         <v>105</v>
@@ -11428,13 +11433,13 @@
     </row>
     <row r="511" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B511" t="s">
-        <v>1104</v>
+        <v>874</v>
       </c>
       <c r="C511" t="s">
-        <v>1105</v>
+        <v>875</v>
       </c>
       <c r="D511" t="s">
-        <v>1105</v>
+        <v>875</v>
       </c>
       <c r="E511" t="s">
         <v>105</v>
@@ -11442,13 +11447,13 @@
     </row>
     <row r="512" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B512" t="s">
-        <v>1106</v>
+        <v>876</v>
       </c>
       <c r="C512" t="s">
-        <v>1107</v>
+        <v>877</v>
       </c>
       <c r="D512" t="s">
-        <v>1107</v>
+        <v>877</v>
       </c>
       <c r="E512" t="s">
         <v>105</v>
@@ -11456,13 +11461,13 @@
     </row>
     <row r="513" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B513" t="s">
-        <v>1108</v>
+        <v>878</v>
       </c>
       <c r="C513" t="s">
-        <v>1109</v>
+        <v>879</v>
       </c>
       <c r="D513" t="s">
-        <v>1109</v>
+        <v>879</v>
       </c>
       <c r="E513" t="s">
         <v>105</v>
@@ -11470,13 +11475,13 @@
     </row>
     <row r="514" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B514" t="s">
-        <v>1110</v>
+        <v>880</v>
       </c>
       <c r="C514" t="s">
-        <v>1111</v>
+        <v>881</v>
       </c>
       <c r="D514" t="s">
-        <v>1111</v>
+        <v>881</v>
       </c>
       <c r="E514" t="s">
         <v>105</v>
@@ -11484,13 +11489,13 @@
     </row>
     <row r="515" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B515" t="s">
-        <v>1112</v>
+        <v>882</v>
       </c>
       <c r="C515" t="s">
-        <v>1113</v>
+        <v>883</v>
       </c>
       <c r="D515" t="s">
-        <v>1113</v>
+        <v>883</v>
       </c>
       <c r="E515" t="s">
         <v>105</v>
@@ -11498,13 +11503,13 @@
     </row>
     <row r="516" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B516" t="s">
-        <v>1114</v>
+        <v>884</v>
       </c>
       <c r="C516" t="s">
-        <v>1115</v>
+        <v>885</v>
       </c>
       <c r="D516" t="s">
-        <v>1115</v>
+        <v>885</v>
       </c>
       <c r="E516" t="s">
         <v>105</v>
@@ -11512,13 +11517,13 @@
     </row>
     <row r="517" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B517" t="s">
-        <v>1116</v>
+        <v>886</v>
       </c>
       <c r="C517" t="s">
-        <v>1117</v>
+        <v>887</v>
       </c>
       <c r="D517" t="s">
-        <v>1117</v>
+        <v>887</v>
       </c>
       <c r="E517" t="s">
         <v>105</v>
@@ -11526,13 +11531,13 @@
     </row>
     <row r="518" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B518" t="s">
-        <v>1118</v>
+        <v>888</v>
       </c>
       <c r="C518" t="s">
-        <v>1119</v>
+        <v>889</v>
       </c>
       <c r="D518" t="s">
-        <v>1119</v>
+        <v>889</v>
       </c>
       <c r="E518" t="s">
         <v>105</v>
@@ -11540,13 +11545,13 @@
     </row>
     <row r="519" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B519" t="s">
-        <v>1120</v>
+        <v>890</v>
       </c>
       <c r="C519" t="s">
-        <v>1121</v>
+        <v>891</v>
       </c>
       <c r="D519" t="s">
-        <v>1121</v>
+        <v>891</v>
       </c>
       <c r="E519" t="s">
         <v>105</v>
@@ -11554,13 +11559,13 @@
     </row>
     <row r="520" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B520" t="s">
-        <v>1122</v>
+        <v>892</v>
       </c>
       <c r="C520" t="s">
-        <v>1123</v>
+        <v>893</v>
       </c>
       <c r="D520" t="s">
-        <v>1123</v>
+        <v>893</v>
       </c>
       <c r="E520" t="s">
         <v>105</v>
@@ -11568,13 +11573,13 @@
     </row>
     <row r="521" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B521" t="s">
-        <v>1124</v>
+        <v>894</v>
       </c>
       <c r="C521" t="s">
-        <v>1125</v>
+        <v>895</v>
       </c>
       <c r="D521" t="s">
-        <v>1125</v>
+        <v>895</v>
       </c>
       <c r="E521" t="s">
         <v>105</v>
@@ -11582,13 +11587,13 @@
     </row>
     <row r="522" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B522" t="s">
-        <v>1126</v>
+        <v>896</v>
       </c>
       <c r="C522" t="s">
-        <v>1127</v>
+        <v>897</v>
       </c>
       <c r="D522" t="s">
-        <v>1127</v>
+        <v>897</v>
       </c>
       <c r="E522" t="s">
         <v>105</v>
@@ -11596,13 +11601,13 @@
     </row>
     <row r="523" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B523" t="s">
-        <v>1128</v>
+        <v>898</v>
       </c>
       <c r="C523" t="s">
-        <v>1129</v>
+        <v>899</v>
       </c>
       <c r="D523" t="s">
-        <v>1129</v>
+        <v>899</v>
       </c>
       <c r="E523" t="s">
         <v>105</v>
@@ -11610,13 +11615,13 @@
     </row>
     <row r="524" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B524" t="s">
-        <v>1130</v>
+        <v>900</v>
       </c>
       <c r="C524" t="s">
-        <v>1131</v>
+        <v>901</v>
       </c>
       <c r="D524" t="s">
-        <v>1131</v>
+        <v>901</v>
       </c>
       <c r="E524" t="s">
         <v>105</v>
@@ -11624,13 +11629,13 @@
     </row>
     <row r="525" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B525" t="s">
-        <v>1132</v>
+        <v>902</v>
       </c>
       <c r="C525" t="s">
-        <v>1133</v>
+        <v>903</v>
       </c>
       <c r="D525" t="s">
-        <v>1133</v>
+        <v>903</v>
       </c>
       <c r="E525" t="s">
         <v>105</v>
@@ -11638,13 +11643,13 @@
     </row>
     <row r="526" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B526" t="s">
-        <v>1134</v>
+        <v>904</v>
       </c>
       <c r="C526" t="s">
-        <v>1135</v>
+        <v>905</v>
       </c>
       <c r="D526" t="s">
-        <v>1135</v>
+        <v>905</v>
       </c>
       <c r="E526" t="s">
         <v>105</v>
@@ -11652,13 +11657,13 @@
     </row>
     <row r="527" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B527" t="s">
-        <v>1136</v>
+        <v>906</v>
       </c>
       <c r="C527" t="s">
-        <v>1137</v>
+        <v>907</v>
       </c>
       <c r="D527" t="s">
-        <v>1137</v>
+        <v>907</v>
       </c>
       <c r="E527" t="s">
         <v>105</v>
@@ -11666,13 +11671,13 @@
     </row>
     <row r="528" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B528" t="s">
-        <v>1138</v>
+        <v>908</v>
       </c>
       <c r="C528" t="s">
-        <v>1139</v>
+        <v>909</v>
       </c>
       <c r="D528" t="s">
-        <v>1139</v>
+        <v>909</v>
       </c>
       <c r="E528" t="s">
         <v>105</v>
@@ -11680,13 +11685,13 @@
     </row>
     <row r="529" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B529" t="s">
-        <v>1140</v>
+        <v>910</v>
       </c>
       <c r="C529" t="s">
-        <v>1141</v>
+        <v>911</v>
       </c>
       <c r="D529" t="s">
-        <v>1141</v>
+        <v>911</v>
       </c>
       <c r="E529" t="s">
         <v>105</v>
@@ -11694,13 +11699,13 @@
     </row>
     <row r="530" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B530" t="s">
-        <v>1142</v>
+        <v>912</v>
       </c>
       <c r="C530" t="s">
-        <v>1143</v>
+        <v>913</v>
       </c>
       <c r="D530" t="s">
-        <v>1143</v>
+        <v>913</v>
       </c>
       <c r="E530" t="s">
         <v>105</v>
@@ -11708,13 +11713,13 @@
     </row>
     <row r="531" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B531" t="s">
-        <v>1144</v>
+        <v>914</v>
       </c>
       <c r="C531" t="s">
-        <v>1145</v>
+        <v>915</v>
       </c>
       <c r="D531" t="s">
-        <v>1145</v>
+        <v>915</v>
       </c>
       <c r="E531" t="s">
         <v>105</v>
@@ -11722,13 +11727,13 @@
     </row>
     <row r="532" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B532" t="s">
-        <v>1146</v>
+        <v>916</v>
       </c>
       <c r="C532" t="s">
-        <v>1147</v>
+        <v>917</v>
       </c>
       <c r="D532" t="s">
-        <v>1147</v>
+        <v>917</v>
       </c>
       <c r="E532" t="s">
         <v>105</v>
@@ -11736,13 +11741,13 @@
     </row>
     <row r="533" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B533" t="s">
-        <v>1148</v>
+        <v>918</v>
       </c>
       <c r="C533" t="s">
-        <v>1149</v>
+        <v>919</v>
       </c>
       <c r="D533" t="s">
-        <v>1149</v>
+        <v>919</v>
       </c>
       <c r="E533" t="s">
         <v>105</v>
@@ -11750,13 +11755,13 @@
     </row>
     <row r="534" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B534" t="s">
-        <v>1150</v>
+        <v>920</v>
       </c>
       <c r="C534" t="s">
-        <v>1151</v>
+        <v>921</v>
       </c>
       <c r="D534" t="s">
-        <v>1151</v>
+        <v>921</v>
       </c>
       <c r="E534" t="s">
         <v>105</v>
@@ -11764,13 +11769,13 @@
     </row>
     <row r="535" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B535" t="s">
-        <v>1152</v>
+        <v>922</v>
       </c>
       <c r="C535" t="s">
-        <v>1153</v>
+        <v>923</v>
       </c>
       <c r="D535" t="s">
-        <v>1153</v>
+        <v>923</v>
       </c>
       <c r="E535" t="s">
         <v>105</v>
@@ -11778,13 +11783,13 @@
     </row>
     <row r="536" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B536" t="s">
-        <v>1154</v>
+        <v>924</v>
       </c>
       <c r="C536" t="s">
-        <v>1155</v>
+        <v>925</v>
       </c>
       <c r="D536" t="s">
-        <v>1155</v>
+        <v>925</v>
       </c>
       <c r="E536" t="s">
         <v>105</v>
@@ -11792,13 +11797,13 @@
     </row>
     <row r="537" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B537" t="s">
-        <v>1156</v>
+        <v>926</v>
       </c>
       <c r="C537" t="s">
-        <v>1157</v>
+        <v>927</v>
       </c>
       <c r="D537" t="s">
-        <v>1157</v>
+        <v>927</v>
       </c>
       <c r="E537" t="s">
         <v>105</v>
@@ -11806,13 +11811,13 @@
     </row>
     <row r="538" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B538" t="s">
-        <v>1158</v>
+        <v>928</v>
       </c>
       <c r="C538" t="s">
-        <v>1159</v>
+        <v>929</v>
       </c>
       <c r="D538" t="s">
-        <v>1159</v>
+        <v>929</v>
       </c>
       <c r="E538" t="s">
         <v>105</v>
@@ -11820,13 +11825,13 @@
     </row>
     <row r="539" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B539" t="s">
-        <v>1160</v>
+        <v>930</v>
       </c>
       <c r="C539" t="s">
-        <v>1161</v>
+        <v>931</v>
       </c>
       <c r="D539" t="s">
-        <v>1161</v>
+        <v>931</v>
       </c>
       <c r="E539" t="s">
         <v>105</v>
@@ -11834,13 +11839,13 @@
     </row>
     <row r="540" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B540" t="s">
-        <v>1162</v>
+        <v>932</v>
       </c>
       <c r="C540" t="s">
-        <v>1163</v>
+        <v>933</v>
       </c>
       <c r="D540" t="s">
-        <v>1163</v>
+        <v>933</v>
       </c>
       <c r="E540" t="s">
         <v>105</v>
@@ -11848,13 +11853,13 @@
     </row>
     <row r="541" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B541" t="s">
-        <v>1164</v>
+        <v>934</v>
       </c>
       <c r="C541" t="s">
-        <v>1165</v>
+        <v>935</v>
       </c>
       <c r="D541" t="s">
-        <v>1165</v>
+        <v>935</v>
       </c>
       <c r="E541" t="s">
         <v>105</v>
@@ -11862,13 +11867,13 @@
     </row>
     <row r="542" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B542" t="s">
-        <v>1166</v>
+        <v>936</v>
       </c>
       <c r="C542" t="s">
-        <v>1167</v>
+        <v>937</v>
       </c>
       <c r="D542" t="s">
-        <v>1167</v>
+        <v>937</v>
       </c>
       <c r="E542" t="s">
         <v>105</v>
@@ -11876,13 +11881,13 @@
     </row>
     <row r="543" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B543" t="s">
-        <v>1168</v>
+        <v>938</v>
       </c>
       <c r="C543" t="s">
-        <v>1169</v>
+        <v>939</v>
       </c>
       <c r="D543" t="s">
-        <v>1169</v>
+        <v>939</v>
       </c>
       <c r="E543" t="s">
         <v>105</v>
@@ -11890,13 +11895,13 @@
     </row>
     <row r="544" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B544" t="s">
-        <v>1170</v>
+        <v>940</v>
       </c>
       <c r="C544" t="s">
-        <v>1171</v>
+        <v>941</v>
       </c>
       <c r="D544" t="s">
-        <v>1171</v>
+        <v>941</v>
       </c>
       <c r="E544" t="s">
         <v>105</v>
@@ -11904,13 +11909,13 @@
     </row>
     <row r="545" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B545" t="s">
-        <v>1172</v>
+        <v>942</v>
       </c>
       <c r="C545" t="s">
-        <v>1173</v>
+        <v>943</v>
       </c>
       <c r="D545" t="s">
-        <v>1173</v>
+        <v>943</v>
       </c>
       <c r="E545" t="s">
         <v>105</v>
@@ -11918,13 +11923,13 @@
     </row>
     <row r="546" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B546" t="s">
-        <v>1174</v>
+        <v>944</v>
       </c>
       <c r="C546" t="s">
-        <v>1175</v>
+        <v>945</v>
       </c>
       <c r="D546" t="s">
-        <v>1175</v>
+        <v>945</v>
       </c>
       <c r="E546" t="s">
         <v>105</v>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BFB2A8-91A1-47FF-8604-8215AB1A8583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77EE0EF8-37E8-4FCD-AB7E-7DFB8938EA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2278,6 +2278,696 @@
     <t>e_BR411*</t>
   </si>
   <si>
+    <t>rez_spv_001</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>rez_spv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>rez_spv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
+    <t>rez_spv_004</t>
+  </si>
+  <si>
+    <t>elc_spv_004</t>
+  </si>
+  <si>
+    <t>rez_spv_005</t>
+  </si>
+  <si>
+    <t>elc_spv_005</t>
+  </si>
+  <si>
+    <t>rez_spv_006</t>
+  </si>
+  <si>
+    <t>elc_spv_006</t>
+  </si>
+  <si>
+    <t>rez_spv_007</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>rez_spv_008</t>
+  </si>
+  <si>
+    <t>elc_spv_008</t>
+  </si>
+  <si>
+    <t>rez_spv_009</t>
+  </si>
+  <si>
+    <t>elc_spv_009</t>
+  </si>
+  <si>
+    <t>rez_spv_010</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>rez_spv_011</t>
+  </si>
+  <si>
+    <t>elc_spv_011</t>
+  </si>
+  <si>
+    <t>rez_spv_012</t>
+  </si>
+  <si>
+    <t>elc_spv_012</t>
+  </si>
+  <si>
+    <t>rez_spv_013</t>
+  </si>
+  <si>
+    <t>elc_spv_013</t>
+  </si>
+  <si>
+    <t>rez_spv_014</t>
+  </si>
+  <si>
+    <t>elc_spv_014</t>
+  </si>
+  <si>
+    <t>rez_spv_015</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>rez_spv_016</t>
+  </si>
+  <si>
+    <t>elc_spv_016</t>
+  </si>
+  <si>
+    <t>rez_spv_017</t>
+  </si>
+  <si>
+    <t>elc_spv_017</t>
+  </si>
+  <si>
+    <t>rez_spv_018</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
+    <t>rez_spv_019</t>
+  </si>
+  <si>
+    <t>elc_spv_019</t>
+  </si>
+  <si>
+    <t>rez_spv_020</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>rez_spv_021</t>
+  </si>
+  <si>
+    <t>elc_spv_021</t>
+  </si>
+  <si>
+    <t>rez_spv_022</t>
+  </si>
+  <si>
+    <t>elc_spv_022</t>
+  </si>
+  <si>
+    <t>rez_spv_023</t>
+  </si>
+  <si>
+    <t>elc_spv_023</t>
+  </si>
+  <si>
+    <t>rez_spv_024</t>
+  </si>
+  <si>
+    <t>elc_spv_024</t>
+  </si>
+  <si>
+    <t>rez_spv_025</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>rez_spv_026</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>rez_spv_027</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>rez_spv_028</t>
+  </si>
+  <si>
+    <t>elc_spv_028</t>
+  </si>
+  <si>
+    <t>rez_spv_029</t>
+  </si>
+  <si>
+    <t>elc_spv_029</t>
+  </si>
+  <si>
+    <t>rez_spv_030</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>rez_spv_031</t>
+  </si>
+  <si>
+    <t>elc_spv_031</t>
+  </si>
+  <si>
+    <t>rez_spv_032</t>
+  </si>
+  <si>
+    <t>elc_spv_032</t>
+  </si>
+  <si>
+    <t>rez_spv_033</t>
+  </si>
+  <si>
+    <t>elc_spv_033</t>
+  </si>
+  <si>
+    <t>rez_spv_034</t>
+  </si>
+  <si>
+    <t>elc_spv_034</t>
+  </si>
+  <si>
+    <t>rez_spv_035</t>
+  </si>
+  <si>
+    <t>elc_spv_035</t>
+  </si>
+  <si>
+    <t>rez_spv_036</t>
+  </si>
+  <si>
+    <t>elc_spv_036</t>
+  </si>
+  <si>
+    <t>rez_spv_037</t>
+  </si>
+  <si>
+    <t>elc_spv_037</t>
+  </si>
+  <si>
+    <t>rez_spv_038</t>
+  </si>
+  <si>
+    <t>elc_spv_038</t>
+  </si>
+  <si>
+    <t>rez_spv_039</t>
+  </si>
+  <si>
+    <t>elc_spv_039</t>
+  </si>
+  <si>
+    <t>rez_spv_040</t>
+  </si>
+  <si>
+    <t>elc_spv_040</t>
+  </si>
+  <si>
+    <t>rez_spv_041</t>
+  </si>
+  <si>
+    <t>elc_spv_041</t>
+  </si>
+  <si>
+    <t>rez_spv_042</t>
+  </si>
+  <si>
+    <t>elc_spv_042</t>
+  </si>
+  <si>
+    <t>rez_spv_043</t>
+  </si>
+  <si>
+    <t>elc_spv_043</t>
+  </si>
+  <si>
+    <t>rez_spv_044</t>
+  </si>
+  <si>
+    <t>elc_spv_044</t>
+  </si>
+  <si>
+    <t>rez_spv_045</t>
+  </si>
+  <si>
+    <t>elc_spv_045</t>
+  </si>
+  <si>
+    <t>rez_spv_046</t>
+  </si>
+  <si>
+    <t>elc_spv_046</t>
+  </si>
+  <si>
+    <t>rez_spv_047</t>
+  </si>
+  <si>
+    <t>elc_spv_047</t>
+  </si>
+  <si>
+    <t>rez_spv_048</t>
+  </si>
+  <si>
+    <t>elc_spv_048</t>
+  </si>
+  <si>
+    <t>rez_spv_049</t>
+  </si>
+  <si>
+    <t>elc_spv_049</t>
+  </si>
+  <si>
+    <t>rez_spv_050</t>
+  </si>
+  <si>
+    <t>elc_spv_050</t>
+  </si>
+  <si>
+    <t>rez_spv_051</t>
+  </si>
+  <si>
+    <t>elc_spv_051</t>
+  </si>
+  <si>
+    <t>rez_spv_052</t>
+  </si>
+  <si>
+    <t>elc_spv_052</t>
+  </si>
+  <si>
+    <t>rez_spv_053</t>
+  </si>
+  <si>
+    <t>elc_spv_053</t>
+  </si>
+  <si>
+    <t>rez_spv_054</t>
+  </si>
+  <si>
+    <t>elc_spv_054</t>
+  </si>
+  <si>
+    <t>rez_spv_055</t>
+  </si>
+  <si>
+    <t>elc_spv_055</t>
+  </si>
+  <si>
+    <t>rez_spv_056</t>
+  </si>
+  <si>
+    <t>elc_spv_056</t>
+  </si>
+  <si>
+    <t>rez_spv_057</t>
+  </si>
+  <si>
+    <t>elc_spv_057</t>
+  </si>
+  <si>
+    <t>rez_spv_058</t>
+  </si>
+  <si>
+    <t>elc_spv_058</t>
+  </si>
+  <si>
+    <t>rez_spv_059</t>
+  </si>
+  <si>
+    <t>elc_spv_059</t>
+  </si>
+  <si>
+    <t>rez_spv_060</t>
+  </si>
+  <si>
+    <t>elc_spv_060</t>
+  </si>
+  <si>
+    <t>rez_spv_061</t>
+  </si>
+  <si>
+    <t>elc_spv_061</t>
+  </si>
+  <si>
+    <t>rez_spv_062</t>
+  </si>
+  <si>
+    <t>elc_spv_062</t>
+  </si>
+  <si>
+    <t>rez_spv_063</t>
+  </si>
+  <si>
+    <t>elc_spv_063</t>
+  </si>
+  <si>
+    <t>rez_spv_064</t>
+  </si>
+  <si>
+    <t>elc_spv_064</t>
+  </si>
+  <si>
+    <t>rez_spv_065</t>
+  </si>
+  <si>
+    <t>elc_spv_065</t>
+  </si>
+  <si>
+    <t>rez_spv_066</t>
+  </si>
+  <si>
+    <t>elc_spv_066</t>
+  </si>
+  <si>
+    <t>rez_spv_067</t>
+  </si>
+  <si>
+    <t>elc_spv_067</t>
+  </si>
+  <si>
+    <t>rez_spv_068</t>
+  </si>
+  <si>
+    <t>elc_spv_068</t>
+  </si>
+  <si>
+    <t>rez_spv_069</t>
+  </si>
+  <si>
+    <t>elc_spv_069</t>
+  </si>
+  <si>
+    <t>rez_spv_070</t>
+  </si>
+  <si>
+    <t>elc_spv_070</t>
+  </si>
+  <si>
+    <t>rez_spv_071</t>
+  </si>
+  <si>
+    <t>elc_spv_071</t>
+  </si>
+  <si>
+    <t>rez_spv_072</t>
+  </si>
+  <si>
+    <t>elc_spv_072</t>
+  </si>
+  <si>
+    <t>rez_spv_073</t>
+  </si>
+  <si>
+    <t>elc_spv_073</t>
+  </si>
+  <si>
+    <t>rez_spv_074</t>
+  </si>
+  <si>
+    <t>elc_spv_074</t>
+  </si>
+  <si>
+    <t>rez_spv_075</t>
+  </si>
+  <si>
+    <t>elc_spv_075</t>
+  </si>
+  <si>
+    <t>rez_spv_076</t>
+  </si>
+  <si>
+    <t>elc_spv_076</t>
+  </si>
+  <si>
+    <t>rez_spv_077</t>
+  </si>
+  <si>
+    <t>elc_spv_077</t>
+  </si>
+  <si>
+    <t>rez_spv_078</t>
+  </si>
+  <si>
+    <t>elc_spv_078</t>
+  </si>
+  <si>
+    <t>rez_spv_079</t>
+  </si>
+  <si>
+    <t>elc_spv_079</t>
+  </si>
+  <si>
+    <t>rez_spv_080</t>
+  </si>
+  <si>
+    <t>elc_spv_080</t>
+  </si>
+  <si>
+    <t>rez_spv_081</t>
+  </si>
+  <si>
+    <t>elc_spv_081</t>
+  </si>
+  <si>
+    <t>rez_spv_082</t>
+  </si>
+  <si>
+    <t>elc_spv_082</t>
+  </si>
+  <si>
+    <t>rez_spv_083</t>
+  </si>
+  <si>
+    <t>elc_spv_083</t>
+  </si>
+  <si>
+    <t>rez_spv_084</t>
+  </si>
+  <si>
+    <t>elc_spv_084</t>
+  </si>
+  <si>
+    <t>rez_spv_085</t>
+  </si>
+  <si>
+    <t>elc_spv_085</t>
+  </si>
+  <si>
+    <t>rez_spv_086</t>
+  </si>
+  <si>
+    <t>elc_spv_086</t>
+  </si>
+  <si>
+    <t>rez_spv_087</t>
+  </si>
+  <si>
+    <t>elc_spv_087</t>
+  </si>
+  <si>
+    <t>rez_spv_088</t>
+  </si>
+  <si>
+    <t>elc_spv_088</t>
+  </si>
+  <si>
+    <t>rez_spv_089</t>
+  </si>
+  <si>
+    <t>elc_spv_089</t>
+  </si>
+  <si>
+    <t>rez_spv_090</t>
+  </si>
+  <si>
+    <t>elc_spv_090</t>
+  </si>
+  <si>
+    <t>rez_spv_091</t>
+  </si>
+  <si>
+    <t>elc_spv_091</t>
+  </si>
+  <si>
+    <t>rez_spv_092</t>
+  </si>
+  <si>
+    <t>elc_spv_092</t>
+  </si>
+  <si>
+    <t>rez_spv_093</t>
+  </si>
+  <si>
+    <t>elc_spv_093</t>
+  </si>
+  <si>
+    <t>rez_spv_094</t>
+  </si>
+  <si>
+    <t>elc_spv_094</t>
+  </si>
+  <si>
+    <t>rez_spv_095</t>
+  </si>
+  <si>
+    <t>elc_spv_095</t>
+  </si>
+  <si>
+    <t>rez_spv_096</t>
+  </si>
+  <si>
+    <t>elc_spv_096</t>
+  </si>
+  <si>
+    <t>rez_spv_097</t>
+  </si>
+  <si>
+    <t>elc_spv_097</t>
+  </si>
+  <si>
+    <t>rez_spv_098</t>
+  </si>
+  <si>
+    <t>elc_spv_098</t>
+  </si>
+  <si>
+    <t>rez_spv_099</t>
+  </si>
+  <si>
+    <t>elc_spv_099</t>
+  </si>
+  <si>
+    <t>rez_spv_100</t>
+  </si>
+  <si>
+    <t>elc_spv_100</t>
+  </si>
+  <si>
+    <t>rez_spv_101</t>
+  </si>
+  <si>
+    <t>elc_spv_101</t>
+  </si>
+  <si>
+    <t>rez_spv_102</t>
+  </si>
+  <si>
+    <t>elc_spv_102</t>
+  </si>
+  <si>
+    <t>rez_spv_103</t>
+  </si>
+  <si>
+    <t>elc_spv_103</t>
+  </si>
+  <si>
+    <t>rez_spv_104</t>
+  </si>
+  <si>
+    <t>elc_spv_104</t>
+  </si>
+  <si>
+    <t>rez_spv_105</t>
+  </si>
+  <si>
+    <t>elc_spv_105</t>
+  </si>
+  <si>
+    <t>rez_spv_106</t>
+  </si>
+  <si>
+    <t>elc_spv_106</t>
+  </si>
+  <si>
+    <t>rez_spv_107</t>
+  </si>
+  <si>
+    <t>elc_spv_107</t>
+  </si>
+  <si>
+    <t>rez_spv_108</t>
+  </si>
+  <si>
+    <t>elc_spv_108</t>
+  </si>
+  <si>
+    <t>rez_spv_109</t>
+  </si>
+  <si>
+    <t>elc_spv_109</t>
+  </si>
+  <si>
+    <t>rez_spv_110</t>
+  </si>
+  <si>
+    <t>elc_spv_110</t>
+  </si>
+  <si>
+    <t>rez_spv_111</t>
+  </si>
+  <si>
+    <t>elc_spv_111</t>
+  </si>
+  <si>
+    <t>rez_spv_112</t>
+  </si>
+  <si>
+    <t>elc_spv_112</t>
+  </si>
+  <si>
+    <t>rez_spv_113</t>
+  </si>
+  <si>
+    <t>elc_spv_113</t>
+  </si>
+  <si>
+    <t>rez_spv_114</t>
+  </si>
+  <si>
+    <t>elc_spv_114</t>
+  </si>
+  <si>
+    <t>rez_spv_115</t>
+  </si>
+  <si>
+    <t>elc_spv_115</t>
+  </si>
+  <si>
     <t>rez_won_001</t>
   </si>
   <si>
@@ -2876,696 +3566,6 @@
   </si>
   <si>
     <t>elc_wof_031</t>
-  </si>
-  <si>
-    <t>rez_spv_001</t>
-  </si>
-  <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>rez_spv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>rez_spv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>rez_spv_004</t>
-  </si>
-  <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>rez_spv_005</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>rez_spv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>rez_spv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>rez_spv_008</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>rez_spv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>rez_spv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>rez_spv_011</t>
-  </si>
-  <si>
-    <t>elc_spv_011</t>
-  </si>
-  <si>
-    <t>rez_spv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>rez_spv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
-    <t>rez_spv_014</t>
-  </si>
-  <si>
-    <t>elc_spv_014</t>
-  </si>
-  <si>
-    <t>rez_spv_015</t>
-  </si>
-  <si>
-    <t>elc_spv_015</t>
-  </si>
-  <si>
-    <t>rez_spv_016</t>
-  </si>
-  <si>
-    <t>elc_spv_016</t>
-  </si>
-  <si>
-    <t>rez_spv_017</t>
-  </si>
-  <si>
-    <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>rez_spv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
-  </si>
-  <si>
-    <t>rez_spv_019</t>
-  </si>
-  <si>
-    <t>elc_spv_019</t>
-  </si>
-  <si>
-    <t>rez_spv_020</t>
-  </si>
-  <si>
-    <t>elc_spv_020</t>
-  </si>
-  <si>
-    <t>rez_spv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
-    <t>rez_spv_022</t>
-  </si>
-  <si>
-    <t>elc_spv_022</t>
-  </si>
-  <si>
-    <t>rez_spv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>rez_spv_024</t>
-  </si>
-  <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
-    <t>rez_spv_025</t>
-  </si>
-  <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>rez_spv_026</t>
-  </si>
-  <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
-    <t>rez_spv_027</t>
-  </si>
-  <si>
-    <t>elc_spv_027</t>
-  </si>
-  <si>
-    <t>rez_spv_028</t>
-  </si>
-  <si>
-    <t>elc_spv_028</t>
-  </si>
-  <si>
-    <t>rez_spv_029</t>
-  </si>
-  <si>
-    <t>elc_spv_029</t>
-  </si>
-  <si>
-    <t>rez_spv_030</t>
-  </si>
-  <si>
-    <t>elc_spv_030</t>
-  </si>
-  <si>
-    <t>rez_spv_031</t>
-  </si>
-  <si>
-    <t>elc_spv_031</t>
-  </si>
-  <si>
-    <t>rez_spv_032</t>
-  </si>
-  <si>
-    <t>elc_spv_032</t>
-  </si>
-  <si>
-    <t>rez_spv_033</t>
-  </si>
-  <si>
-    <t>elc_spv_033</t>
-  </si>
-  <si>
-    <t>rez_spv_034</t>
-  </si>
-  <si>
-    <t>elc_spv_034</t>
-  </si>
-  <si>
-    <t>rez_spv_035</t>
-  </si>
-  <si>
-    <t>elc_spv_035</t>
-  </si>
-  <si>
-    <t>rez_spv_036</t>
-  </si>
-  <si>
-    <t>elc_spv_036</t>
-  </si>
-  <si>
-    <t>rez_spv_037</t>
-  </si>
-  <si>
-    <t>elc_spv_037</t>
-  </si>
-  <si>
-    <t>rez_spv_038</t>
-  </si>
-  <si>
-    <t>elc_spv_038</t>
-  </si>
-  <si>
-    <t>rez_spv_039</t>
-  </si>
-  <si>
-    <t>elc_spv_039</t>
-  </si>
-  <si>
-    <t>rez_spv_040</t>
-  </si>
-  <si>
-    <t>elc_spv_040</t>
-  </si>
-  <si>
-    <t>rez_spv_041</t>
-  </si>
-  <si>
-    <t>elc_spv_041</t>
-  </si>
-  <si>
-    <t>rez_spv_042</t>
-  </si>
-  <si>
-    <t>elc_spv_042</t>
-  </si>
-  <si>
-    <t>rez_spv_043</t>
-  </si>
-  <si>
-    <t>elc_spv_043</t>
-  </si>
-  <si>
-    <t>rez_spv_044</t>
-  </si>
-  <si>
-    <t>elc_spv_044</t>
-  </si>
-  <si>
-    <t>rez_spv_045</t>
-  </si>
-  <si>
-    <t>elc_spv_045</t>
-  </si>
-  <si>
-    <t>rez_spv_046</t>
-  </si>
-  <si>
-    <t>elc_spv_046</t>
-  </si>
-  <si>
-    <t>rez_spv_047</t>
-  </si>
-  <si>
-    <t>elc_spv_047</t>
-  </si>
-  <si>
-    <t>rez_spv_048</t>
-  </si>
-  <si>
-    <t>elc_spv_048</t>
-  </si>
-  <si>
-    <t>rez_spv_049</t>
-  </si>
-  <si>
-    <t>elc_spv_049</t>
-  </si>
-  <si>
-    <t>rez_spv_050</t>
-  </si>
-  <si>
-    <t>elc_spv_050</t>
-  </si>
-  <si>
-    <t>rez_spv_051</t>
-  </si>
-  <si>
-    <t>elc_spv_051</t>
-  </si>
-  <si>
-    <t>rez_spv_052</t>
-  </si>
-  <si>
-    <t>elc_spv_052</t>
-  </si>
-  <si>
-    <t>rez_spv_053</t>
-  </si>
-  <si>
-    <t>elc_spv_053</t>
-  </si>
-  <si>
-    <t>rez_spv_054</t>
-  </si>
-  <si>
-    <t>elc_spv_054</t>
-  </si>
-  <si>
-    <t>rez_spv_055</t>
-  </si>
-  <si>
-    <t>elc_spv_055</t>
-  </si>
-  <si>
-    <t>rez_spv_056</t>
-  </si>
-  <si>
-    <t>elc_spv_056</t>
-  </si>
-  <si>
-    <t>rez_spv_057</t>
-  </si>
-  <si>
-    <t>elc_spv_057</t>
-  </si>
-  <si>
-    <t>rez_spv_058</t>
-  </si>
-  <si>
-    <t>elc_spv_058</t>
-  </si>
-  <si>
-    <t>rez_spv_059</t>
-  </si>
-  <si>
-    <t>elc_spv_059</t>
-  </si>
-  <si>
-    <t>rez_spv_060</t>
-  </si>
-  <si>
-    <t>elc_spv_060</t>
-  </si>
-  <si>
-    <t>rez_spv_061</t>
-  </si>
-  <si>
-    <t>elc_spv_061</t>
-  </si>
-  <si>
-    <t>rez_spv_062</t>
-  </si>
-  <si>
-    <t>elc_spv_062</t>
-  </si>
-  <si>
-    <t>rez_spv_063</t>
-  </si>
-  <si>
-    <t>elc_spv_063</t>
-  </si>
-  <si>
-    <t>rez_spv_064</t>
-  </si>
-  <si>
-    <t>elc_spv_064</t>
-  </si>
-  <si>
-    <t>rez_spv_065</t>
-  </si>
-  <si>
-    <t>elc_spv_065</t>
-  </si>
-  <si>
-    <t>rez_spv_066</t>
-  </si>
-  <si>
-    <t>elc_spv_066</t>
-  </si>
-  <si>
-    <t>rez_spv_067</t>
-  </si>
-  <si>
-    <t>elc_spv_067</t>
-  </si>
-  <si>
-    <t>rez_spv_068</t>
-  </si>
-  <si>
-    <t>elc_spv_068</t>
-  </si>
-  <si>
-    <t>rez_spv_069</t>
-  </si>
-  <si>
-    <t>elc_spv_069</t>
-  </si>
-  <si>
-    <t>rez_spv_070</t>
-  </si>
-  <si>
-    <t>elc_spv_070</t>
-  </si>
-  <si>
-    <t>rez_spv_071</t>
-  </si>
-  <si>
-    <t>elc_spv_071</t>
-  </si>
-  <si>
-    <t>rez_spv_072</t>
-  </si>
-  <si>
-    <t>elc_spv_072</t>
-  </si>
-  <si>
-    <t>rez_spv_073</t>
-  </si>
-  <si>
-    <t>elc_spv_073</t>
-  </si>
-  <si>
-    <t>rez_spv_074</t>
-  </si>
-  <si>
-    <t>elc_spv_074</t>
-  </si>
-  <si>
-    <t>rez_spv_075</t>
-  </si>
-  <si>
-    <t>elc_spv_075</t>
-  </si>
-  <si>
-    <t>rez_spv_076</t>
-  </si>
-  <si>
-    <t>elc_spv_076</t>
-  </si>
-  <si>
-    <t>rez_spv_077</t>
-  </si>
-  <si>
-    <t>elc_spv_077</t>
-  </si>
-  <si>
-    <t>rez_spv_078</t>
-  </si>
-  <si>
-    <t>elc_spv_078</t>
-  </si>
-  <si>
-    <t>rez_spv_079</t>
-  </si>
-  <si>
-    <t>elc_spv_079</t>
-  </si>
-  <si>
-    <t>rez_spv_080</t>
-  </si>
-  <si>
-    <t>elc_spv_080</t>
-  </si>
-  <si>
-    <t>rez_spv_081</t>
-  </si>
-  <si>
-    <t>elc_spv_081</t>
-  </si>
-  <si>
-    <t>rez_spv_082</t>
-  </si>
-  <si>
-    <t>elc_spv_082</t>
-  </si>
-  <si>
-    <t>rez_spv_083</t>
-  </si>
-  <si>
-    <t>elc_spv_083</t>
-  </si>
-  <si>
-    <t>rez_spv_084</t>
-  </si>
-  <si>
-    <t>elc_spv_084</t>
-  </si>
-  <si>
-    <t>rez_spv_085</t>
-  </si>
-  <si>
-    <t>elc_spv_085</t>
-  </si>
-  <si>
-    <t>rez_spv_086</t>
-  </si>
-  <si>
-    <t>elc_spv_086</t>
-  </si>
-  <si>
-    <t>rez_spv_087</t>
-  </si>
-  <si>
-    <t>elc_spv_087</t>
-  </si>
-  <si>
-    <t>rez_spv_088</t>
-  </si>
-  <si>
-    <t>elc_spv_088</t>
-  </si>
-  <si>
-    <t>rez_spv_089</t>
-  </si>
-  <si>
-    <t>elc_spv_089</t>
-  </si>
-  <si>
-    <t>rez_spv_090</t>
-  </si>
-  <si>
-    <t>elc_spv_090</t>
-  </si>
-  <si>
-    <t>rez_spv_091</t>
-  </si>
-  <si>
-    <t>elc_spv_091</t>
-  </si>
-  <si>
-    <t>rez_spv_092</t>
-  </si>
-  <si>
-    <t>elc_spv_092</t>
-  </si>
-  <si>
-    <t>rez_spv_093</t>
-  </si>
-  <si>
-    <t>elc_spv_093</t>
-  </si>
-  <si>
-    <t>rez_spv_094</t>
-  </si>
-  <si>
-    <t>elc_spv_094</t>
-  </si>
-  <si>
-    <t>rez_spv_095</t>
-  </si>
-  <si>
-    <t>elc_spv_095</t>
-  </si>
-  <si>
-    <t>rez_spv_096</t>
-  </si>
-  <si>
-    <t>elc_spv_096</t>
-  </si>
-  <si>
-    <t>rez_spv_097</t>
-  </si>
-  <si>
-    <t>elc_spv_097</t>
-  </si>
-  <si>
-    <t>rez_spv_098</t>
-  </si>
-  <si>
-    <t>elc_spv_098</t>
-  </si>
-  <si>
-    <t>rez_spv_099</t>
-  </si>
-  <si>
-    <t>elc_spv_099</t>
-  </si>
-  <si>
-    <t>rez_spv_100</t>
-  </si>
-  <si>
-    <t>elc_spv_100</t>
-  </si>
-  <si>
-    <t>rez_spv_101</t>
-  </si>
-  <si>
-    <t>elc_spv_101</t>
-  </si>
-  <si>
-    <t>rez_spv_102</t>
-  </si>
-  <si>
-    <t>elc_spv_102</t>
-  </si>
-  <si>
-    <t>rez_spv_103</t>
-  </si>
-  <si>
-    <t>elc_spv_103</t>
-  </si>
-  <si>
-    <t>rez_spv_104</t>
-  </si>
-  <si>
-    <t>elc_spv_104</t>
-  </si>
-  <si>
-    <t>rez_spv_105</t>
-  </si>
-  <si>
-    <t>elc_spv_105</t>
-  </si>
-  <si>
-    <t>rez_spv_106</t>
-  </si>
-  <si>
-    <t>elc_spv_106</t>
-  </si>
-  <si>
-    <t>rez_spv_107</t>
-  </si>
-  <si>
-    <t>elc_spv_107</t>
-  </si>
-  <si>
-    <t>rez_spv_108</t>
-  </si>
-  <si>
-    <t>elc_spv_108</t>
-  </si>
-  <si>
-    <t>rez_spv_109</t>
-  </si>
-  <si>
-    <t>elc_spv_109</t>
-  </si>
-  <si>
-    <t>rez_spv_110</t>
-  </si>
-  <si>
-    <t>elc_spv_110</t>
-  </si>
-  <si>
-    <t>rez_spv_111</t>
-  </si>
-  <si>
-    <t>elc_spv_111</t>
-  </si>
-  <si>
-    <t>rez_spv_112</t>
-  </si>
-  <si>
-    <t>elc_spv_112</t>
-  </si>
-  <si>
-    <t>rez_spv_113</t>
-  </si>
-  <si>
-    <t>elc_spv_113</t>
-  </si>
-  <si>
-    <t>rez_spv_114</t>
-  </si>
-  <si>
-    <t>elc_spv_114</t>
-  </si>
-  <si>
-    <t>rez_spv_115</t>
-  </si>
-  <si>
-    <t>elc_spv_115</t>
   </si>
 </sst>
 </file>
@@ -4403,14 +4403,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1511DC3F-90EC-40F9-8035-02FAF19A6694}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033BF57-ED07-4549-AEB9-94914D0266AA}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.59765625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
@@ -8927,13 +8922,13 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B332" t="s">
-        <v>946</v>
+        <v>746</v>
       </c>
       <c r="C332" t="s">
-        <v>947</v>
+        <v>747</v>
       </c>
       <c r="D332" t="s">
-        <v>947</v>
+        <v>747</v>
       </c>
       <c r="E332" t="s">
         <v>105</v>
@@ -8941,13 +8936,13 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B333" t="s">
-        <v>948</v>
+        <v>748</v>
       </c>
       <c r="C333" t="s">
-        <v>949</v>
+        <v>749</v>
       </c>
       <c r="D333" t="s">
-        <v>949</v>
+        <v>749</v>
       </c>
       <c r="E333" t="s">
         <v>105</v>
@@ -8955,13 +8950,13 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B334" t="s">
-        <v>950</v>
+        <v>750</v>
       </c>
       <c r="C334" t="s">
-        <v>951</v>
+        <v>751</v>
       </c>
       <c r="D334" t="s">
-        <v>951</v>
+        <v>751</v>
       </c>
       <c r="E334" t="s">
         <v>105</v>
@@ -8969,13 +8964,13 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B335" t="s">
-        <v>952</v>
+        <v>752</v>
       </c>
       <c r="C335" t="s">
-        <v>953</v>
+        <v>753</v>
       </c>
       <c r="D335" t="s">
-        <v>953</v>
+        <v>753</v>
       </c>
       <c r="E335" t="s">
         <v>105</v>
@@ -8983,13 +8978,13 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B336" t="s">
-        <v>954</v>
+        <v>754</v>
       </c>
       <c r="C336" t="s">
-        <v>955</v>
+        <v>755</v>
       </c>
       <c r="D336" t="s">
-        <v>955</v>
+        <v>755</v>
       </c>
       <c r="E336" t="s">
         <v>105</v>
@@ -8997,13 +8992,13 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B337" t="s">
-        <v>956</v>
+        <v>756</v>
       </c>
       <c r="C337" t="s">
-        <v>957</v>
+        <v>757</v>
       </c>
       <c r="D337" t="s">
-        <v>957</v>
+        <v>757</v>
       </c>
       <c r="E337" t="s">
         <v>105</v>
@@ -9011,13 +9006,13 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B338" t="s">
-        <v>958</v>
+        <v>758</v>
       </c>
       <c r="C338" t="s">
-        <v>959</v>
+        <v>759</v>
       </c>
       <c r="D338" t="s">
-        <v>959</v>
+        <v>759</v>
       </c>
       <c r="E338" t="s">
         <v>105</v>
@@ -9025,13 +9020,13 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B339" t="s">
-        <v>960</v>
+        <v>760</v>
       </c>
       <c r="C339" t="s">
-        <v>961</v>
+        <v>761</v>
       </c>
       <c r="D339" t="s">
-        <v>961</v>
+        <v>761</v>
       </c>
       <c r="E339" t="s">
         <v>105</v>
@@ -9039,13 +9034,13 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B340" t="s">
-        <v>962</v>
+        <v>762</v>
       </c>
       <c r="C340" t="s">
-        <v>963</v>
+        <v>763</v>
       </c>
       <c r="D340" t="s">
-        <v>963</v>
+        <v>763</v>
       </c>
       <c r="E340" t="s">
         <v>105</v>
@@ -9053,13 +9048,13 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B341" t="s">
-        <v>964</v>
+        <v>764</v>
       </c>
       <c r="C341" t="s">
-        <v>965</v>
+        <v>765</v>
       </c>
       <c r="D341" t="s">
-        <v>965</v>
+        <v>765</v>
       </c>
       <c r="E341" t="s">
         <v>105</v>
@@ -9067,13 +9062,13 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B342" t="s">
-        <v>966</v>
+        <v>766</v>
       </c>
       <c r="C342" t="s">
-        <v>967</v>
+        <v>767</v>
       </c>
       <c r="D342" t="s">
-        <v>967</v>
+        <v>767</v>
       </c>
       <c r="E342" t="s">
         <v>105</v>
@@ -9081,13 +9076,13 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B343" t="s">
-        <v>968</v>
+        <v>768</v>
       </c>
       <c r="C343" t="s">
-        <v>969</v>
+        <v>769</v>
       </c>
       <c r="D343" t="s">
-        <v>969</v>
+        <v>769</v>
       </c>
       <c r="E343" t="s">
         <v>105</v>
@@ -9095,13 +9090,13 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B344" t="s">
-        <v>970</v>
+        <v>770</v>
       </c>
       <c r="C344" t="s">
-        <v>971</v>
+        <v>771</v>
       </c>
       <c r="D344" t="s">
-        <v>971</v>
+        <v>771</v>
       </c>
       <c r="E344" t="s">
         <v>105</v>
@@ -9109,13 +9104,13 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B345" t="s">
-        <v>972</v>
+        <v>772</v>
       </c>
       <c r="C345" t="s">
-        <v>973</v>
+        <v>773</v>
       </c>
       <c r="D345" t="s">
-        <v>973</v>
+        <v>773</v>
       </c>
       <c r="E345" t="s">
         <v>105</v>
@@ -9123,13 +9118,13 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B346" t="s">
-        <v>974</v>
+        <v>774</v>
       </c>
       <c r="C346" t="s">
-        <v>975</v>
+        <v>775</v>
       </c>
       <c r="D346" t="s">
-        <v>975</v>
+        <v>775</v>
       </c>
       <c r="E346" t="s">
         <v>105</v>
@@ -9137,13 +9132,13 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B347" t="s">
-        <v>976</v>
+        <v>776</v>
       </c>
       <c r="C347" t="s">
-        <v>977</v>
+        <v>777</v>
       </c>
       <c r="D347" t="s">
-        <v>977</v>
+        <v>777</v>
       </c>
       <c r="E347" t="s">
         <v>105</v>
@@ -9151,13 +9146,13 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B348" t="s">
-        <v>978</v>
+        <v>778</v>
       </c>
       <c r="C348" t="s">
-        <v>979</v>
+        <v>779</v>
       </c>
       <c r="D348" t="s">
-        <v>979</v>
+        <v>779</v>
       </c>
       <c r="E348" t="s">
         <v>105</v>
@@ -9165,13 +9160,13 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B349" t="s">
-        <v>980</v>
+        <v>780</v>
       </c>
       <c r="C349" t="s">
-        <v>981</v>
+        <v>781</v>
       </c>
       <c r="D349" t="s">
-        <v>981</v>
+        <v>781</v>
       </c>
       <c r="E349" t="s">
         <v>105</v>
@@ -9179,13 +9174,13 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B350" t="s">
-        <v>982</v>
+        <v>782</v>
       </c>
       <c r="C350" t="s">
-        <v>983</v>
+        <v>783</v>
       </c>
       <c r="D350" t="s">
-        <v>983</v>
+        <v>783</v>
       </c>
       <c r="E350" t="s">
         <v>105</v>
@@ -9193,13 +9188,13 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B351" t="s">
-        <v>984</v>
+        <v>784</v>
       </c>
       <c r="C351" t="s">
-        <v>985</v>
+        <v>785</v>
       </c>
       <c r="D351" t="s">
-        <v>985</v>
+        <v>785</v>
       </c>
       <c r="E351" t="s">
         <v>105</v>
@@ -9207,13 +9202,13 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B352" t="s">
-        <v>986</v>
+        <v>786</v>
       </c>
       <c r="C352" t="s">
-        <v>987</v>
+        <v>787</v>
       </c>
       <c r="D352" t="s">
-        <v>987</v>
+        <v>787</v>
       </c>
       <c r="E352" t="s">
         <v>105</v>
@@ -9221,13 +9216,13 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B353" t="s">
-        <v>988</v>
+        <v>788</v>
       </c>
       <c r="C353" t="s">
-        <v>989</v>
+        <v>789</v>
       </c>
       <c r="D353" t="s">
-        <v>989</v>
+        <v>789</v>
       </c>
       <c r="E353" t="s">
         <v>105</v>
@@ -9235,13 +9230,13 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B354" t="s">
-        <v>990</v>
+        <v>790</v>
       </c>
       <c r="C354" t="s">
-        <v>991</v>
+        <v>791</v>
       </c>
       <c r="D354" t="s">
-        <v>991</v>
+        <v>791</v>
       </c>
       <c r="E354" t="s">
         <v>105</v>
@@ -9249,13 +9244,13 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B355" t="s">
-        <v>992</v>
+        <v>792</v>
       </c>
       <c r="C355" t="s">
-        <v>993</v>
+        <v>793</v>
       </c>
       <c r="D355" t="s">
-        <v>993</v>
+        <v>793</v>
       </c>
       <c r="E355" t="s">
         <v>105</v>
@@ -9263,13 +9258,13 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B356" t="s">
-        <v>994</v>
+        <v>794</v>
       </c>
       <c r="C356" t="s">
-        <v>995</v>
+        <v>795</v>
       </c>
       <c r="D356" t="s">
-        <v>995</v>
+        <v>795</v>
       </c>
       <c r="E356" t="s">
         <v>105</v>
@@ -9277,13 +9272,13 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B357" t="s">
-        <v>996</v>
+        <v>796</v>
       </c>
       <c r="C357" t="s">
-        <v>997</v>
+        <v>797</v>
       </c>
       <c r="D357" t="s">
-        <v>997</v>
+        <v>797</v>
       </c>
       <c r="E357" t="s">
         <v>105</v>
@@ -9291,13 +9286,13 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B358" t="s">
-        <v>998</v>
+        <v>798</v>
       </c>
       <c r="C358" t="s">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="D358" t="s">
-        <v>999</v>
+        <v>799</v>
       </c>
       <c r="E358" t="s">
         <v>105</v>
@@ -9305,13 +9300,13 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B359" t="s">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C359" t="s">
-        <v>1001</v>
+        <v>801</v>
       </c>
       <c r="D359" t="s">
-        <v>1001</v>
+        <v>801</v>
       </c>
       <c r="E359" t="s">
         <v>105</v>
@@ -9319,13 +9314,13 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B360" t="s">
-        <v>1002</v>
+        <v>802</v>
       </c>
       <c r="C360" t="s">
-        <v>1003</v>
+        <v>803</v>
       </c>
       <c r="D360" t="s">
-        <v>1003</v>
+        <v>803</v>
       </c>
       <c r="E360" t="s">
         <v>105</v>
@@ -9333,13 +9328,13 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B361" t="s">
-        <v>1004</v>
+        <v>804</v>
       </c>
       <c r="C361" t="s">
-        <v>1005</v>
+        <v>805</v>
       </c>
       <c r="D361" t="s">
-        <v>1005</v>
+        <v>805</v>
       </c>
       <c r="E361" t="s">
         <v>105</v>
@@ -9347,13 +9342,13 @@
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B362" t="s">
-        <v>1006</v>
+        <v>806</v>
       </c>
       <c r="C362" t="s">
-        <v>1007</v>
+        <v>807</v>
       </c>
       <c r="D362" t="s">
-        <v>1007</v>
+        <v>807</v>
       </c>
       <c r="E362" t="s">
         <v>105</v>
@@ -9361,13 +9356,13 @@
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B363" t="s">
-        <v>1008</v>
+        <v>808</v>
       </c>
       <c r="C363" t="s">
-        <v>1009</v>
+        <v>809</v>
       </c>
       <c r="D363" t="s">
-        <v>1009</v>
+        <v>809</v>
       </c>
       <c r="E363" t="s">
         <v>105</v>
@@ -9375,13 +9370,13 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B364" t="s">
-        <v>1010</v>
+        <v>810</v>
       </c>
       <c r="C364" t="s">
-        <v>1011</v>
+        <v>811</v>
       </c>
       <c r="D364" t="s">
-        <v>1011</v>
+        <v>811</v>
       </c>
       <c r="E364" t="s">
         <v>105</v>
@@ -9389,13 +9384,13 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B365" t="s">
-        <v>1012</v>
+        <v>812</v>
       </c>
       <c r="C365" t="s">
-        <v>1013</v>
+        <v>813</v>
       </c>
       <c r="D365" t="s">
-        <v>1013</v>
+        <v>813</v>
       </c>
       <c r="E365" t="s">
         <v>105</v>
@@ -9403,13 +9398,13 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B366" t="s">
-        <v>1014</v>
+        <v>814</v>
       </c>
       <c r="C366" t="s">
-        <v>1015</v>
+        <v>815</v>
       </c>
       <c r="D366" t="s">
-        <v>1015</v>
+        <v>815</v>
       </c>
       <c r="E366" t="s">
         <v>105</v>
@@ -9417,13 +9412,13 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B367" t="s">
-        <v>1016</v>
+        <v>816</v>
       </c>
       <c r="C367" t="s">
-        <v>1017</v>
+        <v>817</v>
       </c>
       <c r="D367" t="s">
-        <v>1017</v>
+        <v>817</v>
       </c>
       <c r="E367" t="s">
         <v>105</v>
@@ -9431,13 +9426,13 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B368" t="s">
-        <v>1018</v>
+        <v>818</v>
       </c>
       <c r="C368" t="s">
-        <v>1019</v>
+        <v>819</v>
       </c>
       <c r="D368" t="s">
-        <v>1019</v>
+        <v>819</v>
       </c>
       <c r="E368" t="s">
         <v>105</v>
@@ -9445,13 +9440,13 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B369" t="s">
-        <v>1020</v>
+        <v>820</v>
       </c>
       <c r="C369" t="s">
-        <v>1021</v>
+        <v>821</v>
       </c>
       <c r="D369" t="s">
-        <v>1021</v>
+        <v>821</v>
       </c>
       <c r="E369" t="s">
         <v>105</v>
@@ -9459,13 +9454,13 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B370" t="s">
-        <v>1022</v>
+        <v>822</v>
       </c>
       <c r="C370" t="s">
-        <v>1023</v>
+        <v>823</v>
       </c>
       <c r="D370" t="s">
-        <v>1023</v>
+        <v>823</v>
       </c>
       <c r="E370" t="s">
         <v>105</v>
@@ -9473,13 +9468,13 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B371" t="s">
-        <v>1024</v>
+        <v>824</v>
       </c>
       <c r="C371" t="s">
-        <v>1025</v>
+        <v>825</v>
       </c>
       <c r="D371" t="s">
-        <v>1025</v>
+        <v>825</v>
       </c>
       <c r="E371" t="s">
         <v>105</v>
@@ -9487,13 +9482,13 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B372" t="s">
-        <v>1026</v>
+        <v>826</v>
       </c>
       <c r="C372" t="s">
-        <v>1027</v>
+        <v>827</v>
       </c>
       <c r="D372" t="s">
-        <v>1027</v>
+        <v>827</v>
       </c>
       <c r="E372" t="s">
         <v>105</v>
@@ -9501,13 +9496,13 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B373" t="s">
-        <v>1028</v>
+        <v>828</v>
       </c>
       <c r="C373" t="s">
-        <v>1029</v>
+        <v>829</v>
       </c>
       <c r="D373" t="s">
-        <v>1029</v>
+        <v>829</v>
       </c>
       <c r="E373" t="s">
         <v>105</v>
@@ -9515,13 +9510,13 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B374" t="s">
-        <v>1030</v>
+        <v>830</v>
       </c>
       <c r="C374" t="s">
-        <v>1031</v>
+        <v>831</v>
       </c>
       <c r="D374" t="s">
-        <v>1031</v>
+        <v>831</v>
       </c>
       <c r="E374" t="s">
         <v>105</v>
@@ -9529,13 +9524,13 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B375" t="s">
-        <v>1032</v>
+        <v>832</v>
       </c>
       <c r="C375" t="s">
-        <v>1033</v>
+        <v>833</v>
       </c>
       <c r="D375" t="s">
-        <v>1033</v>
+        <v>833</v>
       </c>
       <c r="E375" t="s">
         <v>105</v>
@@ -9543,13 +9538,13 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B376" t="s">
-        <v>1034</v>
+        <v>834</v>
       </c>
       <c r="C376" t="s">
-        <v>1035</v>
+        <v>835</v>
       </c>
       <c r="D376" t="s">
-        <v>1035</v>
+        <v>835</v>
       </c>
       <c r="E376" t="s">
         <v>105</v>
@@ -9557,13 +9552,13 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B377" t="s">
-        <v>1036</v>
+        <v>836</v>
       </c>
       <c r="C377" t="s">
-        <v>1037</v>
+        <v>837</v>
       </c>
       <c r="D377" t="s">
-        <v>1037</v>
+        <v>837</v>
       </c>
       <c r="E377" t="s">
         <v>105</v>
@@ -9571,13 +9566,13 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B378" t="s">
-        <v>1038</v>
+        <v>838</v>
       </c>
       <c r="C378" t="s">
-        <v>1039</v>
+        <v>839</v>
       </c>
       <c r="D378" t="s">
-        <v>1039</v>
+        <v>839</v>
       </c>
       <c r="E378" t="s">
         <v>105</v>
@@ -9585,13 +9580,13 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B379" t="s">
-        <v>1040</v>
+        <v>840</v>
       </c>
       <c r="C379" t="s">
-        <v>1041</v>
+        <v>841</v>
       </c>
       <c r="D379" t="s">
-        <v>1041</v>
+        <v>841</v>
       </c>
       <c r="E379" t="s">
         <v>105</v>
@@ -9599,13 +9594,13 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B380" t="s">
-        <v>1042</v>
+        <v>842</v>
       </c>
       <c r="C380" t="s">
-        <v>1043</v>
+        <v>843</v>
       </c>
       <c r="D380" t="s">
-        <v>1043</v>
+        <v>843</v>
       </c>
       <c r="E380" t="s">
         <v>105</v>
@@ -9613,13 +9608,13 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B381" t="s">
-        <v>1044</v>
+        <v>844</v>
       </c>
       <c r="C381" t="s">
-        <v>1045</v>
+        <v>845</v>
       </c>
       <c r="D381" t="s">
-        <v>1045</v>
+        <v>845</v>
       </c>
       <c r="E381" t="s">
         <v>105</v>
@@ -9627,13 +9622,13 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B382" t="s">
-        <v>1046</v>
+        <v>846</v>
       </c>
       <c r="C382" t="s">
-        <v>1047</v>
+        <v>847</v>
       </c>
       <c r="D382" t="s">
-        <v>1047</v>
+        <v>847</v>
       </c>
       <c r="E382" t="s">
         <v>105</v>
@@ -9641,13 +9636,13 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B383" t="s">
-        <v>1048</v>
+        <v>848</v>
       </c>
       <c r="C383" t="s">
-        <v>1049</v>
+        <v>849</v>
       </c>
       <c r="D383" t="s">
-        <v>1049</v>
+        <v>849</v>
       </c>
       <c r="E383" t="s">
         <v>105</v>
@@ -9655,13 +9650,13 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B384" t="s">
-        <v>1050</v>
+        <v>850</v>
       </c>
       <c r="C384" t="s">
-        <v>1051</v>
+        <v>851</v>
       </c>
       <c r="D384" t="s">
-        <v>1051</v>
+        <v>851</v>
       </c>
       <c r="E384" t="s">
         <v>105</v>
@@ -9669,13 +9664,13 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B385" t="s">
-        <v>1052</v>
+        <v>852</v>
       </c>
       <c r="C385" t="s">
-        <v>1053</v>
+        <v>853</v>
       </c>
       <c r="D385" t="s">
-        <v>1053</v>
+        <v>853</v>
       </c>
       <c r="E385" t="s">
         <v>105</v>
@@ -9683,13 +9678,13 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B386" t="s">
-        <v>1054</v>
+        <v>854</v>
       </c>
       <c r="C386" t="s">
-        <v>1055</v>
+        <v>855</v>
       </c>
       <c r="D386" t="s">
-        <v>1055</v>
+        <v>855</v>
       </c>
       <c r="E386" t="s">
         <v>105</v>
@@ -9697,13 +9692,13 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B387" t="s">
-        <v>1056</v>
+        <v>856</v>
       </c>
       <c r="C387" t="s">
-        <v>1057</v>
+        <v>857</v>
       </c>
       <c r="D387" t="s">
-        <v>1057</v>
+        <v>857</v>
       </c>
       <c r="E387" t="s">
         <v>105</v>
@@ -9711,13 +9706,13 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B388" t="s">
-        <v>1058</v>
+        <v>858</v>
       </c>
       <c r="C388" t="s">
-        <v>1059</v>
+        <v>859</v>
       </c>
       <c r="D388" t="s">
-        <v>1059</v>
+        <v>859</v>
       </c>
       <c r="E388" t="s">
         <v>105</v>
@@ -9725,13 +9720,13 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B389" t="s">
-        <v>1060</v>
+        <v>860</v>
       </c>
       <c r="C389" t="s">
-        <v>1061</v>
+        <v>861</v>
       </c>
       <c r="D389" t="s">
-        <v>1061</v>
+        <v>861</v>
       </c>
       <c r="E389" t="s">
         <v>105</v>
@@ -9739,13 +9734,13 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B390" t="s">
-        <v>1062</v>
+        <v>862</v>
       </c>
       <c r="C390" t="s">
-        <v>1063</v>
+        <v>863</v>
       </c>
       <c r="D390" t="s">
-        <v>1063</v>
+        <v>863</v>
       </c>
       <c r="E390" t="s">
         <v>105</v>
@@ -9753,13 +9748,13 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B391" t="s">
-        <v>1064</v>
+        <v>864</v>
       </c>
       <c r="C391" t="s">
-        <v>1065</v>
+        <v>865</v>
       </c>
       <c r="D391" t="s">
-        <v>1065</v>
+        <v>865</v>
       </c>
       <c r="E391" t="s">
         <v>105</v>
@@ -9767,13 +9762,13 @@
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B392" t="s">
-        <v>1066</v>
+        <v>866</v>
       </c>
       <c r="C392" t="s">
-        <v>1067</v>
+        <v>867</v>
       </c>
       <c r="D392" t="s">
-        <v>1067</v>
+        <v>867</v>
       </c>
       <c r="E392" t="s">
         <v>105</v>
@@ -9781,13 +9776,13 @@
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B393" t="s">
-        <v>1068</v>
+        <v>868</v>
       </c>
       <c r="C393" t="s">
-        <v>1069</v>
+        <v>869</v>
       </c>
       <c r="D393" t="s">
-        <v>1069</v>
+        <v>869</v>
       </c>
       <c r="E393" t="s">
         <v>105</v>
@@ -9795,13 +9790,13 @@
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
-        <v>1070</v>
+        <v>870</v>
       </c>
       <c r="C394" t="s">
-        <v>1071</v>
+        <v>871</v>
       </c>
       <c r="D394" t="s">
-        <v>1071</v>
+        <v>871</v>
       </c>
       <c r="E394" t="s">
         <v>105</v>
@@ -9809,13 +9804,13 @@
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B395" t="s">
-        <v>1072</v>
+        <v>872</v>
       </c>
       <c r="C395" t="s">
-        <v>1073</v>
+        <v>873</v>
       </c>
       <c r="D395" t="s">
-        <v>1073</v>
+        <v>873</v>
       </c>
       <c r="E395" t="s">
         <v>105</v>
@@ -9823,13 +9818,13 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B396" t="s">
-        <v>1074</v>
+        <v>874</v>
       </c>
       <c r="C396" t="s">
-        <v>1075</v>
+        <v>875</v>
       </c>
       <c r="D396" t="s">
-        <v>1075</v>
+        <v>875</v>
       </c>
       <c r="E396" t="s">
         <v>105</v>
@@ -9837,13 +9832,13 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B397" t="s">
-        <v>1076</v>
+        <v>876</v>
       </c>
       <c r="C397" t="s">
-        <v>1077</v>
+        <v>877</v>
       </c>
       <c r="D397" t="s">
-        <v>1077</v>
+        <v>877</v>
       </c>
       <c r="E397" t="s">
         <v>105</v>
@@ -9851,13 +9846,13 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B398" t="s">
-        <v>1078</v>
+        <v>878</v>
       </c>
       <c r="C398" t="s">
-        <v>1079</v>
+        <v>879</v>
       </c>
       <c r="D398" t="s">
-        <v>1079</v>
+        <v>879</v>
       </c>
       <c r="E398" t="s">
         <v>105</v>
@@ -9865,13 +9860,13 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B399" t="s">
-        <v>1080</v>
+        <v>880</v>
       </c>
       <c r="C399" t="s">
-        <v>1081</v>
+        <v>881</v>
       </c>
       <c r="D399" t="s">
-        <v>1081</v>
+        <v>881</v>
       </c>
       <c r="E399" t="s">
         <v>105</v>
@@ -9879,13 +9874,13 @@
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B400" t="s">
-        <v>1082</v>
+        <v>882</v>
       </c>
       <c r="C400" t="s">
-        <v>1083</v>
+        <v>883</v>
       </c>
       <c r="D400" t="s">
-        <v>1083</v>
+        <v>883</v>
       </c>
       <c r="E400" t="s">
         <v>105</v>
@@ -9893,13 +9888,13 @@
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B401" t="s">
-        <v>1084</v>
+        <v>884</v>
       </c>
       <c r="C401" t="s">
-        <v>1085</v>
+        <v>885</v>
       </c>
       <c r="D401" t="s">
-        <v>1085</v>
+        <v>885</v>
       </c>
       <c r="E401" t="s">
         <v>105</v>
@@ -9907,13 +9902,13 @@
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B402" t="s">
-        <v>1086</v>
+        <v>886</v>
       </c>
       <c r="C402" t="s">
-        <v>1087</v>
+        <v>887</v>
       </c>
       <c r="D402" t="s">
-        <v>1087</v>
+        <v>887</v>
       </c>
       <c r="E402" t="s">
         <v>105</v>
@@ -9921,13 +9916,13 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B403" t="s">
-        <v>1088</v>
+        <v>888</v>
       </c>
       <c r="C403" t="s">
-        <v>1089</v>
+        <v>889</v>
       </c>
       <c r="D403" t="s">
-        <v>1089</v>
+        <v>889</v>
       </c>
       <c r="E403" t="s">
         <v>105</v>
@@ -9935,13 +9930,13 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B404" t="s">
-        <v>1090</v>
+        <v>890</v>
       </c>
       <c r="C404" t="s">
-        <v>1091</v>
+        <v>891</v>
       </c>
       <c r="D404" t="s">
-        <v>1091</v>
+        <v>891</v>
       </c>
       <c r="E404" t="s">
         <v>105</v>
@@ -9949,13 +9944,13 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B405" t="s">
-        <v>1092</v>
+        <v>892</v>
       </c>
       <c r="C405" t="s">
-        <v>1093</v>
+        <v>893</v>
       </c>
       <c r="D405" t="s">
-        <v>1093</v>
+        <v>893</v>
       </c>
       <c r="E405" t="s">
         <v>105</v>
@@ -9963,13 +9958,13 @@
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B406" t="s">
-        <v>1094</v>
+        <v>894</v>
       </c>
       <c r="C406" t="s">
-        <v>1095</v>
+        <v>895</v>
       </c>
       <c r="D406" t="s">
-        <v>1095</v>
+        <v>895</v>
       </c>
       <c r="E406" t="s">
         <v>105</v>
@@ -9977,13 +9972,13 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B407" t="s">
-        <v>1096</v>
+        <v>896</v>
       </c>
       <c r="C407" t="s">
-        <v>1097</v>
+        <v>897</v>
       </c>
       <c r="D407" t="s">
-        <v>1097</v>
+        <v>897</v>
       </c>
       <c r="E407" t="s">
         <v>105</v>
@@ -9991,13 +9986,13 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B408" t="s">
-        <v>1098</v>
+        <v>898</v>
       </c>
       <c r="C408" t="s">
-        <v>1099</v>
+        <v>899</v>
       </c>
       <c r="D408" t="s">
-        <v>1099</v>
+        <v>899</v>
       </c>
       <c r="E408" t="s">
         <v>105</v>
@@ -10005,13 +10000,13 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B409" t="s">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="C409" t="s">
-        <v>1101</v>
+        <v>901</v>
       </c>
       <c r="D409" t="s">
-        <v>1101</v>
+        <v>901</v>
       </c>
       <c r="E409" t="s">
         <v>105</v>
@@ -10019,13 +10014,13 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B410" t="s">
-        <v>1102</v>
+        <v>902</v>
       </c>
       <c r="C410" t="s">
-        <v>1103</v>
+        <v>903</v>
       </c>
       <c r="D410" t="s">
-        <v>1103</v>
+        <v>903</v>
       </c>
       <c r="E410" t="s">
         <v>105</v>
@@ -10033,13 +10028,13 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B411" t="s">
-        <v>1104</v>
+        <v>904</v>
       </c>
       <c r="C411" t="s">
-        <v>1105</v>
+        <v>905</v>
       </c>
       <c r="D411" t="s">
-        <v>1105</v>
+        <v>905</v>
       </c>
       <c r="E411" t="s">
         <v>105</v>
@@ -10047,13 +10042,13 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B412" t="s">
-        <v>1106</v>
+        <v>906</v>
       </c>
       <c r="C412" t="s">
-        <v>1107</v>
+        <v>907</v>
       </c>
       <c r="D412" t="s">
-        <v>1107</v>
+        <v>907</v>
       </c>
       <c r="E412" t="s">
         <v>105</v>
@@ -10061,13 +10056,13 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B413" t="s">
-        <v>1108</v>
+        <v>908</v>
       </c>
       <c r="C413" t="s">
-        <v>1109</v>
+        <v>909</v>
       </c>
       <c r="D413" t="s">
-        <v>1109</v>
+        <v>909</v>
       </c>
       <c r="E413" t="s">
         <v>105</v>
@@ -10075,13 +10070,13 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B414" t="s">
-        <v>1110</v>
+        <v>910</v>
       </c>
       <c r="C414" t="s">
-        <v>1111</v>
+        <v>911</v>
       </c>
       <c r="D414" t="s">
-        <v>1111</v>
+        <v>911</v>
       </c>
       <c r="E414" t="s">
         <v>105</v>
@@ -10089,13 +10084,13 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B415" t="s">
-        <v>1112</v>
+        <v>912</v>
       </c>
       <c r="C415" t="s">
-        <v>1113</v>
+        <v>913</v>
       </c>
       <c r="D415" t="s">
-        <v>1113</v>
+        <v>913</v>
       </c>
       <c r="E415" t="s">
         <v>105</v>
@@ -10103,13 +10098,13 @@
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B416" t="s">
-        <v>1114</v>
+        <v>914</v>
       </c>
       <c r="C416" t="s">
-        <v>1115</v>
+        <v>915</v>
       </c>
       <c r="D416" t="s">
-        <v>1115</v>
+        <v>915</v>
       </c>
       <c r="E416" t="s">
         <v>105</v>
@@ -10117,13 +10112,13 @@
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B417" t="s">
-        <v>1116</v>
+        <v>916</v>
       </c>
       <c r="C417" t="s">
-        <v>1117</v>
+        <v>917</v>
       </c>
       <c r="D417" t="s">
-        <v>1117</v>
+        <v>917</v>
       </c>
       <c r="E417" t="s">
         <v>105</v>
@@ -10131,13 +10126,13 @@
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B418" t="s">
-        <v>1118</v>
+        <v>918</v>
       </c>
       <c r="C418" t="s">
-        <v>1119</v>
+        <v>919</v>
       </c>
       <c r="D418" t="s">
-        <v>1119</v>
+        <v>919</v>
       </c>
       <c r="E418" t="s">
         <v>105</v>
@@ -10145,13 +10140,13 @@
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B419" t="s">
-        <v>1120</v>
+        <v>920</v>
       </c>
       <c r="C419" t="s">
-        <v>1121</v>
+        <v>921</v>
       </c>
       <c r="D419" t="s">
-        <v>1121</v>
+        <v>921</v>
       </c>
       <c r="E419" t="s">
         <v>105</v>
@@ -10159,13 +10154,13 @@
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B420" t="s">
-        <v>1122</v>
+        <v>922</v>
       </c>
       <c r="C420" t="s">
-        <v>1123</v>
+        <v>923</v>
       </c>
       <c r="D420" t="s">
-        <v>1123</v>
+        <v>923</v>
       </c>
       <c r="E420" t="s">
         <v>105</v>
@@ -10173,13 +10168,13 @@
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B421" t="s">
-        <v>1124</v>
+        <v>924</v>
       </c>
       <c r="C421" t="s">
-        <v>1125</v>
+        <v>925</v>
       </c>
       <c r="D421" t="s">
-        <v>1125</v>
+        <v>925</v>
       </c>
       <c r="E421" t="s">
         <v>105</v>
@@ -10187,13 +10182,13 @@
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B422" t="s">
-        <v>1126</v>
+        <v>926</v>
       </c>
       <c r="C422" t="s">
-        <v>1127</v>
+        <v>927</v>
       </c>
       <c r="D422" t="s">
-        <v>1127</v>
+        <v>927</v>
       </c>
       <c r="E422" t="s">
         <v>105</v>
@@ -10201,13 +10196,13 @@
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B423" t="s">
-        <v>1128</v>
+        <v>928</v>
       </c>
       <c r="C423" t="s">
-        <v>1129</v>
+        <v>929</v>
       </c>
       <c r="D423" t="s">
-        <v>1129</v>
+        <v>929</v>
       </c>
       <c r="E423" t="s">
         <v>105</v>
@@ -10215,13 +10210,13 @@
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B424" t="s">
-        <v>1130</v>
+        <v>930</v>
       </c>
       <c r="C424" t="s">
-        <v>1131</v>
+        <v>931</v>
       </c>
       <c r="D424" t="s">
-        <v>1131</v>
+        <v>931</v>
       </c>
       <c r="E424" t="s">
         <v>105</v>
@@ -10229,13 +10224,13 @@
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B425" t="s">
-        <v>1132</v>
+        <v>932</v>
       </c>
       <c r="C425" t="s">
-        <v>1133</v>
+        <v>933</v>
       </c>
       <c r="D425" t="s">
-        <v>1133</v>
+        <v>933</v>
       </c>
       <c r="E425" t="s">
         <v>105</v>
@@ -10243,13 +10238,13 @@
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B426" t="s">
-        <v>1134</v>
+        <v>934</v>
       </c>
       <c r="C426" t="s">
-        <v>1135</v>
+        <v>935</v>
       </c>
       <c r="D426" t="s">
-        <v>1135</v>
+        <v>935</v>
       </c>
       <c r="E426" t="s">
         <v>105</v>
@@ -10257,13 +10252,13 @@
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B427" t="s">
-        <v>1136</v>
+        <v>936</v>
       </c>
       <c r="C427" t="s">
-        <v>1137</v>
+        <v>937</v>
       </c>
       <c r="D427" t="s">
-        <v>1137</v>
+        <v>937</v>
       </c>
       <c r="E427" t="s">
         <v>105</v>
@@ -10271,13 +10266,13 @@
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B428" t="s">
-        <v>1138</v>
+        <v>938</v>
       </c>
       <c r="C428" t="s">
-        <v>1139</v>
+        <v>939</v>
       </c>
       <c r="D428" t="s">
-        <v>1139</v>
+        <v>939</v>
       </c>
       <c r="E428" t="s">
         <v>105</v>
@@ -10285,13 +10280,13 @@
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B429" t="s">
-        <v>1140</v>
+        <v>940</v>
       </c>
       <c r="C429" t="s">
-        <v>1141</v>
+        <v>941</v>
       </c>
       <c r="D429" t="s">
-        <v>1141</v>
+        <v>941</v>
       </c>
       <c r="E429" t="s">
         <v>105</v>
@@ -10299,13 +10294,13 @@
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B430" t="s">
-        <v>1142</v>
+        <v>942</v>
       </c>
       <c r="C430" t="s">
-        <v>1143</v>
+        <v>943</v>
       </c>
       <c r="D430" t="s">
-        <v>1143</v>
+        <v>943</v>
       </c>
       <c r="E430" t="s">
         <v>105</v>
@@ -10313,13 +10308,13 @@
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B431" t="s">
-        <v>1144</v>
+        <v>944</v>
       </c>
       <c r="C431" t="s">
-        <v>1145</v>
+        <v>945</v>
       </c>
       <c r="D431" t="s">
-        <v>1145</v>
+        <v>945</v>
       </c>
       <c r="E431" t="s">
         <v>105</v>
@@ -10327,13 +10322,13 @@
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B432" t="s">
-        <v>1146</v>
+        <v>946</v>
       </c>
       <c r="C432" t="s">
-        <v>1147</v>
+        <v>947</v>
       </c>
       <c r="D432" t="s">
-        <v>1147</v>
+        <v>947</v>
       </c>
       <c r="E432" t="s">
         <v>105</v>
@@ -10341,13 +10336,13 @@
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B433" t="s">
-        <v>1148</v>
+        <v>948</v>
       </c>
       <c r="C433" t="s">
-        <v>1149</v>
+        <v>949</v>
       </c>
       <c r="D433" t="s">
-        <v>1149</v>
+        <v>949</v>
       </c>
       <c r="E433" t="s">
         <v>105</v>
@@ -10355,13 +10350,13 @@
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B434" t="s">
-        <v>1150</v>
+        <v>950</v>
       </c>
       <c r="C434" t="s">
-        <v>1151</v>
+        <v>951</v>
       </c>
       <c r="D434" t="s">
-        <v>1151</v>
+        <v>951</v>
       </c>
       <c r="E434" t="s">
         <v>105</v>
@@ -10369,13 +10364,13 @@
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B435" t="s">
-        <v>1152</v>
+        <v>952</v>
       </c>
       <c r="C435" t="s">
-        <v>1153</v>
+        <v>953</v>
       </c>
       <c r="D435" t="s">
-        <v>1153</v>
+        <v>953</v>
       </c>
       <c r="E435" t="s">
         <v>105</v>
@@ -10383,13 +10378,13 @@
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B436" t="s">
-        <v>1154</v>
+        <v>954</v>
       </c>
       <c r="C436" t="s">
-        <v>1155</v>
+        <v>955</v>
       </c>
       <c r="D436" t="s">
-        <v>1155</v>
+        <v>955</v>
       </c>
       <c r="E436" t="s">
         <v>105</v>
@@ -10397,13 +10392,13 @@
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B437" t="s">
-        <v>1156</v>
+        <v>956</v>
       </c>
       <c r="C437" t="s">
-        <v>1157</v>
+        <v>957</v>
       </c>
       <c r="D437" t="s">
-        <v>1157</v>
+        <v>957</v>
       </c>
       <c r="E437" t="s">
         <v>105</v>
@@ -10411,13 +10406,13 @@
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B438" t="s">
-        <v>1158</v>
+        <v>958</v>
       </c>
       <c r="C438" t="s">
-        <v>1159</v>
+        <v>959</v>
       </c>
       <c r="D438" t="s">
-        <v>1159</v>
+        <v>959</v>
       </c>
       <c r="E438" t="s">
         <v>105</v>
@@ -10425,13 +10420,13 @@
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B439" t="s">
-        <v>1160</v>
+        <v>960</v>
       </c>
       <c r="C439" t="s">
-        <v>1161</v>
+        <v>961</v>
       </c>
       <c r="D439" t="s">
-        <v>1161</v>
+        <v>961</v>
       </c>
       <c r="E439" t="s">
         <v>105</v>
@@ -10439,13 +10434,13 @@
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B440" t="s">
-        <v>1162</v>
+        <v>962</v>
       </c>
       <c r="C440" t="s">
-        <v>1163</v>
+        <v>963</v>
       </c>
       <c r="D440" t="s">
-        <v>1163</v>
+        <v>963</v>
       </c>
       <c r="E440" t="s">
         <v>105</v>
@@ -10453,13 +10448,13 @@
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B441" t="s">
-        <v>1164</v>
+        <v>964</v>
       </c>
       <c r="C441" t="s">
-        <v>1165</v>
+        <v>965</v>
       </c>
       <c r="D441" t="s">
-        <v>1165</v>
+        <v>965</v>
       </c>
       <c r="E441" t="s">
         <v>105</v>
@@ -10467,13 +10462,13 @@
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B442" t="s">
-        <v>1166</v>
+        <v>966</v>
       </c>
       <c r="C442" t="s">
-        <v>1167</v>
+        <v>967</v>
       </c>
       <c r="D442" t="s">
-        <v>1167</v>
+        <v>967</v>
       </c>
       <c r="E442" t="s">
         <v>105</v>
@@ -10481,13 +10476,13 @@
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B443" t="s">
-        <v>1168</v>
+        <v>968</v>
       </c>
       <c r="C443" t="s">
-        <v>1169</v>
+        <v>969</v>
       </c>
       <c r="D443" t="s">
-        <v>1169</v>
+        <v>969</v>
       </c>
       <c r="E443" t="s">
         <v>105</v>
@@ -10495,13 +10490,13 @@
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B444" t="s">
-        <v>1170</v>
+        <v>970</v>
       </c>
       <c r="C444" t="s">
-        <v>1171</v>
+        <v>971</v>
       </c>
       <c r="D444" t="s">
-        <v>1171</v>
+        <v>971</v>
       </c>
       <c r="E444" t="s">
         <v>105</v>
@@ -10509,13 +10504,13 @@
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B445" t="s">
-        <v>1172</v>
+        <v>972</v>
       </c>
       <c r="C445" t="s">
-        <v>1173</v>
+        <v>973</v>
       </c>
       <c r="D445" t="s">
-        <v>1173</v>
+        <v>973</v>
       </c>
       <c r="E445" t="s">
         <v>105</v>
@@ -10523,13 +10518,13 @@
     </row>
     <row r="446" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B446" t="s">
-        <v>1174</v>
+        <v>974</v>
       </c>
       <c r="C446" t="s">
-        <v>1175</v>
+        <v>975</v>
       </c>
       <c r="D446" t="s">
-        <v>1175</v>
+        <v>975</v>
       </c>
       <c r="E446" t="s">
         <v>105</v>
@@ -10537,13 +10532,13 @@
     </row>
     <row r="447" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B447" t="s">
-        <v>746</v>
+        <v>976</v>
       </c>
       <c r="C447" t="s">
-        <v>747</v>
+        <v>977</v>
       </c>
       <c r="D447" t="s">
-        <v>747</v>
+        <v>977</v>
       </c>
       <c r="E447" t="s">
         <v>105</v>
@@ -10551,13 +10546,13 @@
     </row>
     <row r="448" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B448" t="s">
-        <v>748</v>
+        <v>978</v>
       </c>
       <c r="C448" t="s">
-        <v>749</v>
+        <v>979</v>
       </c>
       <c r="D448" t="s">
-        <v>749</v>
+        <v>979</v>
       </c>
       <c r="E448" t="s">
         <v>105</v>
@@ -10565,13 +10560,13 @@
     </row>
     <row r="449" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B449" t="s">
-        <v>750</v>
+        <v>980</v>
       </c>
       <c r="C449" t="s">
-        <v>751</v>
+        <v>981</v>
       </c>
       <c r="D449" t="s">
-        <v>751</v>
+        <v>981</v>
       </c>
       <c r="E449" t="s">
         <v>105</v>
@@ -10579,13 +10574,13 @@
     </row>
     <row r="450" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B450" t="s">
-        <v>752</v>
+        <v>982</v>
       </c>
       <c r="C450" t="s">
-        <v>753</v>
+        <v>983</v>
       </c>
       <c r="D450" t="s">
-        <v>753</v>
+        <v>983</v>
       </c>
       <c r="E450" t="s">
         <v>105</v>
@@ -10593,13 +10588,13 @@
     </row>
     <row r="451" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B451" t="s">
-        <v>754</v>
+        <v>984</v>
       </c>
       <c r="C451" t="s">
-        <v>755</v>
+        <v>985</v>
       </c>
       <c r="D451" t="s">
-        <v>755</v>
+        <v>985</v>
       </c>
       <c r="E451" t="s">
         <v>105</v>
@@ -10607,13 +10602,13 @@
     </row>
     <row r="452" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B452" t="s">
-        <v>756</v>
+        <v>986</v>
       </c>
       <c r="C452" t="s">
-        <v>757</v>
+        <v>987</v>
       </c>
       <c r="D452" t="s">
-        <v>757</v>
+        <v>987</v>
       </c>
       <c r="E452" t="s">
         <v>105</v>
@@ -10621,13 +10616,13 @@
     </row>
     <row r="453" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B453" t="s">
-        <v>758</v>
+        <v>988</v>
       </c>
       <c r="C453" t="s">
-        <v>759</v>
+        <v>989</v>
       </c>
       <c r="D453" t="s">
-        <v>759</v>
+        <v>989</v>
       </c>
       <c r="E453" t="s">
         <v>105</v>
@@ -10635,13 +10630,13 @@
     </row>
     <row r="454" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B454" t="s">
-        <v>760</v>
+        <v>990</v>
       </c>
       <c r="C454" t="s">
-        <v>761</v>
+        <v>991</v>
       </c>
       <c r="D454" t="s">
-        <v>761</v>
+        <v>991</v>
       </c>
       <c r="E454" t="s">
         <v>105</v>
@@ -10649,13 +10644,13 @@
     </row>
     <row r="455" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B455" t="s">
-        <v>762</v>
+        <v>992</v>
       </c>
       <c r="C455" t="s">
-        <v>763</v>
+        <v>993</v>
       </c>
       <c r="D455" t="s">
-        <v>763</v>
+        <v>993</v>
       </c>
       <c r="E455" t="s">
         <v>105</v>
@@ -10663,13 +10658,13 @@
     </row>
     <row r="456" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B456" t="s">
-        <v>764</v>
+        <v>994</v>
       </c>
       <c r="C456" t="s">
-        <v>765</v>
+        <v>995</v>
       </c>
       <c r="D456" t="s">
-        <v>765</v>
+        <v>995</v>
       </c>
       <c r="E456" t="s">
         <v>105</v>
@@ -10677,13 +10672,13 @@
     </row>
     <row r="457" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B457" t="s">
-        <v>766</v>
+        <v>996</v>
       </c>
       <c r="C457" t="s">
-        <v>767</v>
+        <v>997</v>
       </c>
       <c r="D457" t="s">
-        <v>767</v>
+        <v>997</v>
       </c>
       <c r="E457" t="s">
         <v>105</v>
@@ -10691,13 +10686,13 @@
     </row>
     <row r="458" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B458" t="s">
-        <v>768</v>
+        <v>998</v>
       </c>
       <c r="C458" t="s">
-        <v>769</v>
+        <v>999</v>
       </c>
       <c r="D458" t="s">
-        <v>769</v>
+        <v>999</v>
       </c>
       <c r="E458" t="s">
         <v>105</v>
@@ -10705,13 +10700,13 @@
     </row>
     <row r="459" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B459" t="s">
-        <v>770</v>
+        <v>1000</v>
       </c>
       <c r="C459" t="s">
-        <v>771</v>
+        <v>1001</v>
       </c>
       <c r="D459" t="s">
-        <v>771</v>
+        <v>1001</v>
       </c>
       <c r="E459" t="s">
         <v>105</v>
@@ -10719,13 +10714,13 @@
     </row>
     <row r="460" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B460" t="s">
-        <v>772</v>
+        <v>1002</v>
       </c>
       <c r="C460" t="s">
-        <v>773</v>
+        <v>1003</v>
       </c>
       <c r="D460" t="s">
-        <v>773</v>
+        <v>1003</v>
       </c>
       <c r="E460" t="s">
         <v>105</v>
@@ -10733,13 +10728,13 @@
     </row>
     <row r="461" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B461" t="s">
-        <v>774</v>
+        <v>1004</v>
       </c>
       <c r="C461" t="s">
-        <v>775</v>
+        <v>1005</v>
       </c>
       <c r="D461" t="s">
-        <v>775</v>
+        <v>1005</v>
       </c>
       <c r="E461" t="s">
         <v>105</v>
@@ -10747,13 +10742,13 @@
     </row>
     <row r="462" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B462" t="s">
-        <v>776</v>
+        <v>1006</v>
       </c>
       <c r="C462" t="s">
-        <v>777</v>
+        <v>1007</v>
       </c>
       <c r="D462" t="s">
-        <v>777</v>
+        <v>1007</v>
       </c>
       <c r="E462" t="s">
         <v>105</v>
@@ -10761,13 +10756,13 @@
     </row>
     <row r="463" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B463" t="s">
-        <v>778</v>
+        <v>1008</v>
       </c>
       <c r="C463" t="s">
-        <v>779</v>
+        <v>1009</v>
       </c>
       <c r="D463" t="s">
-        <v>779</v>
+        <v>1009</v>
       </c>
       <c r="E463" t="s">
         <v>105</v>
@@ -10775,13 +10770,13 @@
     </row>
     <row r="464" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B464" t="s">
-        <v>780</v>
+        <v>1010</v>
       </c>
       <c r="C464" t="s">
-        <v>781</v>
+        <v>1011</v>
       </c>
       <c r="D464" t="s">
-        <v>781</v>
+        <v>1011</v>
       </c>
       <c r="E464" t="s">
         <v>105</v>
@@ -10789,13 +10784,13 @@
     </row>
     <row r="465" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B465" t="s">
-        <v>782</v>
+        <v>1012</v>
       </c>
       <c r="C465" t="s">
-        <v>783</v>
+        <v>1013</v>
       </c>
       <c r="D465" t="s">
-        <v>783</v>
+        <v>1013</v>
       </c>
       <c r="E465" t="s">
         <v>105</v>
@@ -10803,13 +10798,13 @@
     </row>
     <row r="466" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B466" t="s">
-        <v>784</v>
+        <v>1014</v>
       </c>
       <c r="C466" t="s">
-        <v>785</v>
+        <v>1015</v>
       </c>
       <c r="D466" t="s">
-        <v>785</v>
+        <v>1015</v>
       </c>
       <c r="E466" t="s">
         <v>105</v>
@@ -10817,13 +10812,13 @@
     </row>
     <row r="467" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B467" t="s">
-        <v>786</v>
+        <v>1016</v>
       </c>
       <c r="C467" t="s">
-        <v>787</v>
+        <v>1017</v>
       </c>
       <c r="D467" t="s">
-        <v>787</v>
+        <v>1017</v>
       </c>
       <c r="E467" t="s">
         <v>105</v>
@@ -10831,13 +10826,13 @@
     </row>
     <row r="468" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B468" t="s">
-        <v>788</v>
+        <v>1018</v>
       </c>
       <c r="C468" t="s">
-        <v>789</v>
+        <v>1019</v>
       </c>
       <c r="D468" t="s">
-        <v>789</v>
+        <v>1019</v>
       </c>
       <c r="E468" t="s">
         <v>105</v>
@@ -10845,13 +10840,13 @@
     </row>
     <row r="469" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B469" t="s">
-        <v>790</v>
+        <v>1020</v>
       </c>
       <c r="C469" t="s">
-        <v>791</v>
+        <v>1021</v>
       </c>
       <c r="D469" t="s">
-        <v>791</v>
+        <v>1021</v>
       </c>
       <c r="E469" t="s">
         <v>105</v>
@@ -10859,13 +10854,13 @@
     </row>
     <row r="470" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B470" t="s">
-        <v>792</v>
+        <v>1022</v>
       </c>
       <c r="C470" t="s">
-        <v>793</v>
+        <v>1023</v>
       </c>
       <c r="D470" t="s">
-        <v>793</v>
+        <v>1023</v>
       </c>
       <c r="E470" t="s">
         <v>105</v>
@@ -10873,13 +10868,13 @@
     </row>
     <row r="471" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B471" t="s">
-        <v>794</v>
+        <v>1024</v>
       </c>
       <c r="C471" t="s">
-        <v>795</v>
+        <v>1025</v>
       </c>
       <c r="D471" t="s">
-        <v>795</v>
+        <v>1025</v>
       </c>
       <c r="E471" t="s">
         <v>105</v>
@@ -10887,13 +10882,13 @@
     </row>
     <row r="472" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B472" t="s">
-        <v>796</v>
+        <v>1026</v>
       </c>
       <c r="C472" t="s">
-        <v>797</v>
+        <v>1027</v>
       </c>
       <c r="D472" t="s">
-        <v>797</v>
+        <v>1027</v>
       </c>
       <c r="E472" t="s">
         <v>105</v>
@@ -10901,13 +10896,13 @@
     </row>
     <row r="473" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B473" t="s">
-        <v>798</v>
+        <v>1028</v>
       </c>
       <c r="C473" t="s">
-        <v>799</v>
+        <v>1029</v>
       </c>
       <c r="D473" t="s">
-        <v>799</v>
+        <v>1029</v>
       </c>
       <c r="E473" t="s">
         <v>105</v>
@@ -10915,13 +10910,13 @@
     </row>
     <row r="474" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B474" t="s">
-        <v>800</v>
+        <v>1030</v>
       </c>
       <c r="C474" t="s">
-        <v>801</v>
+        <v>1031</v>
       </c>
       <c r="D474" t="s">
-        <v>801</v>
+        <v>1031</v>
       </c>
       <c r="E474" t="s">
         <v>105</v>
@@ -10929,13 +10924,13 @@
     </row>
     <row r="475" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B475" t="s">
-        <v>802</v>
+        <v>1032</v>
       </c>
       <c r="C475" t="s">
-        <v>803</v>
+        <v>1033</v>
       </c>
       <c r="D475" t="s">
-        <v>803</v>
+        <v>1033</v>
       </c>
       <c r="E475" t="s">
         <v>105</v>
@@ -10943,13 +10938,13 @@
     </row>
     <row r="476" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B476" t="s">
-        <v>804</v>
+        <v>1034</v>
       </c>
       <c r="C476" t="s">
-        <v>805</v>
+        <v>1035</v>
       </c>
       <c r="D476" t="s">
-        <v>805</v>
+        <v>1035</v>
       </c>
       <c r="E476" t="s">
         <v>105</v>
@@ -10957,13 +10952,13 @@
     </row>
     <row r="477" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B477" t="s">
-        <v>806</v>
+        <v>1036</v>
       </c>
       <c r="C477" t="s">
-        <v>807</v>
+        <v>1037</v>
       </c>
       <c r="D477" t="s">
-        <v>807</v>
+        <v>1037</v>
       </c>
       <c r="E477" t="s">
         <v>105</v>
@@ -10971,13 +10966,13 @@
     </row>
     <row r="478" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B478" t="s">
-        <v>808</v>
+        <v>1038</v>
       </c>
       <c r="C478" t="s">
-        <v>809</v>
+        <v>1039</v>
       </c>
       <c r="D478" t="s">
-        <v>809</v>
+        <v>1039</v>
       </c>
       <c r="E478" t="s">
         <v>105</v>
@@ -10985,13 +10980,13 @@
     </row>
     <row r="479" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B479" t="s">
-        <v>810</v>
+        <v>1040</v>
       </c>
       <c r="C479" t="s">
-        <v>811</v>
+        <v>1041</v>
       </c>
       <c r="D479" t="s">
-        <v>811</v>
+        <v>1041</v>
       </c>
       <c r="E479" t="s">
         <v>105</v>
@@ -10999,13 +10994,13 @@
     </row>
     <row r="480" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B480" t="s">
-        <v>812</v>
+        <v>1042</v>
       </c>
       <c r="C480" t="s">
-        <v>813</v>
+        <v>1043</v>
       </c>
       <c r="D480" t="s">
-        <v>813</v>
+        <v>1043</v>
       </c>
       <c r="E480" t="s">
         <v>105</v>
@@ -11013,13 +11008,13 @@
     </row>
     <row r="481" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B481" t="s">
-        <v>814</v>
+        <v>1044</v>
       </c>
       <c r="C481" t="s">
-        <v>815</v>
+        <v>1045</v>
       </c>
       <c r="D481" t="s">
-        <v>815</v>
+        <v>1045</v>
       </c>
       <c r="E481" t="s">
         <v>105</v>
@@ -11027,13 +11022,13 @@
     </row>
     <row r="482" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B482" t="s">
-        <v>816</v>
+        <v>1046</v>
       </c>
       <c r="C482" t="s">
-        <v>817</v>
+        <v>1047</v>
       </c>
       <c r="D482" t="s">
-        <v>817</v>
+        <v>1047</v>
       </c>
       <c r="E482" t="s">
         <v>105</v>
@@ -11041,13 +11036,13 @@
     </row>
     <row r="483" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B483" t="s">
-        <v>818</v>
+        <v>1048</v>
       </c>
       <c r="C483" t="s">
-        <v>819</v>
+        <v>1049</v>
       </c>
       <c r="D483" t="s">
-        <v>819</v>
+        <v>1049</v>
       </c>
       <c r="E483" t="s">
         <v>105</v>
@@ -11055,13 +11050,13 @@
     </row>
     <row r="484" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B484" t="s">
-        <v>820</v>
+        <v>1050</v>
       </c>
       <c r="C484" t="s">
-        <v>821</v>
+        <v>1051</v>
       </c>
       <c r="D484" t="s">
-        <v>821</v>
+        <v>1051</v>
       </c>
       <c r="E484" t="s">
         <v>105</v>
@@ -11069,13 +11064,13 @@
     </row>
     <row r="485" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B485" t="s">
-        <v>822</v>
+        <v>1052</v>
       </c>
       <c r="C485" t="s">
-        <v>823</v>
+        <v>1053</v>
       </c>
       <c r="D485" t="s">
-        <v>823</v>
+        <v>1053</v>
       </c>
       <c r="E485" t="s">
         <v>105</v>
@@ -11083,13 +11078,13 @@
     </row>
     <row r="486" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B486" t="s">
-        <v>824</v>
+        <v>1054</v>
       </c>
       <c r="C486" t="s">
-        <v>825</v>
+        <v>1055</v>
       </c>
       <c r="D486" t="s">
-        <v>825</v>
+        <v>1055</v>
       </c>
       <c r="E486" t="s">
         <v>105</v>
@@ -11097,13 +11092,13 @@
     </row>
     <row r="487" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B487" t="s">
-        <v>826</v>
+        <v>1056</v>
       </c>
       <c r="C487" t="s">
-        <v>827</v>
+        <v>1057</v>
       </c>
       <c r="D487" t="s">
-        <v>827</v>
+        <v>1057</v>
       </c>
       <c r="E487" t="s">
         <v>105</v>
@@ -11111,13 +11106,13 @@
     </row>
     <row r="488" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B488" t="s">
-        <v>828</v>
+        <v>1058</v>
       </c>
       <c r="C488" t="s">
-        <v>829</v>
+        <v>1059</v>
       </c>
       <c r="D488" t="s">
-        <v>829</v>
+        <v>1059</v>
       </c>
       <c r="E488" t="s">
         <v>105</v>
@@ -11125,13 +11120,13 @@
     </row>
     <row r="489" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B489" t="s">
-        <v>830</v>
+        <v>1060</v>
       </c>
       <c r="C489" t="s">
-        <v>831</v>
+        <v>1061</v>
       </c>
       <c r="D489" t="s">
-        <v>831</v>
+        <v>1061</v>
       </c>
       <c r="E489" t="s">
         <v>105</v>
@@ -11139,13 +11134,13 @@
     </row>
     <row r="490" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B490" t="s">
-        <v>832</v>
+        <v>1062</v>
       </c>
       <c r="C490" t="s">
-        <v>833</v>
+        <v>1063</v>
       </c>
       <c r="D490" t="s">
-        <v>833</v>
+        <v>1063</v>
       </c>
       <c r="E490" t="s">
         <v>105</v>
@@ -11153,13 +11148,13 @@
     </row>
     <row r="491" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B491" t="s">
-        <v>834</v>
+        <v>1064</v>
       </c>
       <c r="C491" t="s">
-        <v>835</v>
+        <v>1065</v>
       </c>
       <c r="D491" t="s">
-        <v>835</v>
+        <v>1065</v>
       </c>
       <c r="E491" t="s">
         <v>105</v>
@@ -11167,13 +11162,13 @@
     </row>
     <row r="492" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B492" t="s">
-        <v>836</v>
+        <v>1066</v>
       </c>
       <c r="C492" t="s">
-        <v>837</v>
+        <v>1067</v>
       </c>
       <c r="D492" t="s">
-        <v>837</v>
+        <v>1067</v>
       </c>
       <c r="E492" t="s">
         <v>105</v>
@@ -11181,13 +11176,13 @@
     </row>
     <row r="493" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B493" t="s">
-        <v>838</v>
+        <v>1068</v>
       </c>
       <c r="C493" t="s">
-        <v>839</v>
+        <v>1069</v>
       </c>
       <c r="D493" t="s">
-        <v>839</v>
+        <v>1069</v>
       </c>
       <c r="E493" t="s">
         <v>105</v>
@@ -11195,13 +11190,13 @@
     </row>
     <row r="494" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B494" t="s">
-        <v>840</v>
+        <v>1070</v>
       </c>
       <c r="C494" t="s">
-        <v>841</v>
+        <v>1071</v>
       </c>
       <c r="D494" t="s">
-        <v>841</v>
+        <v>1071</v>
       </c>
       <c r="E494" t="s">
         <v>105</v>
@@ -11209,13 +11204,13 @@
     </row>
     <row r="495" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B495" t="s">
-        <v>842</v>
+        <v>1072</v>
       </c>
       <c r="C495" t="s">
-        <v>843</v>
+        <v>1073</v>
       </c>
       <c r="D495" t="s">
-        <v>843</v>
+        <v>1073</v>
       </c>
       <c r="E495" t="s">
         <v>105</v>
@@ -11223,13 +11218,13 @@
     </row>
     <row r="496" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B496" t="s">
-        <v>844</v>
+        <v>1074</v>
       </c>
       <c r="C496" t="s">
-        <v>845</v>
+        <v>1075</v>
       </c>
       <c r="D496" t="s">
-        <v>845</v>
+        <v>1075</v>
       </c>
       <c r="E496" t="s">
         <v>105</v>
@@ -11237,13 +11232,13 @@
     </row>
     <row r="497" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B497" t="s">
-        <v>846</v>
+        <v>1076</v>
       </c>
       <c r="C497" t="s">
-        <v>847</v>
+        <v>1077</v>
       </c>
       <c r="D497" t="s">
-        <v>847</v>
+        <v>1077</v>
       </c>
       <c r="E497" t="s">
         <v>105</v>
@@ -11251,13 +11246,13 @@
     </row>
     <row r="498" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B498" t="s">
-        <v>848</v>
+        <v>1078</v>
       </c>
       <c r="C498" t="s">
-        <v>849</v>
+        <v>1079</v>
       </c>
       <c r="D498" t="s">
-        <v>849</v>
+        <v>1079</v>
       </c>
       <c r="E498" t="s">
         <v>105</v>
@@ -11265,13 +11260,13 @@
     </row>
     <row r="499" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B499" t="s">
-        <v>850</v>
+        <v>1080</v>
       </c>
       <c r="C499" t="s">
-        <v>851</v>
+        <v>1081</v>
       </c>
       <c r="D499" t="s">
-        <v>851</v>
+        <v>1081</v>
       </c>
       <c r="E499" t="s">
         <v>105</v>
@@ -11279,13 +11274,13 @@
     </row>
     <row r="500" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B500" t="s">
-        <v>852</v>
+        <v>1082</v>
       </c>
       <c r="C500" t="s">
-        <v>853</v>
+        <v>1083</v>
       </c>
       <c r="D500" t="s">
-        <v>853</v>
+        <v>1083</v>
       </c>
       <c r="E500" t="s">
         <v>105</v>
@@ -11293,13 +11288,13 @@
     </row>
     <row r="501" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B501" t="s">
-        <v>854</v>
+        <v>1084</v>
       </c>
       <c r="C501" t="s">
-        <v>855</v>
+        <v>1085</v>
       </c>
       <c r="D501" t="s">
-        <v>855</v>
+        <v>1085</v>
       </c>
       <c r="E501" t="s">
         <v>105</v>
@@ -11307,13 +11302,13 @@
     </row>
     <row r="502" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B502" t="s">
-        <v>856</v>
+        <v>1086</v>
       </c>
       <c r="C502" t="s">
-        <v>857</v>
+        <v>1087</v>
       </c>
       <c r="D502" t="s">
-        <v>857</v>
+        <v>1087</v>
       </c>
       <c r="E502" t="s">
         <v>105</v>
@@ -11321,13 +11316,13 @@
     </row>
     <row r="503" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B503" t="s">
-        <v>858</v>
+        <v>1088</v>
       </c>
       <c r="C503" t="s">
-        <v>859</v>
+        <v>1089</v>
       </c>
       <c r="D503" t="s">
-        <v>859</v>
+        <v>1089</v>
       </c>
       <c r="E503" t="s">
         <v>105</v>
@@ -11335,13 +11330,13 @@
     </row>
     <row r="504" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B504" t="s">
-        <v>860</v>
+        <v>1090</v>
       </c>
       <c r="C504" t="s">
-        <v>861</v>
+        <v>1091</v>
       </c>
       <c r="D504" t="s">
-        <v>861</v>
+        <v>1091</v>
       </c>
       <c r="E504" t="s">
         <v>105</v>
@@ -11349,13 +11344,13 @@
     </row>
     <row r="505" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B505" t="s">
-        <v>862</v>
+        <v>1092</v>
       </c>
       <c r="C505" t="s">
-        <v>863</v>
+        <v>1093</v>
       </c>
       <c r="D505" t="s">
-        <v>863</v>
+        <v>1093</v>
       </c>
       <c r="E505" t="s">
         <v>105</v>
@@ -11363,13 +11358,13 @@
     </row>
     <row r="506" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B506" t="s">
-        <v>864</v>
+        <v>1094</v>
       </c>
       <c r="C506" t="s">
-        <v>865</v>
+        <v>1095</v>
       </c>
       <c r="D506" t="s">
-        <v>865</v>
+        <v>1095</v>
       </c>
       <c r="E506" t="s">
         <v>105</v>
@@ -11377,13 +11372,13 @@
     </row>
     <row r="507" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B507" t="s">
-        <v>866</v>
+        <v>1096</v>
       </c>
       <c r="C507" t="s">
-        <v>867</v>
+        <v>1097</v>
       </c>
       <c r="D507" t="s">
-        <v>867</v>
+        <v>1097</v>
       </c>
       <c r="E507" t="s">
         <v>105</v>
@@ -11391,13 +11386,13 @@
     </row>
     <row r="508" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B508" t="s">
-        <v>868</v>
+        <v>1098</v>
       </c>
       <c r="C508" t="s">
-        <v>869</v>
+        <v>1099</v>
       </c>
       <c r="D508" t="s">
-        <v>869</v>
+        <v>1099</v>
       </c>
       <c r="E508" t="s">
         <v>105</v>
@@ -11405,13 +11400,13 @@
     </row>
     <row r="509" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B509" t="s">
-        <v>870</v>
+        <v>1100</v>
       </c>
       <c r="C509" t="s">
-        <v>871</v>
+        <v>1101</v>
       </c>
       <c r="D509" t="s">
-        <v>871</v>
+        <v>1101</v>
       </c>
       <c r="E509" t="s">
         <v>105</v>
@@ -11419,13 +11414,13 @@
     </row>
     <row r="510" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B510" t="s">
-        <v>872</v>
+        <v>1102</v>
       </c>
       <c r="C510" t="s">
-        <v>873</v>
+        <v>1103</v>
       </c>
       <c r="D510" t="s">
-        <v>873</v>
+        <v>1103</v>
       </c>
       <c r="E510" t="s">
         <v>105</v>
@@ -11433,13 +11428,13 @@
     </row>
     <row r="511" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B511" t="s">
-        <v>874</v>
+        <v>1104</v>
       </c>
       <c r="C511" t="s">
-        <v>875</v>
+        <v>1105</v>
       </c>
       <c r="D511" t="s">
-        <v>875</v>
+        <v>1105</v>
       </c>
       <c r="E511" t="s">
         <v>105</v>
@@ -11447,13 +11442,13 @@
     </row>
     <row r="512" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B512" t="s">
-        <v>876</v>
+        <v>1106</v>
       </c>
       <c r="C512" t="s">
-        <v>877</v>
+        <v>1107</v>
       </c>
       <c r="D512" t="s">
-        <v>877</v>
+        <v>1107</v>
       </c>
       <c r="E512" t="s">
         <v>105</v>
@@ -11461,13 +11456,13 @@
     </row>
     <row r="513" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B513" t="s">
-        <v>878</v>
+        <v>1108</v>
       </c>
       <c r="C513" t="s">
-        <v>879</v>
+        <v>1109</v>
       </c>
       <c r="D513" t="s">
-        <v>879</v>
+        <v>1109</v>
       </c>
       <c r="E513" t="s">
         <v>105</v>
@@ -11475,13 +11470,13 @@
     </row>
     <row r="514" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B514" t="s">
-        <v>880</v>
+        <v>1110</v>
       </c>
       <c r="C514" t="s">
-        <v>881</v>
+        <v>1111</v>
       </c>
       <c r="D514" t="s">
-        <v>881</v>
+        <v>1111</v>
       </c>
       <c r="E514" t="s">
         <v>105</v>
@@ -11489,13 +11484,13 @@
     </row>
     <row r="515" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B515" t="s">
-        <v>882</v>
+        <v>1112</v>
       </c>
       <c r="C515" t="s">
-        <v>883</v>
+        <v>1113</v>
       </c>
       <c r="D515" t="s">
-        <v>883</v>
+        <v>1113</v>
       </c>
       <c r="E515" t="s">
         <v>105</v>
@@ -11503,13 +11498,13 @@
     </row>
     <row r="516" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B516" t="s">
-        <v>884</v>
+        <v>1114</v>
       </c>
       <c r="C516" t="s">
-        <v>885</v>
+        <v>1115</v>
       </c>
       <c r="D516" t="s">
-        <v>885</v>
+        <v>1115</v>
       </c>
       <c r="E516" t="s">
         <v>105</v>
@@ -11517,13 +11512,13 @@
     </row>
     <row r="517" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B517" t="s">
-        <v>886</v>
+        <v>1116</v>
       </c>
       <c r="C517" t="s">
-        <v>887</v>
+        <v>1117</v>
       </c>
       <c r="D517" t="s">
-        <v>887</v>
+        <v>1117</v>
       </c>
       <c r="E517" t="s">
         <v>105</v>
@@ -11531,13 +11526,13 @@
     </row>
     <row r="518" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B518" t="s">
-        <v>888</v>
+        <v>1118</v>
       </c>
       <c r="C518" t="s">
-        <v>889</v>
+        <v>1119</v>
       </c>
       <c r="D518" t="s">
-        <v>889</v>
+        <v>1119</v>
       </c>
       <c r="E518" t="s">
         <v>105</v>
@@ -11545,13 +11540,13 @@
     </row>
     <row r="519" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B519" t="s">
-        <v>890</v>
+        <v>1120</v>
       </c>
       <c r="C519" t="s">
-        <v>891</v>
+        <v>1121</v>
       </c>
       <c r="D519" t="s">
-        <v>891</v>
+        <v>1121</v>
       </c>
       <c r="E519" t="s">
         <v>105</v>
@@ -11559,13 +11554,13 @@
     </row>
     <row r="520" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B520" t="s">
-        <v>892</v>
+        <v>1122</v>
       </c>
       <c r="C520" t="s">
-        <v>893</v>
+        <v>1123</v>
       </c>
       <c r="D520" t="s">
-        <v>893</v>
+        <v>1123</v>
       </c>
       <c r="E520" t="s">
         <v>105</v>
@@ -11573,13 +11568,13 @@
     </row>
     <row r="521" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B521" t="s">
-        <v>894</v>
+        <v>1124</v>
       </c>
       <c r="C521" t="s">
-        <v>895</v>
+        <v>1125</v>
       </c>
       <c r="D521" t="s">
-        <v>895</v>
+        <v>1125</v>
       </c>
       <c r="E521" t="s">
         <v>105</v>
@@ -11587,13 +11582,13 @@
     </row>
     <row r="522" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B522" t="s">
-        <v>896</v>
+        <v>1126</v>
       </c>
       <c r="C522" t="s">
-        <v>897</v>
+        <v>1127</v>
       </c>
       <c r="D522" t="s">
-        <v>897</v>
+        <v>1127</v>
       </c>
       <c r="E522" t="s">
         <v>105</v>
@@ -11601,13 +11596,13 @@
     </row>
     <row r="523" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B523" t="s">
-        <v>898</v>
+        <v>1128</v>
       </c>
       <c r="C523" t="s">
-        <v>899</v>
+        <v>1129</v>
       </c>
       <c r="D523" t="s">
-        <v>899</v>
+        <v>1129</v>
       </c>
       <c r="E523" t="s">
         <v>105</v>
@@ -11615,13 +11610,13 @@
     </row>
     <row r="524" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B524" t="s">
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="C524" t="s">
-        <v>901</v>
+        <v>1131</v>
       </c>
       <c r="D524" t="s">
-        <v>901</v>
+        <v>1131</v>
       </c>
       <c r="E524" t="s">
         <v>105</v>
@@ -11629,13 +11624,13 @@
     </row>
     <row r="525" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B525" t="s">
-        <v>902</v>
+        <v>1132</v>
       </c>
       <c r="C525" t="s">
-        <v>903</v>
+        <v>1133</v>
       </c>
       <c r="D525" t="s">
-        <v>903</v>
+        <v>1133</v>
       </c>
       <c r="E525" t="s">
         <v>105</v>
@@ -11643,13 +11638,13 @@
     </row>
     <row r="526" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B526" t="s">
-        <v>904</v>
+        <v>1134</v>
       </c>
       <c r="C526" t="s">
-        <v>905</v>
+        <v>1135</v>
       </c>
       <c r="D526" t="s">
-        <v>905</v>
+        <v>1135</v>
       </c>
       <c r="E526" t="s">
         <v>105</v>
@@ -11657,13 +11652,13 @@
     </row>
     <row r="527" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B527" t="s">
-        <v>906</v>
+        <v>1136</v>
       </c>
       <c r="C527" t="s">
-        <v>907</v>
+        <v>1137</v>
       </c>
       <c r="D527" t="s">
-        <v>907</v>
+        <v>1137</v>
       </c>
       <c r="E527" t="s">
         <v>105</v>
@@ -11671,13 +11666,13 @@
     </row>
     <row r="528" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B528" t="s">
-        <v>908</v>
+        <v>1138</v>
       </c>
       <c r="C528" t="s">
-        <v>909</v>
+        <v>1139</v>
       </c>
       <c r="D528" t="s">
-        <v>909</v>
+        <v>1139</v>
       </c>
       <c r="E528" t="s">
         <v>105</v>
@@ -11685,13 +11680,13 @@
     </row>
     <row r="529" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B529" t="s">
-        <v>910</v>
+        <v>1140</v>
       </c>
       <c r="C529" t="s">
-        <v>911</v>
+        <v>1141</v>
       </c>
       <c r="D529" t="s">
-        <v>911</v>
+        <v>1141</v>
       </c>
       <c r="E529" t="s">
         <v>105</v>
@@ -11699,13 +11694,13 @@
     </row>
     <row r="530" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B530" t="s">
-        <v>912</v>
+        <v>1142</v>
       </c>
       <c r="C530" t="s">
-        <v>913</v>
+        <v>1143</v>
       </c>
       <c r="D530" t="s">
-        <v>913</v>
+        <v>1143</v>
       </c>
       <c r="E530" t="s">
         <v>105</v>
@@ -11713,13 +11708,13 @@
     </row>
     <row r="531" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B531" t="s">
-        <v>914</v>
+        <v>1144</v>
       </c>
       <c r="C531" t="s">
-        <v>915</v>
+        <v>1145</v>
       </c>
       <c r="D531" t="s">
-        <v>915</v>
+        <v>1145</v>
       </c>
       <c r="E531" t="s">
         <v>105</v>
@@ -11727,13 +11722,13 @@
     </row>
     <row r="532" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B532" t="s">
-        <v>916</v>
+        <v>1146</v>
       </c>
       <c r="C532" t="s">
-        <v>917</v>
+        <v>1147</v>
       </c>
       <c r="D532" t="s">
-        <v>917</v>
+        <v>1147</v>
       </c>
       <c r="E532" t="s">
         <v>105</v>
@@ -11741,13 +11736,13 @@
     </row>
     <row r="533" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B533" t="s">
-        <v>918</v>
+        <v>1148</v>
       </c>
       <c r="C533" t="s">
-        <v>919</v>
+        <v>1149</v>
       </c>
       <c r="D533" t="s">
-        <v>919</v>
+        <v>1149</v>
       </c>
       <c r="E533" t="s">
         <v>105</v>
@@ -11755,13 +11750,13 @@
     </row>
     <row r="534" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B534" t="s">
-        <v>920</v>
+        <v>1150</v>
       </c>
       <c r="C534" t="s">
-        <v>921</v>
+        <v>1151</v>
       </c>
       <c r="D534" t="s">
-        <v>921</v>
+        <v>1151</v>
       </c>
       <c r="E534" t="s">
         <v>105</v>
@@ -11769,13 +11764,13 @@
     </row>
     <row r="535" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B535" t="s">
-        <v>922</v>
+        <v>1152</v>
       </c>
       <c r="C535" t="s">
-        <v>923</v>
+        <v>1153</v>
       </c>
       <c r="D535" t="s">
-        <v>923</v>
+        <v>1153</v>
       </c>
       <c r="E535" t="s">
         <v>105</v>
@@ -11783,13 +11778,13 @@
     </row>
     <row r="536" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B536" t="s">
-        <v>924</v>
+        <v>1154</v>
       </c>
       <c r="C536" t="s">
-        <v>925</v>
+        <v>1155</v>
       </c>
       <c r="D536" t="s">
-        <v>925</v>
+        <v>1155</v>
       </c>
       <c r="E536" t="s">
         <v>105</v>
@@ -11797,13 +11792,13 @@
     </row>
     <row r="537" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B537" t="s">
-        <v>926</v>
+        <v>1156</v>
       </c>
       <c r="C537" t="s">
-        <v>927</v>
+        <v>1157</v>
       </c>
       <c r="D537" t="s">
-        <v>927</v>
+        <v>1157</v>
       </c>
       <c r="E537" t="s">
         <v>105</v>
@@ -11811,13 +11806,13 @@
     </row>
     <row r="538" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B538" t="s">
-        <v>928</v>
+        <v>1158</v>
       </c>
       <c r="C538" t="s">
-        <v>929</v>
+        <v>1159</v>
       </c>
       <c r="D538" t="s">
-        <v>929</v>
+        <v>1159</v>
       </c>
       <c r="E538" t="s">
         <v>105</v>
@@ -11825,13 +11820,13 @@
     </row>
     <row r="539" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B539" t="s">
-        <v>930</v>
+        <v>1160</v>
       </c>
       <c r="C539" t="s">
-        <v>931</v>
+        <v>1161</v>
       </c>
       <c r="D539" t="s">
-        <v>931</v>
+        <v>1161</v>
       </c>
       <c r="E539" t="s">
         <v>105</v>
@@ -11839,13 +11834,13 @@
     </row>
     <row r="540" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B540" t="s">
-        <v>932</v>
+        <v>1162</v>
       </c>
       <c r="C540" t="s">
-        <v>933</v>
+        <v>1163</v>
       </c>
       <c r="D540" t="s">
-        <v>933</v>
+        <v>1163</v>
       </c>
       <c r="E540" t="s">
         <v>105</v>
@@ -11853,13 +11848,13 @@
     </row>
     <row r="541" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B541" t="s">
-        <v>934</v>
+        <v>1164</v>
       </c>
       <c r="C541" t="s">
-        <v>935</v>
+        <v>1165</v>
       </c>
       <c r="D541" t="s">
-        <v>935</v>
+        <v>1165</v>
       </c>
       <c r="E541" t="s">
         <v>105</v>
@@ -11867,13 +11862,13 @@
     </row>
     <row r="542" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B542" t="s">
-        <v>936</v>
+        <v>1166</v>
       </c>
       <c r="C542" t="s">
-        <v>937</v>
+        <v>1167</v>
       </c>
       <c r="D542" t="s">
-        <v>937</v>
+        <v>1167</v>
       </c>
       <c r="E542" t="s">
         <v>105</v>
@@ -11881,13 +11876,13 @@
     </row>
     <row r="543" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B543" t="s">
-        <v>938</v>
+        <v>1168</v>
       </c>
       <c r="C543" t="s">
-        <v>939</v>
+        <v>1169</v>
       </c>
       <c r="D543" t="s">
-        <v>939</v>
+        <v>1169</v>
       </c>
       <c r="E543" t="s">
         <v>105</v>
@@ -11895,13 +11890,13 @@
     </row>
     <row r="544" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B544" t="s">
-        <v>940</v>
+        <v>1170</v>
       </c>
       <c r="C544" t="s">
-        <v>941</v>
+        <v>1171</v>
       </c>
       <c r="D544" t="s">
-        <v>941</v>
+        <v>1171</v>
       </c>
       <c r="E544" t="s">
         <v>105</v>
@@ -11909,13 +11904,13 @@
     </row>
     <row r="545" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B545" t="s">
-        <v>942</v>
+        <v>1172</v>
       </c>
       <c r="C545" t="s">
-        <v>943</v>
+        <v>1173</v>
       </c>
       <c r="D545" t="s">
-        <v>943</v>
+        <v>1173</v>
       </c>
       <c r="E545" t="s">
         <v>105</v>
@@ -11923,13 +11918,13 @@
     </row>
     <row r="546" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B546" t="s">
-        <v>944</v>
+        <v>1174</v>
       </c>
       <c r="C546" t="s">
-        <v>945</v>
+        <v>1175</v>
       </c>
       <c r="D546" t="s">
-        <v>945</v>
+        <v>1175</v>
       </c>
       <c r="E546" t="s">
         <v>105</v>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77EE0EF8-37E8-4FCD-AB7E-7DFB8938EA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D1F9257-838E-49D6-9153-A8E8CA9C9D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033BF57-ED07-4549-AEB9-94914D0266AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415FA84C-BA04-45C8-989B-A5EE441E4361}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D1F9257-838E-49D6-9153-A8E8CA9C9D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5726E500-633C-42D5-B60A-BEA6C72A256A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{415FA84C-BA04-45C8-989B-A5EE441E4361}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EE7463-8442-4C0F-B500-89CCA348612B}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5726E500-633C-42D5-B60A-BEA6C72A256A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{891BF29E-7B8A-4610-8B95-BA2AE6EBBA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EE7463-8442-4C0F-B500-89CCA348612B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030EB6CF-CC52-46FA-812D-CF9F035137D8}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{891BF29E-7B8A-4610-8B95-BA2AE6EBBA98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80E6FF14-BF92-4CCF-9987-F0AF64AEB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{030EB6CF-CC52-46FA-812D-CF9F035137D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47D5805-89E2-4C8E-AF93-994666775183}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80E6FF14-BF92-4CCF-9987-F0AF64AEB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08902068-F277-4EEB-B0A5-3200375BA8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47D5805-89E2-4C8E-AF93-994666775183}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE88A927-0293-4750-967C-F38D6B6AD002}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08902068-F277-4EEB-B0A5-3200375BA8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EDAFBED-5057-42A3-8F5B-0EB8575A956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE88A927-0293-4750-967C-F38D6B6AD002}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{097B38EB-82EB-47FE-9C4B-74260C2F25D9}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EDAFBED-5057-42A3-8F5B-0EB8575A956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD263F13-D5A5-40E7-ADF4-FBEAE9C8B544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{097B38EB-82EB-47FE-9C4B-74260C2F25D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1F01CF-5F7A-4A60-AC3F-740C838A6E9A}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD263F13-D5A5-40E7-ADF4-FBEAE9C8B544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25F7E382-1D54-4D93-8A08-A7D434FE983A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1F01CF-5F7A-4A60-AC3F-740C838A6E9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5D7288-B057-4631-91F5-EEA9A67E677E}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25F7E382-1D54-4D93-8A08-A7D434FE983A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30FABEBF-507F-4B6F-8323-863337CBD15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5D7288-B057-4631-91F5-EEA9A67E677E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE2BC33-3C2E-42AA-8655-F1FFBEEE3BBB}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30FABEBF-507F-4B6F-8323-863337CBD15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FE97B1C-B4AF-46B6-97E2-F9CFC01D1829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE2BC33-3C2E-42AA-8655-F1FFBEEE3BBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23189A35-4FDD-4892-ACFC-CC1AA033C23B}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FE97B1C-B4AF-46B6-97E2-F9CFC01D1829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B889ED5-064B-4B4A-9BC2-C33949E1EC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23189A35-4FDD-4892-ACFC-CC1AA033C23B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DF5F70-5514-4B3E-999F-B29D0224A455}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B889ED5-064B-4B4A-9BC2-C33949E1EC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD6AD5F5-EE6E-49CC-9DF6-67DE3D8AE164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DF5F70-5514-4B3E-999F-B29D0224A455}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA6DE14-266C-42A4-9C82-E98EAF37BBA4}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD6AD5F5-EE6E-49CC-9DF6-67DE3D8AE164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCDC4AB5-01CC-4F06-99AD-BB1C53030F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA6DE14-266C-42A4-9C82-E98EAF37BBA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7D8AEC-77D6-402E-849F-61173D799115}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCDC4AB5-01CC-4F06-99AD-BB1C53030F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73E17CA7-E17A-44D2-A67D-9E4D1C26F50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7D8AEC-77D6-402E-849F-61173D799115}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4483D4B-E279-46C5-B60E-EBD7FD0A0D59}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD796B44-22DD-45B8-9E0A-1E3D662BBEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A724DAD6-ABC2-48CB-A455-EFF13F3D8D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F67B3097-0E1D-4D50-9694-9FF2128C1B22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4295882D-9480-4B1C-AE21-1DE159C975D5}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A724DAD6-ABC2-48CB-A455-EFF13F3D8D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{991A4ED4-D5CE-4BE6-BD6C-C39823DE48AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4295882D-9480-4B1C-AE21-1DE159C975D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEA1F76-A4CC-445B-BFFC-EC64E9EE3403}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{991A4ED4-D5CE-4BE6-BD6C-C39823DE48AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8547E82E-1BFB-4057-9F96-BDB61E065033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFEA1F76-A4CC-445B-BFFC-EC64E9EE3403}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E063FB-4568-42F1-B4FE-4833416D3FE8}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8547E82E-1BFB-4057-9F96-BDB61E065033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6561E6E-C455-47B3-8D82-40D0EB5A245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70E063FB-4568-42F1-B4FE-4833416D3FE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7D564D-C443-4A9B-8140-E02BADA19D9D}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6561E6E-C455-47B3-8D82-40D0EB5A245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DA38621-0AA8-443D-AE9B-4FF2F76B7AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4403,7 +4403,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F7D564D-C443-4A9B-8140-E02BADA19D9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBCD29D0-933A-46A6-BB5D-4B513D82B7E3}">
   <dimension ref="B9:E546"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
